--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Clipboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\clipboard-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FC35D3-F64A-4EDA-B5F8-29AB06F9F3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1B0E4B-F99F-4F43-9B1D-9AFCEAD74785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1665" yWindow="360" windowWidth="27030" windowHeight="13620" activeTab="1" xr2:uid="{366A1260-1365-4B39-9968-5A4EAE027BF5}"/>
+    <workbookView xWindow="1410" yWindow="1395" windowWidth="27030" windowHeight="13620" activeTab="2" xr2:uid="{366A1260-1365-4B39-9968-5A4EAE027BF5}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -920,9 +920,6 @@
     <t>Ceiling Height</t>
   </si>
   <si>
-    <t>ceiling_hight</t>
-  </si>
-  <si>
     <t>Interior Door Materials</t>
   </si>
   <si>
@@ -2958,6 +2955,9 @@
   </si>
   <si>
     <t>bathroom4_updated</t>
+  </si>
+  <si>
+    <t>ceiling_height</t>
   </si>
 </sst>
 </file>
@@ -3230,14 +3230,14 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4033,28 +4033,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -8206,7 +8206,7 @@
         <v>296</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>297</v>
+        <v>976</v>
       </c>
       <c r="F82" s="27" t="s">
         <v>46</v>
@@ -8251,16 +8251,16 @@
         <v>286</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>48</v>
@@ -8301,16 +8301,16 @@
         <v>286</v>
       </c>
       <c r="D84" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>302</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>48</v>
@@ -8348,13 +8348,13 @@
         <v>276</v>
       </c>
       <c r="C85" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>74</v>
@@ -8382,11 +8382,11 @@
       <c r="O85" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P85" s="31" t="s">
+      <c r="P85" s="28" t="s">
         <v>48</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>51</v>
@@ -8400,19 +8400,19 @@
         <v>276</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D86" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>308</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>48</v>
@@ -8450,13 +8450,13 @@
         <v>276</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D87" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>74</v>
@@ -8500,13 +8500,13 @@
         <v>276</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D88" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>74</v>
@@ -8550,13 +8550,13 @@
         <v>276</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D89" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>74</v>
@@ -8600,13 +8600,13 @@
         <v>276</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D90" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>74</v>
@@ -8650,13 +8650,13 @@
         <v>276</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D91" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>319</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>74</v>
@@ -8700,13 +8700,13 @@
         <v>276</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>74</v>
@@ -8750,13 +8750,13 @@
         <v>276</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D93" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>74</v>
@@ -8800,13 +8800,13 @@
         <v>276</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>46</v>
@@ -8816,7 +8816,7 @@
         <v>48</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>48</v>
@@ -8850,19 +8850,19 @@
         <v>276</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D95" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>48</v>
@@ -8900,19 +8900,19 @@
         <v>276</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>48</v>
@@ -8950,19 +8950,19 @@
         <v>276</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D97" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>48</v>
@@ -9000,13 +9000,13 @@
         <v>276</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D98" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>97</v>
@@ -9048,19 +9048,19 @@
         <v>276</v>
       </c>
       <c r="C99" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="E99" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>48</v>
@@ -9086,7 +9086,7 @@
         <v>47</v>
       </c>
       <c r="Q99" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>51</v>
@@ -9100,19 +9100,19 @@
         <v>276</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D100" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>48</v>
@@ -9150,13 +9150,13 @@
         <v>276</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D101" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>97</v>
@@ -9198,19 +9198,19 @@
         <v>276</v>
       </c>
       <c r="C102" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>48</v>
@@ -9248,19 +9248,19 @@
         <v>276</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D103" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>48</v>
@@ -9298,19 +9298,19 @@
         <v>276</v>
       </c>
       <c r="C104" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="E104" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>48</v>
@@ -9351,10 +9351,10 @@
         <v>276</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>97</v>
@@ -9413,22 +9413,22 @@
         <v>1400</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="D107" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="E107" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>48</v>
@@ -9454,7 +9454,7 @@
         <v>47</v>
       </c>
       <c r="Q107" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="R107" s="1" t="s">
         <v>51</v>
@@ -9465,16 +9465,16 @@
         <v>1410</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="D108" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>74</v>
@@ -9515,22 +9515,22 @@
         <v>1420</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C109" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>48</v>
@@ -9556,7 +9556,7 @@
         <v>47</v>
       </c>
       <c r="Q109" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R109" s="1" t="s">
         <v>51</v>
@@ -9567,16 +9567,16 @@
         <v>1430</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D110" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>74</v>
@@ -9617,22 +9617,22 @@
         <v>1440</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C111" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="E111" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>48</v>
@@ -9658,7 +9658,7 @@
         <v>47</v>
       </c>
       <c r="Q111" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>51</v>
@@ -9669,22 +9669,22 @@
         <v>1450</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C112" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="E112" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>48</v>
@@ -9710,7 +9710,7 @@
         <v>47</v>
       </c>
       <c r="Q112" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R112" s="1" t="s">
         <v>51</v>
@@ -9721,16 +9721,16 @@
         <v>1460</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>131</v>
       </c>
       <c r="D113" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>91</v>
@@ -9771,16 +9771,16 @@
         <v>1470</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>131</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>91</v>
@@ -9821,16 +9821,16 @@
         <v>1480</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>131</v>
       </c>
       <c r="D115" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>386</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>91</v>
@@ -9871,16 +9871,16 @@
         <v>1490</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C116" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>91</v>
@@ -9921,16 +9921,16 @@
         <v>1500</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D117" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>97</v>
@@ -9989,19 +9989,19 @@
         <v>1600</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="F119" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
@@ -10021,7 +10021,7 @@
         <v>49</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O119" s="1" t="s">
         <v>47</v>
@@ -10039,19 +10039,19 @@
         <v>1610</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="D120" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="F120" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
@@ -10087,19 +10087,19 @@
         <v>1620</v>
       </c>
       <c r="B121" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="D121" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="F121" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1" t="s">
@@ -10119,7 +10119,7 @@
         <v>49</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O121" s="1" t="s">
         <v>47</v>
@@ -10157,19 +10157,19 @@
         <v>1700</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="E123" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E123" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="F123" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="1" t="s">
@@ -10189,7 +10189,7 @@
         <v>49</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="O123" s="1" t="s">
         <v>47</v>
@@ -10207,22 +10207,22 @@
         <v>1710</v>
       </c>
       <c r="B124" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="D124" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E124" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="F124" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G124" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>410</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>48</v>
@@ -10257,16 +10257,16 @@
         <v>1800</v>
       </c>
       <c r="B125" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="E125" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>97</v>
@@ -10372,7 +10372,7 @@
         <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>28</v>
@@ -10401,22 +10401,22 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B2" s="1">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>418</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>48</v>
@@ -10432,16 +10432,16 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B3" s="1">
         <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>97</v>
@@ -10461,16 +10461,16 @@
     </row>
     <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B4" s="1">
         <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>97</v>
@@ -10490,16 +10490,16 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B5" s="1">
         <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>967</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>968</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>46</v>
@@ -10519,16 +10519,16 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B6" s="1">
         <v>50</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>969</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>970</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>46</v>
@@ -10548,16 +10548,16 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B7" s="1">
         <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>971</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>972</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>46</v>
@@ -10577,16 +10577,16 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B8" s="1">
         <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>973</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>974</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>46</v>
@@ -10606,16 +10606,16 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B9" s="1">
         <v>80</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>976</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>46</v>
@@ -10635,16 +10635,16 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B10" s="1">
         <v>90</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>91</v>
@@ -10664,16 +10664,16 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B11" s="1">
         <v>100</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>97</v>
@@ -10712,13 +10712,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>430</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
@@ -10741,16 +10741,16 @@
         <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>48</v>
@@ -10772,16 +10772,16 @@
         <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>48</v>
@@ -10803,16 +10803,16 @@
         <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>438</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>48</v>
@@ -10834,10 +10834,10 @@
         <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>441</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>91</v>
@@ -10863,13 +10863,13 @@
         <v>60</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -10892,13 +10892,13 @@
         <v>70</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>447</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -10921,10 +10921,10 @@
         <v>80</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>97</v>
@@ -10963,13 +10963,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
@@ -10992,16 +10992,16 @@
         <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>48</v>
@@ -11023,16 +11023,16 @@
         <v>30</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>48</v>
@@ -11054,10 +11054,10 @@
         <v>40</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>91</v>
@@ -11083,13 +11083,13 @@
         <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1" t="s">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -11112,13 +11112,13 @@
         <v>60</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -11141,10 +11141,10 @@
         <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>97</v>
@@ -11183,10 +11183,10 @@
         <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>463</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>91</v>
@@ -11212,10 +11212,10 @@
         <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>465</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>46</v>
@@ -11241,10 +11241,10 @@
         <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>91</v>
@@ -11270,16 +11270,16 @@
         <v>40</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>48</v>
@@ -11301,10 +11301,10 @@
         <v>50</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>97</v>
@@ -11343,16 +11343,16 @@
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>48</v>
@@ -11374,10 +11374,10 @@
         <v>20</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>46</v>
@@ -11403,13 +11403,13 @@
         <v>30</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="E38" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -11432,10 +11432,10 @@
         <v>40</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>481</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>46</v>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -11461,10 +11461,10 @@
         <v>50</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>91</v>
@@ -11490,10 +11490,10 @@
         <v>60</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>91</v>
@@ -11519,10 +11519,10 @@
         <v>70</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>97</v>
@@ -11561,10 +11561,10 @@
         <v>10</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>91</v>
@@ -11590,10 +11590,10 @@
         <v>20</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>46</v>
@@ -11619,10 +11619,10 @@
         <v>30</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>494</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>91</v>
@@ -11648,10 +11648,10 @@
         <v>40</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>496</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>97</v>
@@ -11684,16 +11684,16 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B49" s="1">
         <v>10</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>498</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>91</v>
@@ -11713,16 +11713,16 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B50" s="1">
         <v>20</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>500</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>46</v>
@@ -11742,22 +11742,22 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B51" s="1">
         <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>48</v>
@@ -11773,16 +11773,16 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B52" s="1">
         <v>40</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>91</v>
@@ -11802,16 +11802,16 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B53" s="1">
         <v>50</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>507</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>97</v>
@@ -11844,16 +11844,16 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B55" s="1">
         <v>10</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>508</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>91</v>
@@ -11873,22 +11873,22 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B56" s="1">
         <v>20</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>48</v>
@@ -11904,16 +11904,16 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B57" s="1">
         <v>30</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>46</v>
@@ -11933,16 +11933,16 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B58" s="1">
         <v>40</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>91</v>
@@ -11962,16 +11962,16 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B59" s="1">
         <v>50</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>97</v>
@@ -12004,16 +12004,16 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B61" s="1">
         <v>10</v>
       </c>
       <c r="C61" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>91</v>
@@ -12033,16 +12033,16 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B62" s="1">
         <v>20</v>
       </c>
       <c r="C62" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>521</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>46</v>
@@ -12062,16 +12062,16 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B63" s="1">
         <v>30</v>
       </c>
       <c r="C63" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>523</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>91</v>
@@ -12091,16 +12091,16 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B64" s="1">
         <v>40</v>
       </c>
       <c r="C64" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>525</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>97</v>
@@ -12133,16 +12133,16 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B66" s="1">
         <v>10</v>
       </c>
       <c r="C66" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>91</v>
@@ -12162,16 +12162,16 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B67" s="1">
         <v>20</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>46</v>
@@ -12191,16 +12191,16 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B68" s="1">
         <v>30</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>97</v>
@@ -12239,10 +12239,10 @@
         <v>10</v>
       </c>
       <c r="C70" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>532</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>46</v>
@@ -12268,10 +12268,10 @@
         <v>20</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>534</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>91</v>
@@ -12297,10 +12297,10 @@
         <v>30</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>536</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>91</v>
@@ -12326,10 +12326,10 @@
         <v>40</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>538</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>97</v>
@@ -12368,10 +12368,10 @@
         <v>10</v>
       </c>
       <c r="C75" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>540</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>46</v>
@@ -12397,16 +12397,16 @@
         <v>20</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>48</v>
@@ -12428,10 +12428,10 @@
         <v>30</v>
       </c>
       <c r="C77" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>545</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>91</v>
@@ -12457,10 +12457,10 @@
         <v>40</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>91</v>
@@ -12486,10 +12486,10 @@
         <v>50</v>
       </c>
       <c r="C79" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>97</v>
@@ -12528,10 +12528,10 @@
         <v>10</v>
       </c>
       <c r="C81" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>551</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>46</v>
@@ -12557,16 +12557,16 @@
         <v>20</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>48</v>
@@ -12588,10 +12588,10 @@
         <v>30</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>91</v>
@@ -12617,10 +12617,10 @@
         <v>40</v>
       </c>
       <c r="C84" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>557</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>97</v>
@@ -12659,16 +12659,16 @@
         <v>10</v>
       </c>
       <c r="C86" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>559</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>48</v>
@@ -12690,10 +12690,10 @@
         <v>20</v>
       </c>
       <c r="C87" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>562</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>46</v>
@@ -12719,10 +12719,10 @@
         <v>30</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>91</v>
@@ -12748,16 +12748,16 @@
         <v>40</v>
       </c>
       <c r="C89" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>564</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>565</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>48</v>
@@ -12779,10 +12779,10 @@
         <v>50</v>
       </c>
       <c r="C90" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>567</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>568</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>97</v>
@@ -12821,10 +12821,10 @@
         <v>10</v>
       </c>
       <c r="C92" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>570</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>91</v>
@@ -12850,16 +12850,16 @@
         <v>20</v>
       </c>
       <c r="C93" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>572</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>48</v>
@@ -12881,10 +12881,10 @@
         <v>30</v>
       </c>
       <c r="C94" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>575</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>97</v>
@@ -12923,10 +12923,10 @@
         <v>10</v>
       </c>
       <c r="C96" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>577</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>91</v>
@@ -12952,10 +12952,10 @@
         <v>20</v>
       </c>
       <c r="C97" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>579</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>46</v>
@@ -12981,10 +12981,10 @@
         <v>30</v>
       </c>
       <c r="C98" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>97</v>
@@ -13023,10 +13023,10 @@
         <v>10</v>
       </c>
       <c r="C100" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>583</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>46</v>
@@ -13052,10 +13052,10 @@
         <v>20</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>91</v>
@@ -13081,10 +13081,10 @@
         <v>30</v>
       </c>
       <c r="C102" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>585</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>586</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>97</v>
@@ -13110,10 +13110,10 @@
         <v>40</v>
       </c>
       <c r="C103" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>588</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>97</v>
@@ -13152,10 +13152,10 @@
         <v>10</v>
       </c>
       <c r="C105" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>590</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>91</v>
@@ -13181,16 +13181,16 @@
         <v>20</v>
       </c>
       <c r="C106" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>591</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>592</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>48</v>
@@ -13212,10 +13212,10 @@
         <v>30</v>
       </c>
       <c r="C107" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>595</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>97</v>
@@ -13248,16 +13248,16 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B109" s="1">
         <v>10</v>
       </c>
       <c r="C109" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>597</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>91</v>
@@ -13277,16 +13277,16 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B110" s="1">
         <v>20</v>
       </c>
       <c r="C110" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>599</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>46</v>
@@ -13306,16 +13306,16 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B111" s="1">
         <v>30</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>91</v>
@@ -13335,16 +13335,16 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B112" s="1">
         <v>40</v>
       </c>
       <c r="C112" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>97</v>
@@ -13364,16 +13364,16 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B113" s="1">
         <v>10</v>
       </c>
       <c r="C113" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>604</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>91</v>
@@ -13393,16 +13393,16 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B114" s="1">
         <v>20</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>46</v>
@@ -13422,16 +13422,16 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B115" s="1">
         <v>30</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>91</v>
@@ -13451,16 +13451,16 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B116" s="1">
         <v>40</v>
       </c>
       <c r="C116" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>608</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>97</v>
@@ -13626,70 +13626,70 @@
         <v>295</v>
       </c>
       <c r="AM1" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AN1" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AO1" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AP1" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AQ1" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AR1" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AS1" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AT1" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AU1" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AV1" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AW1" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AX1" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AY1" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AZ1" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="BA1" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="BB1" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="BC1" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="BD1" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="BE1" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="BF1" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BG1" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="BH1" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="BI1" s="5" t="s">
         <v>213</v>
@@ -13698,33 +13698,33 @@
         <v>217</v>
       </c>
       <c r="BK1" s="5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="BL1" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="BM1" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="BN1" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="BO1" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="BP1" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="BQ1" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BR1" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -13736,7 +13736,7 @@
         <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F2" t="s">
         <v>84</v>
@@ -13745,25 +13745,25 @@
         <v>88</v>
       </c>
       <c r="H2" t="s">
+        <v>610</v>
+      </c>
+      <c r="I2" t="s">
         <v>611</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>612</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>612</v>
+      </c>
+      <c r="L2" t="s">
         <v>613</v>
       </c>
-      <c r="K2" t="s">
-        <v>613</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>614</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>615</v>
-      </c>
-      <c r="N2" t="s">
-        <v>616</v>
       </c>
       <c r="O2" t="s">
         <v>151</v>
@@ -13772,425 +13772,425 @@
         <v>138</v>
       </c>
       <c r="Q2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="R2" t="s">
         <v>151</v>
       </c>
       <c r="S2" t="s">
+        <v>617</v>
+      </c>
+      <c r="T2" t="s">
         <v>618</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
+        <v>618</v>
+      </c>
+      <c r="V2" t="s">
         <v>619</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
+        <v>620</v>
+      </c>
+      <c r="X2" t="s">
+        <v>621</v>
+      </c>
+      <c r="Y2" t="s">
         <v>619</v>
       </c>
-      <c r="V2" t="s">
-        <v>620</v>
-      </c>
-      <c r="W2" t="s">
-        <v>621</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>622</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>620</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>623</v>
       </c>
       <c r="AA2" t="s">
         <v>151</v>
       </c>
       <c r="AB2" t="s">
+        <v>623</v>
+      </c>
+      <c r="AC2" t="s">
         <v>624</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>625</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>626</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>627</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
+        <v>626</v>
+      </c>
+      <c r="AH2" t="s">
         <v>628</v>
       </c>
-      <c r="AG2" t="s">
-        <v>627</v>
-      </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>629</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>630</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>631</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
+        <v>631</v>
+      </c>
+      <c r="AM2" t="s">
         <v>632</v>
       </c>
-      <c r="AL2" t="s">
-        <v>632</v>
-      </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>633</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
+        <v>309</v>
+      </c>
+      <c r="AP2" t="s">
         <v>634</v>
       </c>
-      <c r="AO2" t="s">
-        <v>310</v>
-      </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
+        <v>626</v>
+      </c>
+      <c r="AR2" t="s">
         <v>635</v>
       </c>
-      <c r="AQ2" t="s">
-        <v>627</v>
-      </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>636</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
+        <v>630</v>
+      </c>
+      <c r="AU2" t="s">
         <v>637</v>
       </c>
-      <c r="AT2" t="s">
-        <v>631</v>
-      </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>638</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>639</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>640</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>641</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>642</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>643</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>644</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>645</v>
       </c>
       <c r="BC2" t="s">
         <v>70</v>
       </c>
       <c r="BD2" t="s">
+        <v>645</v>
+      </c>
+      <c r="BE2" t="s">
         <v>646</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>647</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
+        <v>647</v>
+      </c>
+      <c r="BH2" t="s">
         <v>648</v>
       </c>
-      <c r="BG2" t="s">
-        <v>648</v>
-      </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>649</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
+        <v>47</v>
+      </c>
+      <c r="BK2" t="s">
         <v>650</v>
       </c>
-      <c r="BJ2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>651</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>652</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BN2" t="s">
         <v>653</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BO2" t="s">
         <v>654</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BP2" t="s">
         <v>655</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BQ2" t="s">
         <v>656</v>
       </c>
-      <c r="BQ2" t="s">
-        <v>657</v>
-      </c>
       <c r="BR2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>657</v>
+      </c>
+      <c r="B3" t="s">
         <v>658</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>659</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>660</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>661</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>662</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>663</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>615</v>
+      </c>
+      <c r="I3" t="s">
         <v>664</v>
       </c>
-      <c r="H3" t="s">
-        <v>616</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>665</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
+        <v>665</v>
+      </c>
+      <c r="L3" t="s">
         <v>666</v>
       </c>
-      <c r="K3" t="s">
-        <v>666</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>667</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
+        <v>610</v>
+      </c>
+      <c r="O3" t="s">
         <v>668</v>
       </c>
-      <c r="N3" t="s">
-        <v>611</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>669</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>670</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>671</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>672</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>673</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
+        <v>619</v>
+      </c>
+      <c r="V3" t="s">
         <v>674</v>
       </c>
-      <c r="U3" t="s">
-        <v>620</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>675</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>676</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
+        <v>626</v>
+      </c>
+      <c r="Z3" t="s">
         <v>677</v>
       </c>
-      <c r="Y3" t="s">
-        <v>627</v>
-      </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>678</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>679</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>680</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>681</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
         <v>682</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AF3" t="s">
         <v>683</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AG3" t="s">
         <v>684</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AH3" t="s">
         <v>685</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AI3" t="s">
         <v>686</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
+        <v>626</v>
+      </c>
+      <c r="AK3" t="s">
         <v>687</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>627</v>
-      </c>
-      <c r="AK3" t="s">
+      <c r="AL3" t="s">
+        <v>687</v>
+      </c>
+      <c r="AM3" t="s">
         <v>688</v>
       </c>
-      <c r="AL3" t="s">
-        <v>688</v>
-      </c>
-      <c r="AM3" t="s">
+      <c r="AN3" t="s">
         <v>689</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AO3" t="s">
         <v>690</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AP3" t="s">
+        <v>630</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>634</v>
+      </c>
+      <c r="AR3" t="s">
         <v>691</v>
       </c>
-      <c r="AP3" t="s">
-        <v>631</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>635</v>
-      </c>
-      <c r="AR3" t="s">
+      <c r="AS3" t="s">
         <v>692</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AT3" t="s">
         <v>693</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="AU3" t="s">
+        <v>303</v>
+      </c>
+      <c r="AV3" t="s">
         <v>694</v>
       </c>
-      <c r="AU3" t="s">
-        <v>304</v>
-      </c>
-      <c r="AV3" t="s">
+      <c r="AW3" t="s">
         <v>695</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="AX3" t="s">
         <v>696</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="AY3" t="s">
         <v>697</v>
       </c>
-      <c r="AY3" t="s">
+      <c r="AZ3" t="s">
         <v>698</v>
       </c>
-      <c r="AZ3" t="s">
+      <c r="BA3" t="s">
         <v>699</v>
       </c>
-      <c r="BA3" t="s">
+      <c r="BB3" t="s">
         <v>700</v>
       </c>
-      <c r="BB3" t="s">
+      <c r="BC3" t="s">
         <v>701</v>
       </c>
-      <c r="BC3" t="s">
+      <c r="BD3" t="s">
         <v>702</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>703</v>
       </c>
       <c r="BE3" t="s">
         <v>258</v>
       </c>
       <c r="BF3" t="s">
+        <v>703</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>703</v>
+      </c>
+      <c r="BH3" t="s">
         <v>704</v>
       </c>
-      <c r="BG3" t="s">
-        <v>704</v>
-      </c>
-      <c r="BH3" t="s">
+      <c r="BI3" t="s">
         <v>705</v>
       </c>
-      <c r="BI3" t="s">
+      <c r="BJ3" t="s">
+        <v>48</v>
+      </c>
+      <c r="BK3" t="s">
         <v>706</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>48</v>
-      </c>
-      <c r="BK3" t="s">
+      <c r="BL3" t="s">
         <v>707</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BM3" t="s">
+        <v>653</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>652</v>
+      </c>
+      <c r="BO3" t="s">
         <v>708</v>
       </c>
-      <c r="BM3" t="s">
-        <v>654</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>653</v>
-      </c>
-      <c r="BO3" t="s">
+      <c r="BP3" t="s">
         <v>709</v>
       </c>
-      <c r="BP3" t="s">
+      <c r="BQ3" t="s">
         <v>710</v>
       </c>
-      <c r="BQ3" t="s">
+      <c r="BR3" t="s">
         <v>711</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B4" t="s">
+        <v>712</v>
+      </c>
+      <c r="C4" t="s">
         <v>713</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>714</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>715</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>716</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>717</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>718</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>719</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>720</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>721</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>722</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>723</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
+        <v>718</v>
+      </c>
+      <c r="O4" t="s">
         <v>724</v>
-      </c>
-      <c r="N4" t="s">
-        <v>719</v>
-      </c>
-      <c r="O4" t="s">
-        <v>725</v>
       </c>
       <c r="P4" t="s">
         <v>140</v>
@@ -14199,756 +14199,756 @@
         <v>144</v>
       </c>
       <c r="R4" t="s">
+        <v>725</v>
+      </c>
+      <c r="S4" t="s">
         <v>726</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
+        <v>626</v>
+      </c>
+      <c r="U4" t="s">
         <v>727</v>
       </c>
-      <c r="T4" t="s">
-        <v>627</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>728</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>729</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>730</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>731</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>732</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>733</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>734</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>735</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>736</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>737</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>738</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AG4" t="s">
+        <v>615</v>
+      </c>
+      <c r="AH4" t="s">
         <v>739</v>
       </c>
-      <c r="AG4" t="s">
-        <v>616</v>
-      </c>
-      <c r="AH4" t="s">
+      <c r="AI4" t="s">
         <v>740</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
+        <v>634</v>
+      </c>
+      <c r="AK4" t="s">
         <v>741</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>635</v>
-      </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
+        <v>626</v>
+      </c>
+      <c r="AM4" t="s">
         <v>742</v>
       </c>
-      <c r="AL4" t="s">
-        <v>627</v>
-      </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>743</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
+        <v>313</v>
+      </c>
+      <c r="AP4" t="s">
         <v>744</v>
       </c>
-      <c r="AO4" t="s">
-        <v>314</v>
-      </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>745</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>746</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>747</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>748</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>749</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>750</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>751</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>752</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>753</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>754</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>755</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>756</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BC4" t="s">
+        <v>714</v>
+      </c>
+      <c r="BD4" t="s">
         <v>757</v>
       </c>
-      <c r="BC4" t="s">
-        <v>715</v>
-      </c>
-      <c r="BD4" t="s">
+      <c r="BE4" t="s">
         <v>758</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BF4" t="s">
+        <v>709</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>709</v>
+      </c>
+      <c r="BH4" t="s">
         <v>759</v>
       </c>
-      <c r="BF4" t="s">
-        <v>710</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>710</v>
-      </c>
-      <c r="BH4" t="s">
+      <c r="BJ4" t="s">
         <v>760</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BK4" t="s">
         <v>761</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BL4" t="s">
         <v>762</v>
       </c>
-      <c r="BL4" t="s">
+      <c r="BM4" t="s">
         <v>763</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BN4" t="s">
         <v>764</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BO4" t="s">
+        <v>764</v>
+      </c>
+      <c r="BP4" t="s">
         <v>765</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>765</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>766</v>
       </c>
       <c r="BQ4" t="s">
         <v>258</v>
       </c>
       <c r="BR4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>766</v>
+      </c>
+      <c r="C5" t="s">
+        <v>719</v>
+      </c>
+      <c r="D5" t="s">
         <v>767</v>
       </c>
-      <c r="C5" t="s">
-        <v>720</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>768</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>769</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>770</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>771</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>671</v>
+      </c>
+      <c r="L5" t="s">
         <v>772</v>
       </c>
-      <c r="K5" t="s">
-        <v>672</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>773</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
+        <v>630</v>
+      </c>
+      <c r="O5" t="s">
+        <v>719</v>
+      </c>
+      <c r="P5" t="s">
         <v>774</v>
       </c>
-      <c r="N5" t="s">
-        <v>631</v>
-      </c>
-      <c r="O5" t="s">
-        <v>720</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
+        <v>719</v>
+      </c>
+      <c r="R5" t="s">
         <v>775</v>
       </c>
-      <c r="Q5" t="s">
-        <v>720</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>776</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>777</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>778</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>779</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>780</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>781</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>782</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>783</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
         <v>784</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>785</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>786</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>787</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>788</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
         <v>789</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AG5" t="s">
+        <v>630</v>
+      </c>
+      <c r="AH5" t="s">
         <v>790</v>
       </c>
-      <c r="AG5" t="s">
-        <v>631</v>
-      </c>
-      <c r="AH5" t="s">
+      <c r="AI5" t="s">
         <v>791</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AJ5" t="s">
         <v>792</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AK5" t="s">
         <v>793</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AL5" t="s">
         <v>794</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AM5" t="s">
         <v>795</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AN5" t="s">
         <v>796</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AO5" t="s">
         <v>797</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="AP5" t="s">
         <v>798</v>
       </c>
-      <c r="AP5" t="s">
+      <c r="AQ5" t="s">
+        <v>780</v>
+      </c>
+      <c r="AR5" t="s">
         <v>799</v>
       </c>
-      <c r="AQ5" t="s">
-        <v>781</v>
-      </c>
-      <c r="AR5" t="s">
+      <c r="AS5" t="s">
         <v>800</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AT5" t="s">
         <v>801</v>
       </c>
-      <c r="AT5" t="s">
+      <c r="AU5" t="s">
+        <v>625</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>386</v>
+      </c>
+      <c r="AW5" t="s">
         <v>802</v>
       </c>
-      <c r="AU5" t="s">
-        <v>626</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>387</v>
-      </c>
-      <c r="AW5" t="s">
+      <c r="AX5" t="s">
         <v>803</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AY5" t="s">
         <v>804</v>
       </c>
-      <c r="AY5" t="s">
+      <c r="AZ5" t="s">
+        <v>719</v>
+      </c>
+      <c r="BA5" t="s">
         <v>805</v>
       </c>
-      <c r="AZ5" t="s">
-        <v>720</v>
-      </c>
-      <c r="BA5" t="s">
+      <c r="BB5" t="s">
         <v>806</v>
       </c>
-      <c r="BB5" t="s">
+      <c r="BC5" t="s">
         <v>807</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BD5" t="s">
         <v>808</v>
       </c>
-      <c r="BD5" t="s">
+      <c r="BE5" t="s">
         <v>809</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BF5" t="s">
         <v>810</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BG5" t="s">
+        <v>810</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>964</v>
+      </c>
+      <c r="BM5" t="s">
         <v>811</v>
       </c>
-      <c r="BG5" t="s">
-        <v>811</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>965</v>
-      </c>
-      <c r="BM5" t="s">
+      <c r="BN5" t="s">
         <v>812</v>
       </c>
-      <c r="BN5" t="s">
-        <v>813</v>
-      </c>
       <c r="BO5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="BP5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BQ5" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>813</v>
+      </c>
+      <c r="D6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E6" t="s">
+        <v>712</v>
+      </c>
+      <c r="F6" t="s">
         <v>814</v>
       </c>
-      <c r="D6" t="s">
-        <v>387</v>
-      </c>
-      <c r="E6" t="s">
-        <v>713</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>815</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>816</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
+        <v>725</v>
+      </c>
+      <c r="L6" t="s">
+        <v>386</v>
+      </c>
+      <c r="M6" t="s">
+        <v>719</v>
+      </c>
+      <c r="N6" t="s">
         <v>817</v>
       </c>
-      <c r="K6" t="s">
-        <v>726</v>
-      </c>
-      <c r="L6" t="s">
-        <v>387</v>
-      </c>
-      <c r="M6" t="s">
-        <v>720</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="P6" t="s">
+        <v>719</v>
+      </c>
+      <c r="R6" t="s">
         <v>818</v>
       </c>
-      <c r="P6" t="s">
-        <v>720</v>
-      </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>819</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>820</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
+        <v>682</v>
+      </c>
+      <c r="V6" t="s">
         <v>821</v>
       </c>
-      <c r="U6" t="s">
-        <v>683</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>822</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>823</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>824</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Z6" t="s">
         <v>825</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AA6" t="s">
         <v>826</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
         <v>827</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AC6" t="s">
         <v>828</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AD6" t="s">
         <v>829</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>830</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AF6" t="s">
         <v>831</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AG6" t="s">
         <v>832</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AH6" t="s">
         <v>833</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AI6" t="s">
+        <v>809</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>778</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>630</v>
+      </c>
+      <c r="AL6" t="s">
         <v>834</v>
       </c>
-      <c r="AI6" t="s">
-        <v>810</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>779</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>631</v>
-      </c>
-      <c r="AL6" t="s">
+      <c r="AM6" t="s">
+        <v>780</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>386</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>317</v>
+      </c>
+      <c r="AP6" t="s">
         <v>835</v>
       </c>
-      <c r="AM6" t="s">
-        <v>781</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>387</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>318</v>
-      </c>
-      <c r="AP6" t="s">
+      <c r="AQ6" t="s">
         <v>836</v>
       </c>
-      <c r="AQ6" t="s">
+      <c r="AR6" t="s">
         <v>837</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AS6" t="s">
         <v>838</v>
       </c>
-      <c r="AS6" t="s">
+      <c r="AT6" t="s">
+        <v>634</v>
+      </c>
+      <c r="AU6" t="s">
         <v>839</v>
       </c>
-      <c r="AT6" t="s">
-        <v>635</v>
-      </c>
-      <c r="AU6" t="s">
+      <c r="AW6" t="s">
+        <v>386</v>
+      </c>
+      <c r="AX6" t="s">
         <v>840</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>387</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>841</v>
       </c>
       <c r="AY6" t="s">
         <v>197</v>
       </c>
       <c r="AZ6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BA6" t="s">
+        <v>841</v>
+      </c>
+      <c r="BB6" t="s">
         <v>842</v>
       </c>
-      <c r="BB6" t="s">
+      <c r="BC6" t="s">
         <v>843</v>
       </c>
-      <c r="BC6" t="s">
+      <c r="BD6" t="s">
+        <v>386</v>
+      </c>
+      <c r="BE6" t="s">
         <v>844</v>
       </c>
-      <c r="BD6" t="s">
-        <v>387</v>
-      </c>
-      <c r="BE6" t="s">
+      <c r="BF6" t="s">
         <v>845</v>
       </c>
-      <c r="BF6" t="s">
-        <v>846</v>
-      </c>
       <c r="BG6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="BL6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="BM6" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="BN6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="BO6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="BQ6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>846</v>
+      </c>
+      <c r="E7" t="s">
         <v>847</v>
       </c>
-      <c r="E7" t="s">
+      <c r="H7" t="s">
+        <v>817</v>
+      </c>
+      <c r="J7" t="s">
         <v>848</v>
       </c>
-      <c r="H7" t="s">
-        <v>818</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
+        <v>775</v>
+      </c>
+      <c r="N7" t="s">
+        <v>770</v>
+      </c>
+      <c r="R7" t="s">
         <v>849</v>
       </c>
-      <c r="K7" t="s">
-        <v>776</v>
-      </c>
-      <c r="N7" t="s">
-        <v>771</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>850</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
+        <v>386</v>
+      </c>
+      <c r="U7" t="s">
+        <v>626</v>
+      </c>
+      <c r="V7" t="s">
         <v>851</v>
       </c>
-      <c r="T7" t="s">
-        <v>387</v>
-      </c>
-      <c r="U7" t="s">
-        <v>627</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>852</v>
       </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
         <v>853</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
+        <v>386</v>
+      </c>
+      <c r="Z7" t="s">
         <v>854</v>
       </c>
-      <c r="Y7" t="s">
-        <v>387</v>
-      </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
         <v>855</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>856</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AC7" t="s">
         <v>857</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AD7" t="s">
         <v>858</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>859</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>860</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AG7" t="s">
+        <v>386</v>
+      </c>
+      <c r="AH7" t="s">
         <v>861</v>
       </c>
-      <c r="AG7" t="s">
-        <v>387</v>
-      </c>
-      <c r="AH7" t="s">
+      <c r="AI7" t="s">
+        <v>386</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>862</v>
       </c>
-      <c r="AI7" t="s">
-        <v>387</v>
-      </c>
-      <c r="AJ7" t="s">
+      <c r="AK7" t="s">
+        <v>626</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>386</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>386</v>
+      </c>
+      <c r="AO7" t="s">
         <v>863</v>
       </c>
-      <c r="AK7" t="s">
-        <v>627</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>387</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>387</v>
-      </c>
-      <c r="AO7" t="s">
+      <c r="AP7" t="s">
         <v>864</v>
       </c>
-      <c r="AP7" t="s">
+      <c r="AQ7" t="s">
+        <v>386</v>
+      </c>
+      <c r="AR7" t="s">
         <v>865</v>
       </c>
-      <c r="AQ7" t="s">
-        <v>387</v>
-      </c>
-      <c r="AR7" t="s">
+      <c r="AS7" t="s">
         <v>866</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="AT7" t="s">
+        <v>386</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>386</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>386</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>386</v>
+      </c>
+      <c r="BA7" t="s">
         <v>867</v>
       </c>
-      <c r="AT7" t="s">
-        <v>387</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>387</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>387</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>387</v>
-      </c>
-      <c r="BA7" t="s">
+      <c r="BB7" t="s">
         <v>868</v>
       </c>
-      <c r="BB7" t="s">
+      <c r="BC7" t="s">
         <v>869</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BE7" t="s">
         <v>870</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BF7" t="s">
         <v>871</v>
       </c>
-      <c r="BF7" t="s">
+      <c r="BG7" t="s">
+        <v>871</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>386</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>346</v>
+      </c>
+      <c r="BN7" t="s">
         <v>872</v>
       </c>
-      <c r="BG7" t="s">
-        <v>872</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>387</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>347</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>873</v>
-      </c>
       <c r="BO7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>873</v>
+      </c>
+      <c r="E8" t="s">
         <v>874</v>
       </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
+        <v>386</v>
+      </c>
+      <c r="J8" t="s">
         <v>875</v>
       </c>
-      <c r="H8" t="s">
-        <v>387</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
+        <v>818</v>
+      </c>
+      <c r="N8" t="s">
         <v>876</v>
       </c>
-      <c r="K8" t="s">
-        <v>819</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="R8" t="s">
         <v>877</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
+        <v>386</v>
+      </c>
+      <c r="U8" t="s">
+        <v>824</v>
+      </c>
+      <c r="V8" t="s">
+        <v>780</v>
+      </c>
+      <c r="W8" t="s">
         <v>878</v>
       </c>
-      <c r="S8" t="s">
-        <v>387</v>
-      </c>
-      <c r="U8" t="s">
+      <c r="X8" t="s">
+        <v>721</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>879</v>
+      </c>
+      <c r="AA8" t="s">
         <v>825</v>
       </c>
-      <c r="V8" t="s">
-        <v>781</v>
-      </c>
-      <c r="W8" t="s">
-        <v>879</v>
-      </c>
-      <c r="X8" t="s">
-        <v>722</v>
-      </c>
-      <c r="Z8" t="s">
+      <c r="AB8" t="s">
+        <v>386</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>386</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>386</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>386</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>386</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>748</v>
+      </c>
+      <c r="AJ8" t="s">
         <v>880</v>
       </c>
-      <c r="AA8" t="s">
-        <v>826</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>387</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>387</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>387</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>387</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>387</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>749</v>
-      </c>
-      <c r="AJ8" t="s">
+      <c r="AK8" t="s">
+        <v>386</v>
+      </c>
+      <c r="AO8" t="s">
         <v>881</v>
       </c>
-      <c r="AK8" t="s">
-        <v>387</v>
-      </c>
-      <c r="AO8" t="s">
+      <c r="AP8" t="s">
         <v>882</v>
       </c>
-      <c r="AP8" t="s">
+      <c r="AR8" t="s">
         <v>883</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AS8" t="s">
         <v>884</v>
       </c>
-      <c r="AS8" t="s">
+      <c r="BA8" t="s">
         <v>885</v>
       </c>
-      <c r="BA8" t="s">
+      <c r="BB8" t="s">
         <v>886</v>
       </c>
-      <c r="BB8" t="s">
+      <c r="BC8" t="s">
+        <v>386</v>
+      </c>
+      <c r="BE8" t="s">
         <v>887</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>387</v>
-      </c>
-      <c r="BE8" t="s">
-        <v>888</v>
       </c>
       <c r="BF8" t="s">
         <v>177</v>
@@ -14957,190 +14957,190 @@
         <v>177</v>
       </c>
       <c r="BM8" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="BN8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BO8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>889</v>
+      </c>
+      <c r="E9" t="s">
+        <v>658</v>
+      </c>
+      <c r="J9" t="s">
         <v>890</v>
       </c>
-      <c r="E9" t="s">
-        <v>659</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>891</v>
       </c>
-      <c r="K9" t="s">
+      <c r="N9" t="s">
         <v>892</v>
       </c>
-      <c r="N9" t="s">
+      <c r="R9" t="s">
         <v>893</v>
       </c>
-      <c r="R9" t="s">
+      <c r="U9" t="s">
+        <v>777</v>
+      </c>
+      <c r="V9" t="s">
+        <v>699</v>
+      </c>
+      <c r="W9" t="s">
         <v>894</v>
       </c>
-      <c r="U9" t="s">
-        <v>778</v>
-      </c>
-      <c r="V9" t="s">
-        <v>700</v>
-      </c>
-      <c r="W9" t="s">
+      <c r="X9" t="s">
+        <v>386</v>
+      </c>
+      <c r="Z9" t="s">
         <v>895</v>
       </c>
-      <c r="X9" t="s">
-        <v>387</v>
-      </c>
-      <c r="Z9" t="s">
+      <c r="AA9" t="s">
+        <v>386</v>
+      </c>
+      <c r="AH9" t="s">
         <v>896</v>
       </c>
-      <c r="AA9" t="s">
-        <v>387</v>
-      </c>
-      <c r="AH9" t="s">
+      <c r="AJ9" t="s">
+        <v>693</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>321</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>386</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>386</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>386</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>719</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>303</v>
+      </c>
+      <c r="BE9" t="s">
         <v>897</v>
       </c>
-      <c r="AJ9" t="s">
-        <v>694</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>322</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>387</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>387</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>387</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>720</v>
-      </c>
-      <c r="BB9" t="s">
-        <v>304</v>
-      </c>
-      <c r="BE9" t="s">
+      <c r="BF9" t="s">
+        <v>386</v>
+      </c>
+      <c r="BG9" t="s">
         <v>898</v>
       </c>
-      <c r="BF9" t="s">
-        <v>387</v>
-      </c>
-      <c r="BG9" t="s">
+      <c r="BM9" t="s">
         <v>899</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J10" t="s">
         <v>147</v>
       </c>
       <c r="K10" t="s">
+        <v>901</v>
+      </c>
+      <c r="N10" t="s">
+        <v>386</v>
+      </c>
+      <c r="R10" t="s">
+        <v>386</v>
+      </c>
+      <c r="U10" t="s">
+        <v>832</v>
+      </c>
+      <c r="V10" t="s">
+        <v>386</v>
+      </c>
+      <c r="W10" t="s">
+        <v>386</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>775</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>386</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>615</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>386</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>386</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>763</v>
+      </c>
+      <c r="BE10" t="s">
         <v>902</v>
       </c>
-      <c r="N10" t="s">
-        <v>387</v>
-      </c>
-      <c r="R10" t="s">
-        <v>387</v>
-      </c>
-      <c r="U10" t="s">
-        <v>833</v>
-      </c>
-      <c r="V10" t="s">
-        <v>387</v>
-      </c>
-      <c r="W10" t="s">
-        <v>387</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>776</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>387</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>616</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>387</v>
-      </c>
-      <c r="BA10" t="s">
-        <v>387</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>764</v>
-      </c>
-      <c r="BE10" t="s">
-        <v>903</v>
-      </c>
       <c r="BG10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BM10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K11" t="s">
+        <v>903</v>
+      </c>
+      <c r="U11" t="s">
+        <v>780</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>386</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>386</v>
+      </c>
+      <c r="BB11" t="s">
         <v>904</v>
       </c>
-      <c r="U11" t="s">
-        <v>781</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>387</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>387</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>905</v>
-      </c>
       <c r="BE11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" spans="1:70" x14ac:dyDescent="0.25">
       <c r="K12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="U12" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="BB12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:70" x14ac:dyDescent="0.25">
       <c r="U13" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="BB13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" spans="1:70" x14ac:dyDescent="0.25">
       <c r="U14" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="BB14" t="s">
         <v>258</v>
@@ -15148,7 +15148,7 @@
     </row>
     <row r="15" spans="1:70" x14ac:dyDescent="0.25">
       <c r="BB15" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="1508" spans="60:60" x14ac:dyDescent="0.25">
@@ -15348,7 +15348,7 @@
     </row>
     <row r="1573" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
       <c r="BH1573" s="13" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="1574" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
@@ -16943,47 +16943,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>909</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>911</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>913</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>915</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>917</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>47</v>
@@ -16991,7 +16991,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>47</v>
@@ -16999,15 +16999,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>921</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>47</v>
@@ -17015,7 +17015,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>47</v>
@@ -17023,74 +17023,74 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>925</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>927</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>929</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>931</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>932</v>
+      </c>
+      <c r="B15" t="s">
         <v>933</v>
-      </c>
-      <c r="B15" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B16" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B17" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B18" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>937</v>
+      </c>
+      <c r="B19" t="s">
         <v>938</v>
-      </c>
-      <c r="B19" t="s">
-        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -17113,46 +17113,46 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>941</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -17465,7 +17465,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -17473,7 +17473,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -17481,7 +17481,7 @@
         <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -17489,7 +17489,7 @@
         <v>59</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -17497,7 +17497,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -17505,15 +17505,15 @@
         <v>68</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>951</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -17521,7 +17521,7 @@
         <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -17529,55 +17529,55 @@
         <v>74</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>956</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>960</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
   </sheetData>
@@ -17599,7 +17599,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>25</v>
@@ -17642,7 +17642,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -17650,7 +17650,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -17658,7 +17658,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -17666,7 +17666,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -17674,7 +17674,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>

--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\clipboard-test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Clipboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1B0E4B-F99F-4F43-9B1D-9AFCEAD74785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FC35D3-F64A-4EDA-B5F8-29AB06F9F3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="1395" windowWidth="27030" windowHeight="13620" activeTab="2" xr2:uid="{366A1260-1365-4B39-9968-5A4EAE027BF5}"/>
+    <workbookView xWindow="1665" yWindow="360" windowWidth="27030" windowHeight="13620" activeTab="1" xr2:uid="{366A1260-1365-4B39-9968-5A4EAE027BF5}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -920,6 +920,9 @@
     <t>Ceiling Height</t>
   </si>
   <si>
+    <t>ceiling_hight</t>
+  </si>
+  <si>
     <t>Interior Door Materials</t>
   </si>
   <si>
@@ -2955,9 +2958,6 @@
   </si>
   <si>
     <t>bathroom4_updated</t>
-  </si>
-  <si>
-    <t>ceiling_height</t>
   </si>
 </sst>
 </file>
@@ -3230,14 +3230,14 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4033,28 +4033,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -8206,7 +8206,7 @@
         <v>296</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>976</v>
+        <v>297</v>
       </c>
       <c r="F82" s="27" t="s">
         <v>46</v>
@@ -8251,16 +8251,16 @@
         <v>286</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>48</v>
@@ -8301,16 +8301,16 @@
         <v>286</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>48</v>
@@ -8348,13 +8348,13 @@
         <v>276</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>74</v>
@@ -8382,11 +8382,11 @@
       <c r="O85" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P85" s="28" t="s">
+      <c r="P85" s="31" t="s">
         <v>48</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>51</v>
@@ -8400,19 +8400,19 @@
         <v>276</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>48</v>
@@ -8450,13 +8450,13 @@
         <v>276</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>74</v>
@@ -8500,13 +8500,13 @@
         <v>276</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>74</v>
@@ -8550,13 +8550,13 @@
         <v>276</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>74</v>
@@ -8600,13 +8600,13 @@
         <v>276</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>74</v>
@@ -8650,13 +8650,13 @@
         <v>276</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>74</v>
@@ -8700,13 +8700,13 @@
         <v>276</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>74</v>
@@ -8750,13 +8750,13 @@
         <v>276</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>74</v>
@@ -8800,13 +8800,13 @@
         <v>276</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>46</v>
@@ -8816,7 +8816,7 @@
         <v>48</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>48</v>
@@ -8850,19 +8850,19 @@
         <v>276</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>48</v>
@@ -8900,19 +8900,19 @@
         <v>276</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>48</v>
@@ -8950,19 +8950,19 @@
         <v>276</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>48</v>
@@ -9000,13 +9000,13 @@
         <v>276</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>97</v>
@@ -9048,19 +9048,19 @@
         <v>276</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>48</v>
@@ -9086,7 +9086,7 @@
         <v>47</v>
       </c>
       <c r="Q99" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>51</v>
@@ -9100,19 +9100,19 @@
         <v>276</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>48</v>
@@ -9150,13 +9150,13 @@
         <v>276</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>97</v>
@@ -9198,19 +9198,19 @@
         <v>276</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>48</v>
@@ -9248,19 +9248,19 @@
         <v>276</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>48</v>
@@ -9298,19 +9298,19 @@
         <v>276</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>48</v>
@@ -9351,10 +9351,10 @@
         <v>276</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>97</v>
@@ -9413,22 +9413,22 @@
         <v>1400</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>48</v>
@@ -9454,7 +9454,7 @@
         <v>47</v>
       </c>
       <c r="Q107" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="R107" s="1" t="s">
         <v>51</v>
@@ -9465,16 +9465,16 @@
         <v>1410</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>74</v>
@@ -9515,22 +9515,22 @@
         <v>1420</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>48</v>
@@ -9556,7 +9556,7 @@
         <v>47</v>
       </c>
       <c r="Q109" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="R109" s="1" t="s">
         <v>51</v>
@@ -9567,16 +9567,16 @@
         <v>1430</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>74</v>
@@ -9617,22 +9617,22 @@
         <v>1440</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>48</v>
@@ -9658,7 +9658,7 @@
         <v>47</v>
       </c>
       <c r="Q111" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>51</v>
@@ -9669,22 +9669,22 @@
         <v>1450</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>48</v>
@@ -9710,7 +9710,7 @@
         <v>47</v>
       </c>
       <c r="Q112" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="R112" s="1" t="s">
         <v>51</v>
@@ -9721,16 +9721,16 @@
         <v>1460</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>131</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>91</v>
@@ -9771,16 +9771,16 @@
         <v>1470</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>131</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>91</v>
@@ -9821,16 +9821,16 @@
         <v>1480</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>131</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>91</v>
@@ -9871,16 +9871,16 @@
         <v>1490</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>91</v>
@@ -9921,16 +9921,16 @@
         <v>1500</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>97</v>
@@ -9989,19 +9989,19 @@
         <v>1600</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
@@ -10021,7 +10021,7 @@
         <v>49</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O119" s="1" t="s">
         <v>47</v>
@@ -10039,19 +10039,19 @@
         <v>1610</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C120" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
@@ -10087,19 +10087,19 @@
         <v>1620</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C121" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1" t="s">
@@ -10119,7 +10119,7 @@
         <v>49</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O121" s="1" t="s">
         <v>47</v>
@@ -10157,19 +10157,19 @@
         <v>1700</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="1" t="s">
@@ -10189,7 +10189,7 @@
         <v>49</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O123" s="1" t="s">
         <v>47</v>
@@ -10207,22 +10207,22 @@
         <v>1710</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>48</v>
@@ -10257,16 +10257,16 @@
         <v>1800</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>97</v>
@@ -10372,7 +10372,7 @@
         <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>28</v>
@@ -10401,22 +10401,22 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B2" s="1">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>48</v>
@@ -10432,16 +10432,16 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B3" s="1">
         <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>97</v>
@@ -10461,16 +10461,16 @@
     </row>
     <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B4" s="1">
         <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>97</v>
@@ -10490,16 +10490,16 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B5" s="1">
         <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>46</v>
@@ -10519,16 +10519,16 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B6" s="1">
         <v>50</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>46</v>
@@ -10548,16 +10548,16 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B7" s="1">
         <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>46</v>
@@ -10577,16 +10577,16 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B8" s="1">
         <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>46</v>
@@ -10606,16 +10606,16 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B9" s="1">
         <v>80</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>46</v>
@@ -10635,16 +10635,16 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B10" s="1">
         <v>90</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>91</v>
@@ -10664,16 +10664,16 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B11" s="1">
         <v>100</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>97</v>
@@ -10712,13 +10712,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
@@ -10741,16 +10741,16 @@
         <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>48</v>
@@ -10772,16 +10772,16 @@
         <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>48</v>
@@ -10803,16 +10803,16 @@
         <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>48</v>
@@ -10834,10 +10834,10 @@
         <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>91</v>
@@ -10863,13 +10863,13 @@
         <v>60</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -10892,13 +10892,13 @@
         <v>70</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -10921,10 +10921,10 @@
         <v>80</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>97</v>
@@ -10963,13 +10963,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
@@ -10992,16 +10992,16 @@
         <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>48</v>
@@ -11023,16 +11023,16 @@
         <v>30</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>48</v>
@@ -11054,10 +11054,10 @@
         <v>40</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>91</v>
@@ -11083,13 +11083,13 @@
         <v>50</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1" t="s">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -11112,13 +11112,13 @@
         <v>60</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -11141,10 +11141,10 @@
         <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>97</v>
@@ -11183,10 +11183,10 @@
         <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>91</v>
@@ -11212,10 +11212,10 @@
         <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>46</v>
@@ -11241,10 +11241,10 @@
         <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>91</v>
@@ -11270,16 +11270,16 @@
         <v>40</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>48</v>
@@ -11301,10 +11301,10 @@
         <v>50</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>97</v>
@@ -11343,16 +11343,16 @@
         <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>48</v>
@@ -11374,10 +11374,10 @@
         <v>20</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>46</v>
@@ -11403,13 +11403,13 @@
         <v>30</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -11432,10 +11432,10 @@
         <v>40</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>46</v>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -11461,10 +11461,10 @@
         <v>50</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>91</v>
@@ -11490,10 +11490,10 @@
         <v>60</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>91</v>
@@ -11519,10 +11519,10 @@
         <v>70</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>97</v>
@@ -11561,10 +11561,10 @@
         <v>10</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>91</v>
@@ -11590,10 +11590,10 @@
         <v>20</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>46</v>
@@ -11619,10 +11619,10 @@
         <v>30</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>91</v>
@@ -11648,10 +11648,10 @@
         <v>40</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>97</v>
@@ -11684,16 +11684,16 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B49" s="1">
         <v>10</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>91</v>
@@ -11713,16 +11713,16 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B50" s="1">
         <v>20</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>46</v>
@@ -11742,22 +11742,22 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B51" s="1">
         <v>30</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>48</v>
@@ -11773,16 +11773,16 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B52" s="1">
         <v>40</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>91</v>
@@ -11802,16 +11802,16 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B53" s="1">
         <v>50</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>97</v>
@@ -11844,16 +11844,16 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B55" s="1">
         <v>10</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>91</v>
@@ -11873,22 +11873,22 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B56" s="1">
         <v>20</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>48</v>
@@ -11904,16 +11904,16 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B57" s="1">
         <v>30</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>46</v>
@@ -11933,16 +11933,16 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B58" s="1">
         <v>40</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>91</v>
@@ -11962,16 +11962,16 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B59" s="1">
         <v>50</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>97</v>
@@ -12004,16 +12004,16 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B61" s="1">
         <v>10</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>91</v>
@@ -12033,16 +12033,16 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B62" s="1">
         <v>20</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>46</v>
@@ -12062,16 +12062,16 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B63" s="1">
         <v>30</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>91</v>
@@ -12091,16 +12091,16 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B64" s="1">
         <v>40</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>97</v>
@@ -12133,16 +12133,16 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B66" s="1">
         <v>10</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>91</v>
@@ -12162,16 +12162,16 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B67" s="1">
         <v>20</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>46</v>
@@ -12191,16 +12191,16 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B68" s="1">
         <v>30</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>97</v>
@@ -12239,10 +12239,10 @@
         <v>10</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>46</v>
@@ -12268,10 +12268,10 @@
         <v>20</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>91</v>
@@ -12297,10 +12297,10 @@
         <v>30</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>91</v>
@@ -12326,10 +12326,10 @@
         <v>40</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>97</v>
@@ -12368,10 +12368,10 @@
         <v>10</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>46</v>
@@ -12397,16 +12397,16 @@
         <v>20</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>48</v>
@@ -12428,10 +12428,10 @@
         <v>30</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>91</v>
@@ -12457,10 +12457,10 @@
         <v>40</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>91</v>
@@ -12486,10 +12486,10 @@
         <v>50</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>97</v>
@@ -12528,10 +12528,10 @@
         <v>10</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>46</v>
@@ -12557,16 +12557,16 @@
         <v>20</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>48</v>
@@ -12588,10 +12588,10 @@
         <v>30</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>91</v>
@@ -12617,10 +12617,10 @@
         <v>40</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>97</v>
@@ -12659,16 +12659,16 @@
         <v>10</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>48</v>
@@ -12690,10 +12690,10 @@
         <v>20</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>46</v>
@@ -12719,10 +12719,10 @@
         <v>30</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>91</v>
@@ -12748,16 +12748,16 @@
         <v>40</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>48</v>
@@ -12779,10 +12779,10 @@
         <v>50</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>97</v>
@@ -12821,10 +12821,10 @@
         <v>10</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>91</v>
@@ -12850,16 +12850,16 @@
         <v>20</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>48</v>
@@ -12881,10 +12881,10 @@
         <v>30</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>97</v>
@@ -12923,10 +12923,10 @@
         <v>10</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>91</v>
@@ -12952,10 +12952,10 @@
         <v>20</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>46</v>
@@ -12981,10 +12981,10 @@
         <v>30</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>97</v>
@@ -13023,10 +13023,10 @@
         <v>10</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>46</v>
@@ -13052,10 +13052,10 @@
         <v>20</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>91</v>
@@ -13081,10 +13081,10 @@
         <v>30</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>97</v>
@@ -13110,10 +13110,10 @@
         <v>40</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>97</v>
@@ -13152,10 +13152,10 @@
         <v>10</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>91</v>
@@ -13181,16 +13181,16 @@
         <v>20</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>48</v>
@@ -13212,10 +13212,10 @@
         <v>30</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>97</v>
@@ -13248,16 +13248,16 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B109" s="1">
         <v>10</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>91</v>
@@ -13277,16 +13277,16 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B110" s="1">
         <v>20</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>46</v>
@@ -13306,16 +13306,16 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B111" s="1">
         <v>30</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>91</v>
@@ -13335,16 +13335,16 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B112" s="1">
         <v>40</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>97</v>
@@ -13364,16 +13364,16 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B113" s="1">
         <v>10</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>91</v>
@@ -13393,16 +13393,16 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B114" s="1">
         <v>20</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>46</v>
@@ -13422,16 +13422,16 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B115" s="1">
         <v>30</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>91</v>
@@ -13451,16 +13451,16 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B116" s="1">
         <v>40</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>97</v>
@@ -13626,70 +13626,70 @@
         <v>295</v>
       </c>
       <c r="AM1" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN1" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO1" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AP1" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AQ1" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AR1" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AS1" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AT1" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AU1" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AV1" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AW1" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AX1" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AY1" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AZ1" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="BA1" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="BB1" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="BC1" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="BD1" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="BE1" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="BF1" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="BG1" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="BH1" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="BI1" s="5" t="s">
         <v>213</v>
@@ -13698,33 +13698,33 @@
         <v>217</v>
       </c>
       <c r="BK1" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="BL1" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="BM1" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="BN1" s="5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="BO1" s="5" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="BP1" s="5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="BQ1" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="BR1" s="5" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -13736,7 +13736,7 @@
         <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F2" t="s">
         <v>84</v>
@@ -13745,25 +13745,25 @@
         <v>88</v>
       </c>
       <c r="H2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O2" t="s">
         <v>151</v>
@@ -13772,425 +13772,425 @@
         <v>138</v>
       </c>
       <c r="Q2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="R2" t="s">
         <v>151</v>
       </c>
       <c r="S2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="T2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="U2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="V2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="W2" t="s">
+        <v>621</v>
+      </c>
+      <c r="X2" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y2" t="s">
         <v>620</v>
       </c>
-      <c r="X2" t="s">
-        <v>621</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>619</v>
-      </c>
       <c r="Z2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AA2" t="s">
         <v>151</v>
       </c>
       <c r="AB2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AC2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AD2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AE2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AF2" t="s">
+        <v>628</v>
+      </c>
+      <c r="AG2" t="s">
         <v>627</v>
       </c>
-      <c r="AG2" t="s">
-        <v>626</v>
-      </c>
       <c r="AH2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AI2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AJ2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AK2" t="s">
+        <v>632</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>632</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>633</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>634</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>310</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>635</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>627</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>636</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>637</v>
+      </c>
+      <c r="AT2" t="s">
         <v>631</v>
       </c>
-      <c r="AL2" t="s">
-        <v>631</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>632</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>633</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>309</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>634</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>626</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>635</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>636</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>630</v>
-      </c>
       <c r="AU2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AV2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AW2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AX2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AY2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AZ2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="BA2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="BB2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="BC2" t="s">
         <v>70</v>
       </c>
       <c r="BD2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="BE2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="BF2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="BG2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="BH2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="BI2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="BJ2" t="s">
         <v>47</v>
       </c>
       <c r="BK2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="BL2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="BM2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="BN2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="BO2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="BP2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="BQ2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="BR2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C3" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J3" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K3" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="P3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="Q3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="R3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="S3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="T3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="U3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="V3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="W3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="X3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="Y3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="Z3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AA3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AB3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AC3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AD3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AE3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AF3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AH3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AI3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AJ3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AK3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AL3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AM3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AN3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AO3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AP3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AQ3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AR3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AS3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AT3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AU3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AV3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AW3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AX3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AY3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AZ3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="BA3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="BB3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="BC3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="BD3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="BE3" t="s">
         <v>258</v>
       </c>
       <c r="BF3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="BG3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="BH3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="BI3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="BJ3" t="s">
         <v>48</v>
       </c>
       <c r="BK3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="BL3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="BM3" t="s">
+        <v>654</v>
+      </c>
+      <c r="BN3" t="s">
         <v>653</v>
       </c>
-      <c r="BN3" t="s">
-        <v>652</v>
-      </c>
       <c r="BO3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="BP3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="BQ3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="BR3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="G4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="I4" t="s">
+        <v>720</v>
+      </c>
+      <c r="J4" t="s">
+        <v>721</v>
+      </c>
+      <c r="K4" t="s">
+        <v>722</v>
+      </c>
+      <c r="L4" t="s">
+        <v>723</v>
+      </c>
+      <c r="M4" t="s">
+        <v>724</v>
+      </c>
+      <c r="N4" t="s">
         <v>719</v>
       </c>
-      <c r="J4" t="s">
-        <v>720</v>
-      </c>
-      <c r="K4" t="s">
-        <v>721</v>
-      </c>
-      <c r="L4" t="s">
-        <v>722</v>
-      </c>
-      <c r="M4" t="s">
-        <v>723</v>
-      </c>
-      <c r="N4" t="s">
-        <v>718</v>
-      </c>
       <c r="O4" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="P4" t="s">
         <v>140</v>
@@ -14199,756 +14199,756 @@
         <v>144</v>
       </c>
       <c r="R4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="S4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="T4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="U4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="V4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="W4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="X4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="Y4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="Z4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AA4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AB4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AC4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AD4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AE4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AF4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AH4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AI4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AJ4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AK4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AL4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AM4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AN4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AO4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AP4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AQ4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AR4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AS4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AT4" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AU4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AV4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AW4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AX4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AY4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AZ4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="BA4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="BB4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="BC4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="BD4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="BE4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="BF4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="BG4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="BH4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="BJ4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="BK4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="BL4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="BM4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="BN4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="BO4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="BP4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="BQ4" t="s">
         <v>258</v>
       </c>
       <c r="BR4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D5" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E5" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F5" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H5" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="J5" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="K5" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L5" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="M5" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N5" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P5" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="Q5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="R5" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="S5" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="T5" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="U5" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="V5" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="W5" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="X5" t="s">
+        <v>782</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>783</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>784</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>786</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>788</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>789</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>790</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>631</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>791</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>792</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>793</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>794</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>795</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>796</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>797</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>798</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>799</v>
+      </c>
+      <c r="AQ5" t="s">
         <v>781</v>
       </c>
-      <c r="Y5" t="s">
-        <v>782</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>783</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>784</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>785</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>786</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>787</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>788</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>789</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>630</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>790</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>791</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>792</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>793</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>794</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>795</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>796</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>797</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>798</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>780</v>
-      </c>
       <c r="AR5" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AS5" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AT5" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AU5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AV5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AW5" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AX5" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AY5" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AZ5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="BA5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="BB5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="BC5" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="BD5" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="BE5" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="BF5" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="BG5" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="BL5" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="BM5" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="BN5" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="BO5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BP5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BQ5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E6" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F6" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H6" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="J6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="K6" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="L6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M6" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N6" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="P6" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="R6" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="S6" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="T6" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="U6" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="V6" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="W6" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="X6" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="Y6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="Z6" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AA6" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AB6" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AC6" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AD6" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AE6" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AF6" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AG6" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AH6" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AI6" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AJ6" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AK6" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AL6" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AM6" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AN6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AP6" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AQ6" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AR6" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AS6" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AT6" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AU6" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AW6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AX6" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AY6" t="s">
         <v>197</v>
       </c>
       <c r="AZ6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BA6" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="BB6" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="BC6" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="BD6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BE6" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="BF6" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="BG6" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="BL6" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="BM6" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="BN6" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="BO6" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="BQ6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E7" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H7" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="J7" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="K7" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N7" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="R7" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="S7" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="T7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="V7" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="W7" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="X7" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="Y7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Z7" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AA7" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AB7" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AC7" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AD7" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AE7" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AF7" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AG7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AH7" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AI7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ7" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AK7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AL7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO7" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AP7" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AQ7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AR7" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AS7" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AT7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AU7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AX7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AY7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BA7" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="BB7" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="BC7" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="BE7" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="BF7" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="BG7" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="BL7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BM7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="BN7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="BO7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E8" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J8" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="K8" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N8" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="R8" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="S8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U8" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="V8" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="W8" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="X8" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="Z8" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="AA8" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AB8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AC8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AD8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AE8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AF8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AH8" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AJ8" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="AK8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO8" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AP8" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AR8" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AS8" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="BA8" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="BB8" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="BC8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BE8" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="BF8" t="s">
         <v>177</v>
@@ -14957,190 +14957,190 @@
         <v>177</v>
       </c>
       <c r="BM8" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="BN8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BO8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E9" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="J9" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="K9" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="N9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="R9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="U9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="V9" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="W9" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="X9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Z9" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AA9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AH9" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="AJ9" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AR9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AS9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BA9" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="BB9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="BE9" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="BF9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BG9" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="BM9" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="J10" t="s">
         <v>147</v>
       </c>
       <c r="K10" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="N10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="R10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U10" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="V10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="W10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Z10" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AH10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AO10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BA10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BB10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="BE10" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="BG10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BM10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K11" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="U11" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="Z11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BB11" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="BE11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" spans="1:70" x14ac:dyDescent="0.25">
       <c r="K12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U12" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="BB12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" spans="1:70" x14ac:dyDescent="0.25">
       <c r="U13" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="BB13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" spans="1:70" x14ac:dyDescent="0.25">
       <c r="U14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="BB14" t="s">
         <v>258</v>
@@ -15148,7 +15148,7 @@
     </row>
     <row r="15" spans="1:70" x14ac:dyDescent="0.25">
       <c r="BB15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="1508" spans="60:60" x14ac:dyDescent="0.25">
@@ -15348,7 +15348,7 @@
     </row>
     <row r="1573" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
       <c r="BH1573" s="13" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="1574" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
@@ -16943,47 +16943,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>47</v>
@@ -16991,7 +16991,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>47</v>
@@ -16999,15 +16999,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>47</v>
@@ -17015,7 +17015,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>47</v>
@@ -17023,74 +17023,74 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B15" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>935</v>
+      </c>
+      <c r="B16" t="s">
         <v>934</v>
-      </c>
-      <c r="B16" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B17" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B18" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B19" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -17113,46 +17113,46 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -17465,7 +17465,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -17473,7 +17473,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -17481,7 +17481,7 @@
         <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -17489,7 +17489,7 @@
         <v>59</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -17497,7 +17497,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -17505,15 +17505,15 @@
         <v>68</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -17521,7 +17521,7 @@
         <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -17529,55 +17529,55 @@
         <v>74</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
   </sheetData>
@@ -17599,7 +17599,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>25</v>
@@ -17642,7 +17642,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -17650,7 +17650,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -17658,7 +17658,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -17666,7 +17666,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -17674,7 +17674,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>

--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Clipboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\clipboard-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FC35D3-F64A-4EDA-B5F8-29AB06F9F3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E81E72-F931-409E-8E2F-890984BA743C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1665" yWindow="360" windowWidth="27030" windowHeight="13620" activeTab="1" xr2:uid="{366A1260-1365-4B39-9968-5A4EAE027BF5}"/>
+    <workbookView xWindow="285" yWindow="420" windowWidth="14715" windowHeight="13920" activeTab="1" xr2:uid="{B5A7B246-83E3-4800-9863-625CA16CE35B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3031" uniqueCount="977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3044" uniqueCount="979">
   <si>
     <t>Clipboard v3.0 Master Workbook — Base Configuration</t>
   </si>
@@ -2288,9 +2288,6 @@
     <t>Pull-Down Stair</t>
   </si>
   <si>
-    <t>Mini-Split</t>
-  </si>
-  <si>
     <t>Tankless Electric</t>
   </si>
   <si>
@@ -2958,6 +2955,15 @@
   </si>
   <si>
     <t>bathroom4_updated</t>
+  </si>
+  <si>
+    <t>Vacation Rental</t>
+  </si>
+  <si>
+    <t>Inside Main Living Area</t>
+  </si>
+  <si>
+    <t>Mini-Split / Ductls</t>
   </si>
 </sst>
 </file>
@@ -3230,14 +3236,14 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4033,28 +4039,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -4162,22 +4168,23 @@
   <dimension ref="A1:R125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="38" customWidth="1"/>
-    <col min="15" max="15" width="9" customWidth="1"/>
-    <col min="16" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="22" customWidth="1"/>
-    <col min="18" max="18" width="26" customWidth="1"/>
+    <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="38.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" x14ac:dyDescent="0.25">
@@ -4953,7 +4960,9 @@
       <c r="H16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1" t="s">
+        <v>611</v>
+      </c>
       <c r="J16" s="1" t="s">
         <v>47</v>
       </c>
@@ -5003,7 +5012,9 @@
       <c r="H17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I17" s="1"/>
+      <c r="I17" s="1" t="s">
+        <v>612</v>
+      </c>
       <c r="J17" s="1" t="s">
         <v>47</v>
       </c>
@@ -5203,7 +5214,9 @@
       <c r="H21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I21" s="1"/>
+      <c r="I21" s="1" t="s">
+        <v>613</v>
+      </c>
       <c r="J21" s="1" t="s">
         <v>47</v>
       </c>
@@ -5253,7 +5266,9 @@
       <c r="H22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I22" s="1"/>
+      <c r="I22" t="s">
+        <v>613</v>
+      </c>
       <c r="J22" s="1" t="s">
         <v>47</v>
       </c>
@@ -5303,7 +5318,9 @@
       <c r="H23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I23" s="1"/>
+      <c r="I23" t="s">
+        <v>614</v>
+      </c>
       <c r="J23" s="1" t="s">
         <v>48</v>
       </c>
@@ -5353,7 +5370,9 @@
       <c r="H24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I24" s="1"/>
+      <c r="I24" t="s">
+        <v>615</v>
+      </c>
       <c r="J24" s="1" t="s">
         <v>48</v>
       </c>
@@ -5503,7 +5522,9 @@
       <c r="H27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I27" s="1"/>
+      <c r="I27" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="J27" s="1" t="s">
         <v>48</v>
       </c>
@@ -5609,7 +5630,9 @@
       <c r="H29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I29" s="1"/>
+      <c r="I29" t="s">
+        <v>617</v>
+      </c>
       <c r="J29" s="1" t="s">
         <v>47</v>
       </c>
@@ -5937,7 +5960,9 @@
       <c r="H36" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I36" s="1"/>
+      <c r="I36" t="s">
+        <v>618</v>
+      </c>
       <c r="J36" s="1" t="s">
         <v>47</v>
       </c>
@@ -5987,7 +6012,9 @@
       <c r="H37" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I37" s="1"/>
+      <c r="I37" t="s">
+        <v>619</v>
+      </c>
       <c r="J37" s="1" t="s">
         <v>48</v>
       </c>
@@ -6037,7 +6064,9 @@
       <c r="H38" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I38" s="1"/>
+      <c r="I38" t="s">
+        <v>619</v>
+      </c>
       <c r="J38" s="1" t="s">
         <v>47</v>
       </c>
@@ -6089,7 +6118,9 @@
       <c r="H39" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I39" s="1"/>
+      <c r="I39" t="s">
+        <v>620</v>
+      </c>
       <c r="J39" s="1" t="s">
         <v>48</v>
       </c>
@@ -8382,7 +8413,7 @@
       <c r="O85" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P85" s="31" t="s">
+      <c r="P85" s="28" t="s">
         <v>48</v>
       </c>
       <c r="Q85" s="1" t="s">
@@ -9839,9 +9870,7 @@
       <c r="H115" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I115" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="I115" s="1"/>
       <c r="J115" s="1" t="s">
         <v>48</v>
       </c>
@@ -9889,9 +9918,7 @@
       <c r="H116" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I116" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="I116" s="1"/>
       <c r="J116" s="1" t="s">
         <v>48</v>
       </c>
@@ -10496,10 +10523,10 @@
         <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>967</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>968</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>46</v>
@@ -10525,10 +10552,10 @@
         <v>50</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>969</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>970</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>46</v>
@@ -10554,10 +10581,10 @@
         <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>971</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>972</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>46</v>
@@ -10583,10 +10610,10 @@
         <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>973</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>974</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>46</v>
@@ -10612,10 +10639,10 @@
         <v>80</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>976</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>46</v>
@@ -13862,7 +13889,7 @@
         <v>631</v>
       </c>
       <c r="AU2" t="s">
-        <v>638</v>
+        <v>977</v>
       </c>
       <c r="AV2" t="s">
         <v>639</v>
@@ -14074,7 +14101,7 @@
         <v>694</v>
       </c>
       <c r="AU3" t="s">
-        <v>304</v>
+        <v>638</v>
       </c>
       <c r="AV3" t="s">
         <v>695</v>
@@ -14148,7 +14175,7 @@
     </row>
     <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>387</v>
+        <v>665</v>
       </c>
       <c r="B4" t="s">
         <v>713</v>
@@ -14286,7 +14313,7 @@
         <v>749</v>
       </c>
       <c r="AU4" t="s">
-        <v>750</v>
+        <v>304</v>
       </c>
       <c r="AV4" t="s">
         <v>751</v>
@@ -14295,28 +14322,28 @@
         <v>752</v>
       </c>
       <c r="AX4" t="s">
+        <v>978</v>
+      </c>
+      <c r="AY4" t="s">
         <v>753</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>754</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
         <v>755</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BB4" t="s">
         <v>756</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>757</v>
       </c>
       <c r="BC4" t="s">
         <v>715</v>
       </c>
       <c r="BD4" t="s">
+        <v>757</v>
+      </c>
+      <c r="BE4" t="s">
         <v>758</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>759</v>
       </c>
       <c r="BF4" t="s">
         <v>710</v>
@@ -14325,28 +14352,28 @@
         <v>710</v>
       </c>
       <c r="BH4" t="s">
+        <v>759</v>
+      </c>
+      <c r="BJ4" t="s">
         <v>760</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BK4" t="s">
         <v>761</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BL4" t="s">
         <v>762</v>
       </c>
-      <c r="BL4" t="s">
+      <c r="BM4" t="s">
         <v>763</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BN4" t="s">
         <v>764</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BO4" t="s">
+        <v>764</v>
+      </c>
+      <c r="BP4" t="s">
         <v>765</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>765</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>766</v>
       </c>
       <c r="BQ4" t="s">
         <v>258</v>
@@ -14356,35 +14383,38 @@
       </c>
     </row>
     <row r="5" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>387</v>
+      </c>
       <c r="B5" t="s">
+        <v>766</v>
+      </c>
+      <c r="C5" t="s">
+        <v>976</v>
+      </c>
+      <c r="D5" t="s">
         <v>767</v>
       </c>
-      <c r="C5" t="s">
-        <v>720</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>768</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>769</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>770</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>771</v>
-      </c>
-      <c r="J5" t="s">
-        <v>772</v>
       </c>
       <c r="K5" t="s">
         <v>672</v>
       </c>
       <c r="L5" t="s">
+        <v>772</v>
+      </c>
+      <c r="M5" t="s">
         <v>773</v>
-      </c>
-      <c r="M5" t="s">
-        <v>774</v>
       </c>
       <c r="N5" t="s">
         <v>631</v>
@@ -14393,145 +14423,145 @@
         <v>720</v>
       </c>
       <c r="P5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="Q5" t="s">
         <v>720</v>
       </c>
       <c r="R5" t="s">
+        <v>775</v>
+      </c>
+      <c r="S5" t="s">
         <v>776</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>777</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>778</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>779</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>780</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>781</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>782</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>783</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
         <v>784</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>785</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>786</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>787</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>788</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
         <v>789</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>790</v>
       </c>
       <c r="AG5" t="s">
         <v>631</v>
       </c>
       <c r="AH5" t="s">
+        <v>790</v>
+      </c>
+      <c r="AI5" t="s">
         <v>791</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AJ5" t="s">
         <v>792</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AK5" t="s">
         <v>793</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AL5" t="s">
         <v>794</v>
       </c>
-      <c r="AL5" t="s">
+      <c r="AM5" t="s">
         <v>795</v>
       </c>
-      <c r="AM5" t="s">
+      <c r="AN5" t="s">
         <v>796</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AO5" t="s">
         <v>797</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="AP5" t="s">
         <v>798</v>
       </c>
-      <c r="AP5" t="s">
+      <c r="AQ5" t="s">
+        <v>780</v>
+      </c>
+      <c r="AR5" t="s">
         <v>799</v>
       </c>
-      <c r="AQ5" t="s">
-        <v>781</v>
-      </c>
-      <c r="AR5" t="s">
+      <c r="AS5" t="s">
         <v>800</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AT5" t="s">
         <v>801</v>
       </c>
-      <c r="AT5" t="s">
-        <v>802</v>
-      </c>
       <c r="AU5" t="s">
-        <v>626</v>
+        <v>750</v>
       </c>
       <c r="AV5" t="s">
         <v>387</v>
       </c>
       <c r="AW5" t="s">
+        <v>802</v>
+      </c>
+      <c r="AX5" t="s">
         <v>803</v>
       </c>
-      <c r="AX5" t="s">
+      <c r="AY5" t="s">
         <v>804</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>805</v>
       </c>
       <c r="AZ5" t="s">
         <v>720</v>
       </c>
       <c r="BA5" t="s">
+        <v>805</v>
+      </c>
+      <c r="BB5" t="s">
         <v>806</v>
       </c>
-      <c r="BB5" t="s">
+      <c r="BC5" t="s">
         <v>807</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BD5" t="s">
         <v>808</v>
       </c>
-      <c r="BD5" t="s">
+      <c r="BE5" t="s">
         <v>809</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BF5" t="s">
         <v>810</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BG5" t="s">
+        <v>810</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>964</v>
+      </c>
+      <c r="BM5" t="s">
         <v>811</v>
       </c>
-      <c r="BG5" t="s">
-        <v>811</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>965</v>
-      </c>
-      <c r="BM5" t="s">
+      <c r="BN5" t="s">
         <v>812</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>813</v>
       </c>
       <c r="BO5" t="s">
         <v>304</v>
@@ -14545,7 +14575,10 @@
     </row>
     <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>814</v>
+        <v>813</v>
+      </c>
+      <c r="C6" t="s">
+        <v>720</v>
       </c>
       <c r="D6" t="s">
         <v>387</v>
@@ -14554,13 +14587,13 @@
         <v>713</v>
       </c>
       <c r="F6" t="s">
+        <v>814</v>
+      </c>
+      <c r="H6" t="s">
         <v>815</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>816</v>
-      </c>
-      <c r="J6" t="s">
-        <v>817</v>
       </c>
       <c r="K6" t="s">
         <v>726</v>
@@ -14572,76 +14605,76 @@
         <v>720</v>
       </c>
       <c r="N6" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="P6" t="s">
         <v>720</v>
       </c>
       <c r="R6" t="s">
+        <v>818</v>
+      </c>
+      <c r="S6" t="s">
         <v>819</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>820</v>
-      </c>
-      <c r="T6" t="s">
-        <v>821</v>
       </c>
       <c r="U6" t="s">
         <v>683</v>
       </c>
       <c r="V6" t="s">
+        <v>821</v>
+      </c>
+      <c r="W6" t="s">
         <v>822</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>823</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>824</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Z6" t="s">
         <v>825</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AA6" t="s">
         <v>826</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
         <v>827</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AC6" t="s">
         <v>828</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AD6" t="s">
         <v>829</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>830</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AF6" t="s">
         <v>831</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AG6" t="s">
         <v>832</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AH6" t="s">
         <v>833</v>
       </c>
-      <c r="AH6" t="s">
-        <v>834</v>
-      </c>
       <c r="AI6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="AJ6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AK6" t="s">
         <v>631</v>
       </c>
       <c r="AL6" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="AM6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AN6" t="s">
         <v>387</v>
@@ -14650,28 +14683,28 @@
         <v>318</v>
       </c>
       <c r="AP6" t="s">
+        <v>835</v>
+      </c>
+      <c r="AQ6" t="s">
         <v>836</v>
       </c>
-      <c r="AQ6" t="s">
+      <c r="AR6" t="s">
         <v>837</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AS6" t="s">
         <v>838</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>839</v>
       </c>
       <c r="AT6" t="s">
         <v>635</v>
       </c>
       <c r="AU6" t="s">
-        <v>840</v>
+        <v>626</v>
       </c>
       <c r="AW6" t="s">
         <v>387</v>
       </c>
       <c r="AX6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AY6" t="s">
         <v>197</v>
@@ -14680,37 +14713,37 @@
         <v>387</v>
       </c>
       <c r="BA6" t="s">
+        <v>841</v>
+      </c>
+      <c r="BB6" t="s">
         <v>842</v>
       </c>
-      <c r="BB6" t="s">
+      <c r="BC6" t="s">
         <v>843</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>844</v>
       </c>
       <c r="BD6" t="s">
         <v>387</v>
       </c>
       <c r="BE6" t="s">
+        <v>844</v>
+      </c>
+      <c r="BF6" t="s">
         <v>845</v>
       </c>
-      <c r="BF6" t="s">
-        <v>846</v>
-      </c>
       <c r="BG6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="BL6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="BM6" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="BN6" t="s">
         <v>626</v>
       </c>
       <c r="BO6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="BQ6" t="s">
         <v>387</v>
@@ -14718,28 +14751,28 @@
     </row>
     <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>846</v>
+      </c>
+      <c r="E7" t="s">
         <v>847</v>
       </c>
-      <c r="E7" t="s">
+      <c r="H7" t="s">
+        <v>817</v>
+      </c>
+      <c r="J7" t="s">
         <v>848</v>
       </c>
-      <c r="H7" t="s">
-        <v>818</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
+        <v>775</v>
+      </c>
+      <c r="N7" t="s">
+        <v>770</v>
+      </c>
+      <c r="R7" t="s">
         <v>849</v>
       </c>
-      <c r="K7" t="s">
-        <v>776</v>
-      </c>
-      <c r="N7" t="s">
-        <v>771</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>850</v>
-      </c>
-      <c r="S7" t="s">
-        <v>851</v>
       </c>
       <c r="T7" t="s">
         <v>387</v>
@@ -14748,49 +14781,49 @@
         <v>627</v>
       </c>
       <c r="V7" t="s">
+        <v>851</v>
+      </c>
+      <c r="W7" t="s">
         <v>852</v>
       </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
         <v>853</v>
-      </c>
-      <c r="X7" t="s">
-        <v>854</v>
       </c>
       <c r="Y7" t="s">
         <v>387</v>
       </c>
       <c r="Z7" t="s">
+        <v>854</v>
+      </c>
+      <c r="AA7" t="s">
         <v>855</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>856</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AC7" t="s">
         <v>857</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AD7" t="s">
         <v>858</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>859</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>860</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>861</v>
       </c>
       <c r="AG7" t="s">
         <v>387</v>
       </c>
       <c r="AH7" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AI7" t="s">
         <v>387</v>
       </c>
       <c r="AJ7" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AK7" t="s">
         <v>627</v>
@@ -14802,25 +14835,25 @@
         <v>387</v>
       </c>
       <c r="AO7" t="s">
+        <v>863</v>
+      </c>
+      <c r="AP7" t="s">
         <v>864</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>865</v>
       </c>
       <c r="AQ7" t="s">
         <v>387</v>
       </c>
       <c r="AR7" t="s">
+        <v>865</v>
+      </c>
+      <c r="AS7" t="s">
         <v>866</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>867</v>
       </c>
       <c r="AT7" t="s">
         <v>387</v>
       </c>
       <c r="AU7" t="s">
-        <v>387</v>
+        <v>839</v>
       </c>
       <c r="AX7" t="s">
         <v>387</v>
@@ -14829,22 +14862,22 @@
         <v>387</v>
       </c>
       <c r="BA7" t="s">
+        <v>867</v>
+      </c>
+      <c r="BB7" t="s">
         <v>868</v>
       </c>
-      <c r="BB7" t="s">
+      <c r="BC7" t="s">
         <v>869</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BE7" t="s">
         <v>870</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BF7" t="s">
         <v>871</v>
       </c>
-      <c r="BF7" t="s">
-        <v>872</v>
-      </c>
       <c r="BG7" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="BL7" t="s">
         <v>387</v>
@@ -14853,7 +14886,7 @@
         <v>347</v>
       </c>
       <c r="BN7" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="BO7" t="s">
         <v>361</v>
@@ -14861,46 +14894,46 @@
     </row>
     <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>873</v>
+      </c>
+      <c r="E8" t="s">
         <v>874</v>
-      </c>
-      <c r="E8" t="s">
-        <v>875</v>
       </c>
       <c r="H8" t="s">
         <v>387</v>
       </c>
       <c r="J8" t="s">
+        <v>875</v>
+      </c>
+      <c r="K8" t="s">
+        <v>818</v>
+      </c>
+      <c r="N8" t="s">
         <v>876</v>
       </c>
-      <c r="K8" t="s">
-        <v>819</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="R8" t="s">
         <v>877</v>
-      </c>
-      <c r="R8" t="s">
-        <v>878</v>
       </c>
       <c r="S8" t="s">
         <v>387</v>
       </c>
       <c r="U8" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="V8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="W8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="X8" t="s">
         <v>722</v>
       </c>
       <c r="Z8" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AA8" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AB8" t="s">
         <v>387</v>
@@ -14921,34 +14954,37 @@
         <v>749</v>
       </c>
       <c r="AJ8" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="AK8" t="s">
         <v>387</v>
       </c>
       <c r="AO8" t="s">
+        <v>881</v>
+      </c>
+      <c r="AP8" t="s">
         <v>882</v>
       </c>
-      <c r="AP8" t="s">
+      <c r="AR8" t="s">
         <v>883</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AS8" t="s">
         <v>884</v>
       </c>
-      <c r="AS8" t="s">
+      <c r="AU8" t="s">
+        <v>387</v>
+      </c>
+      <c r="BA8" t="s">
         <v>885</v>
       </c>
-      <c r="BA8" t="s">
+      <c r="BB8" t="s">
         <v>886</v>
-      </c>
-      <c r="BB8" t="s">
-        <v>887</v>
       </c>
       <c r="BC8" t="s">
         <v>387</v>
       </c>
       <c r="BE8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="BF8" t="s">
         <v>177</v>
@@ -14957,7 +14993,7 @@
         <v>177</v>
       </c>
       <c r="BM8" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="BN8" t="s">
         <v>387</v>
@@ -14968,43 +15004,43 @@
     </row>
     <row r="9" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E9" t="s">
         <v>659</v>
       </c>
       <c r="J9" t="s">
+        <v>890</v>
+      </c>
+      <c r="K9" t="s">
         <v>891</v>
       </c>
-      <c r="K9" t="s">
+      <c r="N9" t="s">
         <v>892</v>
       </c>
-      <c r="N9" t="s">
+      <c r="R9" t="s">
         <v>893</v>
       </c>
-      <c r="R9" t="s">
-        <v>894</v>
-      </c>
       <c r="U9" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="V9" t="s">
         <v>700</v>
       </c>
       <c r="W9" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="X9" t="s">
         <v>387</v>
       </c>
       <c r="Z9" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="AA9" t="s">
         <v>387</v>
       </c>
       <c r="AH9" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="AJ9" t="s">
         <v>694</v>
@@ -15028,27 +15064,27 @@
         <v>304</v>
       </c>
       <c r="BE9" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="BF9" t="s">
         <v>387</v>
       </c>
       <c r="BG9" t="s">
+        <v>898</v>
+      </c>
+      <c r="BM9" t="s">
         <v>899</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J10" t="s">
         <v>147</v>
       </c>
       <c r="K10" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="N10" t="s">
         <v>387</v>
@@ -15057,7 +15093,7 @@
         <v>387</v>
       </c>
       <c r="U10" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="V10" t="s">
         <v>387</v>
@@ -15066,7 +15102,7 @@
         <v>387</v>
       </c>
       <c r="Z10" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AH10" t="s">
         <v>387</v>
@@ -15081,10 +15117,10 @@
         <v>387</v>
       </c>
       <c r="BB10" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="BE10" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="BG10" t="s">
         <v>387</v>
@@ -15101,10 +15137,10 @@
         <v>387</v>
       </c>
       <c r="K11" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="U11" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="Z11" t="s">
         <v>387</v>
@@ -15113,7 +15149,7 @@
         <v>387</v>
       </c>
       <c r="BB11" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="BE11" t="s">
         <v>387</v>
@@ -15124,7 +15160,7 @@
         <v>387</v>
       </c>
       <c r="U12" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="BB12" t="s">
         <v>361</v>
@@ -15132,7 +15168,7 @@
     </row>
     <row r="13" spans="1:70" x14ac:dyDescent="0.25">
       <c r="U13" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="BB13" t="s">
         <v>367</v>
@@ -15348,7 +15384,7 @@
     </row>
     <row r="1573" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
       <c r="BH1573" s="13" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="1574" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
@@ -16943,47 +16979,47 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>909</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>911</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>913</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>915</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>917</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>47</v>
@@ -16991,7 +17027,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>47</v>
@@ -16999,15 +17035,15 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>921</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>47</v>
@@ -17015,7 +17051,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>47</v>
@@ -17023,74 +17059,74 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>925</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>927</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>929</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>931</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>932</v>
+      </c>
+      <c r="B15" t="s">
         <v>933</v>
-      </c>
-      <c r="B15" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B16" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B17" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B18" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>937</v>
+      </c>
+      <c r="B19" t="s">
         <v>938</v>
-      </c>
-      <c r="B19" t="s">
-        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -17113,46 +17149,46 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>447</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>941</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -17465,7 +17501,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -17473,7 +17509,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -17481,7 +17517,7 @@
         <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -17489,7 +17525,7 @@
         <v>59</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -17497,7 +17533,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -17505,15 +17541,15 @@
         <v>68</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>951</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -17521,7 +17557,7 @@
         <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -17529,7 +17565,7 @@
         <v>74</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -17537,15 +17573,15 @@
         <v>447</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>956</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -17553,7 +17589,7 @@
         <v>396</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -17561,15 +17597,15 @@
         <v>392</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>960</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -17577,7 +17613,7 @@
         <v>430</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
   </sheetData>
@@ -17599,7 +17635,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>25</v>
@@ -17666,7 +17702,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">

--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\clipboard-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E81E72-F931-409E-8E2F-890984BA743C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AA634C-DC9E-4759-8CC5-FEEF52EB8FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="420" windowWidth="14715" windowHeight="13920" activeTab="1" xr2:uid="{B5A7B246-83E3-4800-9863-625CA16CE35B}"/>
+    <workbookView xWindow="810" yWindow="1095" windowWidth="25710" windowHeight="13920" activeTab="1" xr2:uid="{B5A7B246-83E3-4800-9863-625CA16CE35B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -4345,7 +4345,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>20</v>
       </c>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>48</v>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>48</v>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>48</v>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="N99" s="1"/>
       <c r="O99" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>47</v>

--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -671,7 +671,7 @@
     <t>SecurityBarsType</t>
   </si>
   <si>
-    <t>Security Bars=Yes</t>
+    <t>security_bars=Yes</t>
   </si>
   <si>
     <t>Security Bars Quick Release</t>

--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\clipboard-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AA634C-DC9E-4759-8CC5-FEEF52EB8FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CD6C32-447F-4EC7-99B2-50A7D373DE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="1095" windowWidth="25710" windowHeight="13920" activeTab="1" xr2:uid="{B5A7B246-83E3-4800-9863-625CA16CE35B}"/>
   </bookViews>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>48</v>
@@ -8414,7 +8414,7 @@
         <v>47</v>
       </c>
       <c r="P85" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q85" s="1" t="s">
         <v>304</v>

--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -7966,9 +7966,11 @@
         <v>47</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q76" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="Q76" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="R76" s="1" t="s">
         <v>51</v>
       </c>
@@ -9114,11 +9116,9 @@
         <v>48</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q99" s="1" t="s">
-        <v>338</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q99" s="1"/>
       <c r="R99" s="1" t="s">
         <v>51</v>
       </c>

--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -6887,7 +6887,7 @@
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>48</v>

--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -6239,7 +6239,7 @@
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>48</v>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>48</v>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>48</v>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="N86" s="1"/>
       <c r="O86" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P86" s="1" t="s">
         <v>48</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="N99" s="1"/>
       <c r="O99" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>48</v>

--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\clipboard-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CD6C32-447F-4EC7-99B2-50A7D373DE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0503F35B-1C55-4199-AC30-243021760131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="1095" windowWidth="25710" windowHeight="13920" activeTab="1" xr2:uid="{B5A7B246-83E3-4800-9863-625CA16CE35B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B5A7B246-83E3-4800-9863-625CA16CE35B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>48</v>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>48</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="N99" s="1"/>
       <c r="O99" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>48</v>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="N112" s="1"/>
       <c r="O112" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P112" s="1" t="s">
         <v>47</v>

--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\clipboard-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0503F35B-1C55-4199-AC30-243021760131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B8B624-5BC1-43C5-8887-B8A1D9D2B6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B5A7B246-83E3-4800-9863-625CA16CE35B}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3044" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="1007">
   <si>
     <t>Clipboard v3.0 Master Workbook — Base Configuration</t>
   </si>
@@ -2964,6 +2964,90 @@
   </si>
   <si>
     <t>Mini-Split / Ductls</t>
+  </si>
+  <si>
+    <t>Living Room</t>
+  </si>
+  <si>
+    <t>Presence checklist</t>
+  </si>
+  <si>
+    <t>Dining Room</t>
+  </si>
+  <si>
+    <t>dining_room_observed</t>
+  </si>
+  <si>
+    <t>kitchen_observed</t>
+  </si>
+  <si>
+    <t>Intentional redundancy with Kitchen section</t>
+  </si>
+  <si>
+    <t>family_room_observed</t>
+  </si>
+  <si>
+    <t>Great Room</t>
+  </si>
+  <si>
+    <t>great_room_observed</t>
+  </si>
+  <si>
+    <t>den_observed</t>
+  </si>
+  <si>
+    <t>Office / Study</t>
+  </si>
+  <si>
+    <t>office_observed</t>
+  </si>
+  <si>
+    <t>Florida Room</t>
+  </si>
+  <si>
+    <t>florida_room_observed</t>
+  </si>
+  <si>
+    <t>Sunroom</t>
+  </si>
+  <si>
+    <t>sunroom_observed</t>
+  </si>
+  <si>
+    <t>Loft</t>
+  </si>
+  <si>
+    <t>loft_observed</t>
+  </si>
+  <si>
+    <t>Bonus Room</t>
+  </si>
+  <si>
+    <t>bonus_room_observed</t>
+  </si>
+  <si>
+    <t>common_room_other</t>
+  </si>
+  <si>
+    <t>Other room description</t>
+  </si>
+  <si>
+    <t>Dining Area</t>
+  </si>
+  <si>
+    <t>dining_area_observed</t>
+  </si>
+  <si>
+    <t>Breakfast Area</t>
+  </si>
+  <si>
+    <t>living_room_observed</t>
+  </si>
+  <si>
+    <t>breakfast_area_observed</t>
+  </si>
+  <si>
+    <t>Living Areas</t>
   </si>
 </sst>
 </file>
@@ -3797,7 +3881,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AppDesignTable" displayName="AppDesignTable" ref="A1:R125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AppDesignTable" displayName="AppDesignTable" ref="A1:R140">
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Display Order"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tab"/>
@@ -4165,7 +4249,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R125"/>
+  <dimension ref="A1:R140"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
@@ -7875,32 +7959,32 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>277</v>
+        <v>1006</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>278</v>
+        <v>979</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>279</v>
+        <v>1004</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I75" s="1">
-        <v>0</v>
+      <c r="I75" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>48</v>
@@ -7911,7 +7995,9 @@
       <c r="M75" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N75" s="1"/>
+      <c r="N75" s="1" t="s">
+        <v>980</v>
+      </c>
       <c r="O75" s="1" t="s">
         <v>47</v>
       </c>
@@ -7925,32 +8011,32 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>1010</v>
+        <v>952</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>277</v>
+        <v>1006</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>280</v>
+        <v>981</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>281</v>
+        <v>982</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I76" s="1">
-        <v>0</v>
+      <c r="I76" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K76" s="1" t="s">
         <v>48</v>
@@ -7961,48 +8047,46 @@
       <c r="M76" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N76" s="1"/>
+      <c r="N76" s="1" t="s">
+        <v>980</v>
+      </c>
       <c r="O76" s="1" t="s">
         <v>47</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q76" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="R76" s="1" t="s">
-        <v>51</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>1020</v>
+        <v>954</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>277</v>
+        <v>1006</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>282</v>
+        <v>1001</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>283</v>
+        <v>1002</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I77" s="1">
-        <v>0</v>
+      <c r="I77" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K77" s="1" t="s">
         <v>48</v>
@@ -8013,7 +8097,9 @@
       <c r="M77" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N77" s="1"/>
+      <c r="N77" s="1" t="s">
+        <v>980</v>
+      </c>
       <c r="O77" s="1" t="s">
         <v>47</v>
       </c>
@@ -8027,43 +8113,45 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>1030</v>
-      </c>
-      <c r="B78" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="B78" s="12" t="s">
         <v>276</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I78" s="1">
-        <v>0</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N78" s="1"/>
+        <v>1006</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K78" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L78" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M78" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N78" s="12" t="s">
+        <v>984</v>
+      </c>
       <c r="O78" s="1" t="s">
         <v>47</v>
       </c>
@@ -8077,43 +8165,45 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>1040</v>
-      </c>
-      <c r="B79" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B79" s="12" t="s">
         <v>276</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M79" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N79" s="1"/>
+        <v>1006</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G79" s="12"/>
+      <c r="H79" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J79" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K79" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L79" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M79" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N79" s="12" t="s">
+        <v>980</v>
+      </c>
       <c r="O79" s="1" t="s">
         <v>47</v>
       </c>
@@ -8127,43 +8217,45 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>1050</v>
-      </c>
-      <c r="B80" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="B80" s="12" t="s">
         <v>276</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L80" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M80" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N80" s="1"/>
+        <v>1006</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G80" s="12"/>
+      <c r="H80" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I80" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K80" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L80" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M80" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N80" s="12" t="s">
+        <v>980</v>
+      </c>
       <c r="O80" s="1" t="s">
         <v>47</v>
       </c>
@@ -8177,43 +8269,45 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>1060</v>
-      </c>
-      <c r="B81" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B81" s="12" t="s">
         <v>276</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M81" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N81" s="1"/>
+        <v>1006</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>986</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I81" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J81" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K81" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L81" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M81" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N81" s="12" t="s">
+        <v>980</v>
+      </c>
       <c r="O81" s="1" t="s">
         <v>47</v>
       </c>
@@ -8227,41 +8321,45 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>1061</v>
-      </c>
-      <c r="B82" s="27" t="s">
+        <v>964</v>
+      </c>
+      <c r="B82" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="C82" s="27" t="s">
-        <v>286</v>
-      </c>
-      <c r="D82" s="27" t="s">
-        <v>296</v>
-      </c>
-      <c r="E82" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="F82" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G82" s="1"/>
-      <c r="H82" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="I82" s="1"/>
-      <c r="J82" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="K82" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M82" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N82" s="1"/>
+      <c r="C82" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>899</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G82" s="12"/>
+      <c r="H82" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I82" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J82" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K82" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L82" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M82" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N82" s="12" t="s">
+        <v>980</v>
+      </c>
       <c r="O82" s="1" t="s">
         <v>47</v>
       </c>
@@ -8269,49 +8367,51 @@
         <v>48</v>
       </c>
       <c r="Q82" s="1"/>
-      <c r="R82" s="27" t="s">
+      <c r="R82" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>1070</v>
-      </c>
-      <c r="B83" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="B83" s="12" t="s">
         <v>276</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L83" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M83" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N83" s="1"/>
+        <v>1006</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>989</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>990</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G83" s="12"/>
+      <c r="H83" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I83" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K83" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L83" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M83" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N83" s="12" t="s">
+        <v>980</v>
+      </c>
       <c r="O83" s="1" t="s">
         <v>47</v>
       </c>
@@ -8325,43 +8425,45 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>1080</v>
-      </c>
-      <c r="B84" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B84" s="12" t="s">
         <v>276</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N84" s="1"/>
+        <v>1006</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="F84" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I84" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J84" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K84" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L84" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M84" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N84" s="12" t="s">
+        <v>980</v>
+      </c>
       <c r="O84" s="1" t="s">
         <v>47</v>
       </c>
@@ -8375,95 +8477,97 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>1099</v>
-      </c>
-      <c r="B85" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="B85" s="12" t="s">
         <v>276</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I85" s="1">
-        <v>1</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L85" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N85" s="1"/>
+        <v>1006</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>993</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>994</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G85" s="12"/>
+      <c r="H85" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I85" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J85" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K85" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L85" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M85" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N85" s="12" t="s">
+        <v>980</v>
+      </c>
       <c r="O85" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P85" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q85" s="1" t="s">
-        <v>304</v>
-      </c>
+      <c r="P85" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q85" s="1"/>
       <c r="R85" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>1100</v>
-      </c>
-      <c r="B86" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B86" s="12" t="s">
         <v>276</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N86" s="1"/>
+        <v>1006</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>996</v>
+      </c>
+      <c r="F86" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G86" s="12"/>
+      <c r="H86" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I86" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J86" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K86" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L86" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M86" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N86" s="12" t="s">
+        <v>980</v>
+      </c>
       <c r="O86" s="1" t="s">
         <v>47</v>
       </c>
@@ -8477,43 +8581,45 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>1101</v>
-      </c>
-      <c r="B87" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="B87" s="12" t="s">
         <v>276</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I87" s="1">
-        <v>0</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M87" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N87" s="1"/>
+        <v>1006</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>997</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>998</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G87" s="12"/>
+      <c r="H87" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I87" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K87" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L87" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M87" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N87" s="12" t="s">
+        <v>980</v>
+      </c>
       <c r="O87" s="1" t="s">
         <v>47</v>
       </c>
@@ -8527,43 +8633,43 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>1102</v>
-      </c>
-      <c r="B88" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B88" s="12" t="s">
         <v>276</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I88" s="1">
-        <v>0</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L88" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M88" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N88" s="1"/>
+        <v>1006</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G88" s="12"/>
+      <c r="H88" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I88" s="12"/>
+      <c r="J88" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K88" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L88" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M88" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N88" s="12" t="s">
+        <v>1000</v>
+      </c>
       <c r="O88" s="1" t="s">
         <v>47</v>
       </c>
@@ -8576,70 +8682,40 @@
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>1103</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
       <c r="G89" s="1"/>
-      <c r="H89" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I89" s="1">
-        <v>0</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M89" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1"/>
       <c r="N89" s="1"/>
-      <c r="O89" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="P89" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="O89" s="1"/>
+      <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
-      <c r="R89" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="R89" s="1"/>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>1104</v>
+        <v>1005</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>316</v>
+        <v>278</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>317</v>
+        <v>279</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>74</v>
@@ -8652,7 +8728,7 @@
         <v>0</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K90" s="1" t="s">
         <v>48</v>
@@ -8677,19 +8753,19 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>1105</v>
+        <v>1010</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>318</v>
+        <v>280</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>74</v>
@@ -8702,7 +8778,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K91" s="1" t="s">
         <v>48</v>
@@ -8718,28 +8794,30 @@
         <v>47</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q91" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="Q91" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="R91" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>1106</v>
+        <v>1020</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>320</v>
+        <v>282</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>321</v>
+        <v>283</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>74</v>
@@ -8752,7 +8830,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K92" s="1" t="s">
         <v>48</v>
@@ -8777,19 +8855,19 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>1107</v>
+        <v>1030</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D93" s="27" t="s">
-        <v>322</v>
+        <v>277</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>323</v>
+        <v>285</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>74</v>
@@ -8802,10 +8880,10 @@
         <v>0</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L93" s="1" t="s">
         <v>47</v>
@@ -8827,35 +8905,35 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>1108</v>
+        <v>1040</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>324</v>
+        <v>287</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>325</v>
+        <v>288</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G94" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="H94" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I94" s="1" t="s">
-        <v>326</v>
-      </c>
+      <c r="I94" s="1"/>
       <c r="J94" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L94" s="1" t="s">
         <v>47</v>
@@ -8877,25 +8955,25 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>1110</v>
+        <v>1050</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>327</v>
+        <v>290</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>328</v>
+        <v>291</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>329</v>
+        <v>292</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>48</v>
@@ -8927,25 +9005,25 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>1120</v>
+        <v>1060</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>330</v>
+        <v>293</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>331</v>
+        <v>294</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>332</v>
+        <v>295</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>48</v>
@@ -8977,35 +9055,33 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>1130</v>
-      </c>
-      <c r="B97" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B97" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="H97" s="1" t="s">
+      <c r="C97" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="D97" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="E97" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="F97" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="G97" s="1"/>
+      <c r="H97" s="27" t="s">
         <v>48</v>
       </c>
       <c r="I97" s="1"/>
-      <c r="J97" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>47</v>
+      <c r="J97" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="K97" s="27" t="s">
+        <v>48</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>47</v>
@@ -9021,30 +9097,32 @@
         <v>48</v>
       </c>
       <c r="Q97" s="1"/>
-      <c r="R97" s="1" t="s">
+      <c r="R97" s="27" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>1140</v>
+        <v>1070</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>336</v>
+        <v>298</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>337</v>
+        <v>299</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G98" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>300</v>
+      </c>
       <c r="H98" s="1" t="s">
         <v>48</v>
       </c>
@@ -9075,32 +9153,32 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>338</v>
+        <v>286</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>339</v>
+        <v>301</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>340</v>
+        <v>302</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>341</v>
+        <v>303</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>48</v>
       </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K99" s="1" t="s">
         <v>47</v>
@@ -9113,7 +9191,7 @@
       </c>
       <c r="N99" s="1"/>
       <c r="O99" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P99" s="1" t="s">
         <v>48</v>
@@ -9125,35 +9203,35 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>1210</v>
+        <v>1099</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>342</v>
+        <v>305</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>343</v>
+        <v>306</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>344</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G100" s="1"/>
       <c r="H100" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I100" s="1"/>
+      <c r="I100" s="1">
+        <v>1</v>
+      </c>
       <c r="J100" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L100" s="1" t="s">
         <v>47</v>
@@ -9165,34 +9243,38 @@
       <c r="O100" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P100" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q100" s="1"/>
+      <c r="P100" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q100" s="1" t="s">
+        <v>304</v>
+      </c>
       <c r="R100" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>1220</v>
+        <v>1100</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>345</v>
+        <v>307</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>346</v>
+        <v>308</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G101" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>309</v>
+      </c>
       <c r="H101" s="1" t="s">
         <v>48</v>
       </c>
@@ -9201,7 +9283,7 @@
         <v>48</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>47</v>
@@ -9223,35 +9305,35 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>1300</v>
+        <v>1101</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>347</v>
+        <v>304</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>349</v>
+        <v>311</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>350</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G102" s="1"/>
       <c r="H102" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I102" s="1"/>
+      <c r="I102" s="1">
+        <v>0</v>
+      </c>
       <c r="J102" s="1" t="s">
         <v>48</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L102" s="1" t="s">
         <v>47</v>
@@ -9273,35 +9355,35 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>1310</v>
+        <v>1102</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>347</v>
+        <v>304</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>351</v>
+        <v>312</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>352</v>
+        <v>313</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>353</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G103" s="1"/>
       <c r="H103" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I103" s="1"/>
+      <c r="I103" s="1">
+        <v>0</v>
+      </c>
       <c r="J103" s="1" t="s">
         <v>48</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L103" s="1" t="s">
         <v>47</v>
@@ -9323,35 +9405,35 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>1320</v>
+        <v>1103</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>354</v>
+        <v>304</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>357</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G104" s="1"/>
       <c r="H104" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I104" s="1"/>
+      <c r="I104" s="1">
+        <v>0</v>
+      </c>
       <c r="J104" s="1" t="s">
         <v>48</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L104" s="1" t="s">
         <v>47</v>
@@ -9373,33 +9455,35 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>1330</v>
+        <v>1104</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>358</v>
+        <v>316</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>359</v>
+        <v>317</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="G105" s="1"/>
       <c r="H105" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I105" s="1"/>
+      <c r="I105" s="1">
+        <v>0</v>
+      </c>
       <c r="J105" s="1" t="s">
         <v>48</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L105" s="1" t="s">
         <v>47</v>
@@ -9419,57 +9503,87 @@
         <v>51</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="8"/>
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="8"/>
-      <c r="L106" s="8"/>
-      <c r="M106" s="8"/>
-      <c r="N106" s="8"/>
-      <c r="O106" s="8"/>
-      <c r="P106" s="8"/>
-      <c r="Q106" s="8"/>
-      <c r="R106" s="8"/>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>1105</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I106" s="1">
+        <v>0</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N106" s="1"/>
+      <c r="O106" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P106" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q106" s="1"/>
+      <c r="R106" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>1400</v>
+        <v>1106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>361</v>
+        <v>304</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>362</v>
+        <v>320</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>363</v>
+        <v>321</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>364</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G107" s="1"/>
       <c r="H107" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I107" s="1"/>
+      <c r="I107" s="1">
+        <v>0</v>
+      </c>
       <c r="J107" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L107" s="1" t="s">
         <v>47</v>
@@ -9482,30 +9596,28 @@
         <v>47</v>
       </c>
       <c r="P107" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q107" s="1" t="s">
-        <v>361</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q107" s="1"/>
       <c r="R107" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>1410</v>
+        <v>1107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>365</v>
+        <v>304</v>
+      </c>
+      <c r="D108" s="27" t="s">
+        <v>322</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>366</v>
+        <v>323</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>74</v>
@@ -9518,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K108" s="1" t="s">
         <v>48</v>
@@ -9543,35 +9655,35 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>1420</v>
+        <v>1108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>367</v>
+        <v>304</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>369</v>
+        <v>325</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>370</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="G109" s="1"/>
       <c r="H109" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I109" s="1"/>
+      <c r="I109" s="1" t="s">
+        <v>326</v>
+      </c>
       <c r="J109" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L109" s="1" t="s">
         <v>47</v>
@@ -9584,46 +9696,44 @@
         <v>47</v>
       </c>
       <c r="P109" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q109" s="1" t="s">
-        <v>367</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q109" s="1"/>
       <c r="R109" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>1430</v>
+        <v>1110</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>367</v>
+        <v>304</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>371</v>
+        <v>327</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G110" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="H110" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I110" s="1">
-        <v>0</v>
-      </c>
+      <c r="I110" s="1"/>
       <c r="J110" s="1" t="s">
         <v>48</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L110" s="1" t="s">
         <v>47</v>
@@ -9645,25 +9755,25 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>1440</v>
+        <v>1120</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>373</v>
+        <v>304</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>374</v>
+        <v>330</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>376</v>
+        <v>332</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>48</v>
@@ -9686,36 +9796,34 @@
         <v>47</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q111" s="1" t="s">
-        <v>373</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q111" s="1"/>
       <c r="R111" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>1450</v>
+        <v>1130</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>379</v>
+        <v>334</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>380</v>
+        <v>335</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>48</v>
@@ -9735,49 +9843,45 @@
       </c>
       <c r="N112" s="1"/>
       <c r="O112" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P112" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q112" s="1" t="s">
-        <v>377</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q112" s="1"/>
       <c r="R112" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>1460</v>
+        <v>1140</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>381</v>
+        <v>336</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>382</v>
+        <v>337</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G113" s="1"/>
       <c r="H113" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I113" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="I113" s="1"/>
       <c r="J113" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L113" s="1" t="s">
         <v>47</v>
@@ -9799,35 +9903,35 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>1470</v>
+        <v>1200</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>131</v>
+        <v>338</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>383</v>
+        <v>339</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>384</v>
+        <v>340</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G114" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="H114" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I114" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="I114" s="1"/>
       <c r="J114" s="1" t="s">
         <v>47</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>47</v>
@@ -9837,7 +9941,7 @@
       </c>
       <c r="N114" s="1"/>
       <c r="O114" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P114" s="1" t="s">
         <v>48</v>
@@ -9849,24 +9953,26 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>1480</v>
+        <v>1210</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>131</v>
+        <v>338</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>386</v>
+        <v>343</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G115" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>344</v>
+      </c>
       <c r="H115" s="1" t="s">
         <v>48</v>
       </c>
@@ -9875,7 +9981,7 @@
         <v>48</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>47</v>
@@ -9897,22 +10003,22 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>1490</v>
+        <v>1220</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>388</v>
+        <v>345</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>389</v>
+        <v>346</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="1" t="s">
@@ -9945,24 +10051,26 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>360</v>
+        <v>276</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G117" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>350</v>
+      </c>
       <c r="H117" s="1" t="s">
         <v>48</v>
       </c>
@@ -9991,46 +10099,78 @@
         <v>51</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="8"/>
-      <c r="B118" s="8"/>
-      <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="8"/>
-      <c r="G118" s="8"/>
-      <c r="H118" s="8"/>
-      <c r="I118" s="8"/>
-      <c r="J118" s="8"/>
-      <c r="K118" s="8"/>
-      <c r="L118" s="8"/>
-      <c r="M118" s="8"/>
-      <c r="N118" s="8"/>
-      <c r="O118" s="8"/>
-      <c r="P118" s="8"/>
-      <c r="Q118" s="8"/>
-      <c r="R118" s="8"/>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>1310</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M118" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N118" s="1"/>
+      <c r="O118" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P118" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q118" s="1"/>
+      <c r="R118" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>1600</v>
+        <v>1320</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>392</v>
+        <v>276</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>393</v>
+        <v>354</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>394</v>
+        <v>355</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>395</v>
+        <v>356</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="G119" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="H119" s="1" t="s">
         <v>48</v>
       </c>
@@ -10047,9 +10187,7 @@
       <c r="M119" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N119" s="1" t="s">
-        <v>397</v>
-      </c>
+      <c r="N119" s="1"/>
       <c r="O119" s="1" t="s">
         <v>47</v>
       </c>
@@ -10063,22 +10201,22 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>1610</v>
+        <v>1330</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>392</v>
+        <v>276</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>398</v>
+        <v>358</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>399</v>
+        <v>359</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>392</v>
+        <v>97</v>
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
@@ -10089,7 +10227,7 @@
         <v>48</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L120" s="1" t="s">
         <v>47</v>
@@ -10109,105 +10247,109 @@
         <v>51</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
-        <v>1620</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="G121" s="1"/>
-      <c r="H121" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I121" s="1"/>
-      <c r="J121" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L121" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M121" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N121" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="O121" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="P121" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q121" s="1"/>
-      <c r="R121" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="122" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="8"/>
-      <c r="B122" s="8"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
-      <c r="G122" s="8"/>
-      <c r="H122" s="8"/>
-      <c r="I122" s="8"/>
-      <c r="J122" s="8"/>
-      <c r="K122" s="8"/>
-      <c r="L122" s="8"/>
-      <c r="M122" s="8"/>
-      <c r="N122" s="8"/>
-      <c r="O122" s="8"/>
-      <c r="P122" s="8"/>
-      <c r="Q122" s="8"/>
-      <c r="R122" s="8"/>
+    <row r="121" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="8"/>
+      <c r="B121" s="8"/>
+      <c r="C121" s="8"/>
+      <c r="D121" s="8"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="8"/>
+      <c r="G121" s="8"/>
+      <c r="H121" s="8"/>
+      <c r="I121" s="8"/>
+      <c r="J121" s="8"/>
+      <c r="K121" s="8"/>
+      <c r="L121" s="8"/>
+      <c r="M121" s="8"/>
+      <c r="N121" s="8"/>
+      <c r="O121" s="8"/>
+      <c r="P121" s="8"/>
+      <c r="Q121" s="8"/>
+      <c r="R121" s="8"/>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>1400</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N122" s="1"/>
+      <c r="O122" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P122" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q122" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="R122" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>1700</v>
+        <v>1410</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>403</v>
+        <v>360</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>404</v>
+        <v>361</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>396</v>
+        <v>74</v>
       </c>
       <c r="G123" s="1"/>
       <c r="H123" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I123" s="1"/>
+      <c r="I123" s="1">
+        <v>0</v>
+      </c>
       <c r="J123" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L123" s="1" t="s">
         <v>47</v>
@@ -10215,9 +10357,7 @@
       <c r="M123" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N123" s="1" t="s">
-        <v>407</v>
-      </c>
+      <c r="N123" s="1"/>
       <c r="O123" s="1" t="s">
         <v>47</v>
       </c>
@@ -10231,32 +10371,32 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>1710</v>
+        <v>1420</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>403</v>
+        <v>360</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>404</v>
+        <v>367</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>408</v>
+        <v>368</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>409</v>
+        <v>369</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>396</v>
+        <v>68</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="1"/>
       <c r="J124" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K124" s="1" t="s">
         <v>47</v>
@@ -10272,37 +10412,41 @@
         <v>47</v>
       </c>
       <c r="P124" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q124" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="Q124" s="1" t="s">
+        <v>367</v>
+      </c>
       <c r="R124" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>1800</v>
+        <v>1430</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>411</v>
+        <v>360</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>412</v>
+        <v>367</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>413</v>
+        <v>371</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>414</v>
+        <v>372</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="G125" s="1"/>
       <c r="H125" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I125" s="1"/>
+      <c r="I125" s="1">
+        <v>0</v>
+      </c>
       <c r="J125" s="1" t="s">
         <v>48</v>
       </c>
@@ -10327,11 +10471,695 @@
         <v>51</v>
       </c>
     </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>1440</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M126" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N126" s="1"/>
+      <c r="O126" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P126" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q126" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="R126" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>1450</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M127" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N127" s="1"/>
+      <c r="O127" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P127" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q127" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="R127" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>1460</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M128" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N128" s="1"/>
+      <c r="O128" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P128" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q128" s="1"/>
+      <c r="R128" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>1470</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M129" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N129" s="1"/>
+      <c r="O129" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P129" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q129" s="1"/>
+      <c r="R129" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>1480</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G130" s="1"/>
+      <c r="H130" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I130" s="1"/>
+      <c r="J130" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M130" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N130" s="1"/>
+      <c r="O130" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P130" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q130" s="1"/>
+      <c r="R130" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>1490</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G131" s="1"/>
+      <c r="H131" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I131" s="1"/>
+      <c r="J131" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M131" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N131" s="1"/>
+      <c r="O131" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P131" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q131" s="1"/>
+      <c r="R131" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>1500</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M132" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N132" s="1"/>
+      <c r="O132" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P132" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q132" s="1"/>
+      <c r="R132" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="8"/>
+      <c r="B133" s="8"/>
+      <c r="C133" s="8"/>
+      <c r="D133" s="8"/>
+      <c r="E133" s="8"/>
+      <c r="F133" s="8"/>
+      <c r="G133" s="8"/>
+      <c r="H133" s="8"/>
+      <c r="I133" s="8"/>
+      <c r="J133" s="8"/>
+      <c r="K133" s="8"/>
+      <c r="L133" s="8"/>
+      <c r="M133" s="8"/>
+      <c r="N133" s="8"/>
+      <c r="O133" s="8"/>
+      <c r="P133" s="8"/>
+      <c r="Q133" s="8"/>
+      <c r="R133" s="8"/>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>1600</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="G134" s="1"/>
+      <c r="H134" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I134" s="1"/>
+      <c r="J134" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M134" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N134" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="O134" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P134" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q134" s="1"/>
+      <c r="R134" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>1610</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G135" s="1"/>
+      <c r="H135" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I135" s="1"/>
+      <c r="J135" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N135" s="1"/>
+      <c r="O135" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P135" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q135" s="1"/>
+      <c r="R135" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>1620</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N136" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="O136" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P136" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q136" s="1"/>
+      <c r="R136" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="8"/>
+      <c r="B137" s="8"/>
+      <c r="C137" s="8"/>
+      <c r="D137" s="8"/>
+      <c r="E137" s="8"/>
+      <c r="F137" s="8"/>
+      <c r="G137" s="8"/>
+      <c r="H137" s="8"/>
+      <c r="I137" s="8"/>
+      <c r="J137" s="8"/>
+      <c r="K137" s="8"/>
+      <c r="L137" s="8"/>
+      <c r="M137" s="8"/>
+      <c r="N137" s="8"/>
+      <c r="O137" s="8"/>
+      <c r="P137" s="8"/>
+      <c r="Q137" s="8"/>
+      <c r="R137" s="8"/>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>1700</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M138" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N138" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="O138" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P138" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q138" s="1"/>
+      <c r="R138" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>1710</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I139" s="1"/>
+      <c r="J139" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M139" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N139" s="1"/>
+      <c r="O139" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P139" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q139" s="1"/>
+      <c r="R139" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>1800</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I140" s="1"/>
+      <c r="J140" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L140" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M140" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N140" s="1"/>
+      <c r="O140" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P140" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q140" s="1"/>
+      <c r="R140" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E1048576">
+  <conditionalFormatting sqref="E89:E1048576 E1:E77">
     <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M125">
+  <conditionalFormatting sqref="M2:M77 M89:M140">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>M2="Draft"</formula>
     </cfRule>
@@ -10342,27 +11170,27 @@
       <formula>M2="Complete"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P125">
+  <conditionalFormatting sqref="P2:P140">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>P2="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R125">
+  <conditionalFormatting sqref="R2:R140">
     <cfRule type="expression" dxfId="1" priority="3">
       <formula>R2&lt;&gt;"Always"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="B2:B125" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="B2:B77 B89:B140" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Property,Site,Exterior,Interior,Mechanical,Sketch,Photos,Exit Interview,Review"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F2:F125" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="F2:F77 F89:F140" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Text,LongText,Button,Dropdown,MultiSelect,Checkbox,Toggle,Counter,Date,Time,Camera,Sketch,Rating,Currency"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2:L14 H2:H125 O2:P125 J2:K125 L16:L125" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" sqref="L2:L14 H2:H77 J2:K77 L16:L77 H89:H140 J89:L140 O2:P140" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M2:M125" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" sqref="M2:M77 M89:M140" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"Draft,Testing,Complete"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Clipboard_v4_Master_Base.xlsx
+++ b/Clipboard_v4_Master_Base.xlsx
@@ -1,33 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\clipboard-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B8B624-5BC1-43C5-8887-B8A1D9D2B6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFF52DE-420B-46DB-99E7-D66AA23DB066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B5A7B246-83E3-4800-9863-625CA16CE35B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="APP DESIGN" sheetId="2" r:id="rId2"/>
-    <sheet name="FOLLOW-UP TEMPLATES" sheetId="3" r:id="rId3"/>
-    <sheet name="Lists" sheetId="4" r:id="rId4"/>
-    <sheet name="Settings" sheetId="5" r:id="rId5"/>
-    <sheet name="Changelog" sheetId="6" r:id="rId6"/>
-    <sheet name="Input Types" sheetId="7" r:id="rId7"/>
-    <sheet name="Navigation" sheetId="8" r:id="rId8"/>
+    <sheet name="Rules" sheetId="9" r:id="rId3"/>
+    <sheet name="FOLLOW-UP TEMPLATES" sheetId="3" r:id="rId4"/>
+    <sheet name="Lists" sheetId="4" r:id="rId5"/>
+    <sheet name="Settings" sheetId="5" r:id="rId6"/>
+    <sheet name="Changelog" sheetId="6" r:id="rId7"/>
+    <sheet name="Input Types" sheetId="7" r:id="rId8"/>
+    <sheet name="Navigation" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3308" uniqueCount="1057">
   <si>
     <t>Clipboard v3.0 Master Workbook — Base Configuration</t>
   </si>
@@ -3048,6 +3049,156 @@
   </si>
   <si>
     <t>Living Areas</t>
+  </si>
+  <si>
+    <t>Syntax</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>Field is always visible.</t>
+  </si>
+  <si>
+    <t>FieldID=Value</t>
+  </si>
+  <si>
+    <t>Show when the referenced field equals the value.</t>
+  </si>
+  <si>
+    <t>FieldID!=Value</t>
+  </si>
+  <si>
+    <t>Show when the referenced field does not equal the value.</t>
+  </si>
+  <si>
+    <t>FieldID&gt;Value</t>
+  </si>
+  <si>
+    <t>Show when the referenced numeric field is greater than the value.</t>
+  </si>
+  <si>
+    <t>FieldID&gt;=Value</t>
+  </si>
+  <si>
+    <t>Show when the referenced numeric field is greater than or equal to the value.</t>
+  </si>
+  <si>
+    <t>FieldID&lt;Value</t>
+  </si>
+  <si>
+    <t>Show when the referenced numeric field is less than the value.</t>
+  </si>
+  <si>
+    <t>FieldID&lt;=Value</t>
+  </si>
+  <si>
+    <t>Show when the referenced numeric field is less than or equal to the value.</t>
+  </si>
+  <si>
+    <t>FieldID contains Value</t>
+  </si>
+  <si>
+    <t>Show when a MultiSelect field includes the value.</t>
+  </si>
+  <si>
+    <t>Rule1 AND Rule2</t>
+  </si>
+  <si>
+    <t>Show only when both rules are true.</t>
+  </si>
+  <si>
+    <t>Rule1 OR Rule2</t>
+  </si>
+  <si>
+    <t>Show when either rule is true.</t>
+  </si>
+  <si>
+    <t>Visibility Rule Syntax</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>Always show the field.</t>
+  </si>
+  <si>
+    <t>pud=Yes</t>
+  </si>
+  <si>
+    <t>Show when PUD is marked Yes.</t>
+  </si>
+  <si>
+    <t>occupancy=Vacant</t>
+  </si>
+  <si>
+    <t>Show when occupancy is Vacant.</t>
+  </si>
+  <si>
+    <t>stories&gt;1</t>
+  </si>
+  <si>
+    <t>Show when the property has more than one story.</t>
+  </si>
+  <si>
+    <t>pool=Yes</t>
+  </si>
+  <si>
+    <t>Show when a pool is present.</t>
+  </si>
+  <si>
+    <t>solar_panels=Yes</t>
+  </si>
+  <si>
+    <t>Show when solar panels are present.</t>
+  </si>
+  <si>
+    <t>roof_material contains Modified Bitumen</t>
+  </si>
+  <si>
+    <t>Show when Modified Bitumen is one of the selected roof materials.</t>
+  </si>
+  <si>
+    <t>occupancy=Vacant AND utilities_on=Yes</t>
+  </si>
+  <si>
+    <t>Show only when the property is vacant and utilities are on.</t>
+  </si>
+  <si>
+    <t>pool=Yes OR spa=Yes</t>
+  </si>
+  <si>
+    <t>Show when either a pool or spa is present.</t>
+  </si>
+  <si>
+    <t>hoa!=No</t>
+  </si>
+  <si>
+    <t>Show when HOA is anything other than No.</t>
+  </si>
+  <si>
+    <t>Examples</t>
+  </si>
+  <si>
+    <t>Rule ID</t>
+  </si>
+  <si>
+    <t>Expression</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>VACANT_PROPERTY</t>
+  </si>
+  <si>
+    <t>Property is vacant</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -3057,7 +3208,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -3144,8 +3295,42 @@
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3174,8 +3359,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -3235,11 +3426,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3323,11 +3527,37 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4116,37 +4346,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:8" ht="21">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -4154,7 +4384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -4162,7 +4392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -4170,7 +4400,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -4178,7 +4408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -4186,7 +4416,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -4194,7 +4424,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -4202,7 +4432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -4210,11 +4440,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -4222,7 +4452,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -4230,7 +4460,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="30">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -4250,7 +4480,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R140"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
@@ -4271,7 +4501,7 @@
     <col min="18" max="18" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="30">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -4327,7 +4557,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18">
       <c r="A2" s="1">
         <v>10</v>
       </c>
@@ -4377,7 +4607,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18">
       <c r="A3" s="1">
         <v>15</v>
       </c>
@@ -4429,7 +4659,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18">
       <c r="A4" s="1">
         <v>20</v>
       </c>
@@ -4483,7 +4713,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18">
       <c r="A5" s="1">
         <v>30</v>
       </c>
@@ -4535,7 +4765,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18">
       <c r="A6" s="1">
         <v>35</v>
       </c>
@@ -4589,7 +4819,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18">
       <c r="A7" s="1">
         <v>40</v>
       </c>
@@ -4639,7 +4869,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18">
       <c r="A8" s="1">
         <v>50</v>
       </c>
@@ -4689,7 +4919,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18">
       <c r="A9" s="1">
         <v>60</v>
       </c>
@@ -4741,7 +4971,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18">
       <c r="A10" s="1">
         <v>70</v>
       </c>
@@ -4793,7 +5023,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18">
       <c r="A11" s="1">
         <v>80</v>
       </c>
@@ -4845,7 +5075,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18">
       <c r="A12" s="1">
         <v>90</v>
       </c>
@@ -4897,7 +5127,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18">
       <c r="A13" s="1">
         <v>100</v>
       </c>
@@ -4949,7 +5179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="30">
       <c r="A14" s="1">
         <v>110</v>
       </c>
@@ -4999,7 +5229,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="9" customHeight="1">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -5019,7 +5249,7 @@
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18">
       <c r="A16" s="1">
         <v>200</v>
       </c>
@@ -5071,7 +5301,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18">
       <c r="A17" s="1">
         <v>210</v>
       </c>
@@ -5123,7 +5353,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18">
       <c r="A18" s="1">
         <v>220</v>
       </c>
@@ -5173,7 +5403,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18">
       <c r="A19" s="1">
         <v>230</v>
       </c>
@@ -5223,7 +5453,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18">
       <c r="A20" s="1">
         <v>240</v>
       </c>
@@ -5273,7 +5503,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18">
       <c r="A21" s="1">
         <v>250</v>
       </c>
@@ -5325,7 +5555,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18">
       <c r="A22" s="1">
         <v>260</v>
       </c>
@@ -5377,7 +5607,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18">
       <c r="A23" s="1">
         <v>270</v>
       </c>
@@ -5429,7 +5659,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18">
       <c r="A24" s="1">
         <v>280</v>
       </c>
@@ -5481,7 +5711,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18">
       <c r="A25" s="1">
         <v>290</v>
       </c>
@@ -5531,7 +5761,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18">
       <c r="A26" s="1">
         <v>300</v>
       </c>
@@ -5581,7 +5811,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18">
       <c r="A27" s="1">
         <v>310</v>
       </c>
@@ -5633,7 +5863,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18">
       <c r="A28" s="1">
         <v>320</v>
       </c>
@@ -5689,7 +5919,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18">
       <c r="A29" s="1">
         <v>330</v>
       </c>
@@ -5745,7 +5975,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18">
       <c r="A30" s="1">
         <v>340</v>
       </c>
@@ -5795,7 +6025,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18">
       <c r="A31" s="1">
         <v>350</v>
       </c>
@@ -5847,7 +6077,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18">
       <c r="A32" s="1">
         <v>360</v>
       </c>
@@ -5899,7 +6129,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18">
       <c r="A33" s="1">
         <v>365</v>
       </c>
@@ -5951,7 +6181,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18">
       <c r="A34" s="1">
         <v>370</v>
       </c>
@@ -5999,7 +6229,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="9" customHeight="1">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -6019,7 +6249,7 @@
       <c r="Q35" s="8"/>
       <c r="R35" s="8"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18">
       <c r="A36" s="1">
         <v>400</v>
       </c>
@@ -6071,7 +6301,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18">
       <c r="A37" s="1">
         <v>410</v>
       </c>
@@ -6123,7 +6353,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18">
       <c r="A38" s="1">
         <v>420</v>
       </c>
@@ -6177,7 +6407,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18">
       <c r="A39" s="1">
         <v>430</v>
       </c>
@@ -6229,7 +6459,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="15" customHeight="1">
       <c r="A40" s="1">
         <v>500</v>
       </c>
@@ -6283,7 +6513,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18">
       <c r="A41" s="1">
         <v>510</v>
       </c>
@@ -6333,7 +6563,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18">
       <c r="A42" s="1">
         <v>520</v>
       </c>
@@ -6383,7 +6613,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18">
       <c r="A43" s="1">
         <v>530</v>
       </c>
@@ -6423,7 +6653,7 @@
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>48</v>
@@ -6433,7 +6663,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18">
       <c r="A44" s="1">
         <v>540</v>
       </c>
@@ -6473,7 +6703,7 @@
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>48</v>
@@ -6483,7 +6713,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18">
       <c r="A45" s="1">
         <v>550</v>
       </c>
@@ -6535,7 +6765,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18">
       <c r="A46" s="1">
         <v>560</v>
       </c>
@@ -6587,7 +6817,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18">
       <c r="A47" s="1">
         <v>570</v>
       </c>
@@ -6635,7 +6865,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18">
       <c r="A48" s="1">
         <v>600</v>
       </c>
@@ -6687,7 +6917,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18">
       <c r="A49" s="1">
         <v>610</v>
       </c>
@@ -6737,7 +6967,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18">
       <c r="A50" s="1">
         <v>620</v>
       </c>
@@ -6787,7 +7017,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18">
       <c r="A51" s="1">
         <v>630</v>
       </c>
@@ -6837,7 +7067,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18">
       <c r="A52" s="1">
         <v>631</v>
       </c>
@@ -6887,7 +7117,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18">
       <c r="A53" s="1">
         <v>632</v>
       </c>
@@ -6931,7 +7161,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18">
       <c r="A54" s="1">
         <v>640</v>
       </c>
@@ -6981,7 +7211,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18">
       <c r="A55" s="1">
         <v>650</v>
       </c>
@@ -7031,7 +7261,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18">
       <c r="A56" s="1">
         <v>700</v>
       </c>
@@ -7081,7 +7311,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18">
       <c r="A57" s="1">
         <v>710</v>
       </c>
@@ -7131,7 +7361,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18">
       <c r="A58" s="1">
         <v>720</v>
       </c>
@@ -7181,7 +7411,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18">
       <c r="A59" s="1">
         <v>730</v>
       </c>
@@ -7233,7 +7463,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18">
       <c r="A60" s="1">
         <v>740</v>
       </c>
@@ -7285,7 +7515,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="30">
       <c r="A61" s="1">
         <v>750</v>
       </c>
@@ -7337,7 +7567,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18">
       <c r="A62" s="1">
         <v>800</v>
       </c>
@@ -7387,7 +7617,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18">
       <c r="A63" s="1">
         <v>810</v>
       </c>
@@ -7437,7 +7667,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18">
       <c r="A64" s="1">
         <v>820</v>
       </c>
@@ -7487,7 +7717,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18">
       <c r="A65" s="1">
         <v>830</v>
       </c>
@@ -7537,7 +7767,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18">
       <c r="A66" s="1">
         <v>840</v>
       </c>
@@ -7589,7 +7819,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18">
       <c r="A67" s="1">
         <v>850</v>
       </c>
@@ -7639,7 +7869,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18">
       <c r="A68" s="1">
         <v>860</v>
       </c>
@@ -7689,7 +7919,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18">
       <c r="A69" s="1">
         <v>870</v>
       </c>
@@ -7739,7 +7969,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18">
       <c r="A70" s="1">
         <v>880</v>
       </c>
@@ -7789,7 +8019,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18">
       <c r="A71" s="1">
         <v>890</v>
       </c>
@@ -7839,7 +8069,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18">
       <c r="A72" s="1">
         <v>900</v>
       </c>
@@ -7889,7 +8119,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18">
       <c r="A73" s="1">
         <v>910</v>
       </c>
@@ -7937,7 +8167,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="9" customHeight="1">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -7957,7 +8187,7 @@
       <c r="Q74" s="8"/>
       <c r="R74" s="8"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18">
       <c r="A75" s="1">
         <v>950</v>
       </c>
@@ -8009,7 +8239,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18">
       <c r="A76" s="1">
         <v>952</v>
       </c>
@@ -8059,7 +8289,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18">
       <c r="A77" s="1">
         <v>954</v>
       </c>
@@ -8111,7 +8341,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18">
       <c r="A78" s="1">
         <v>958</v>
       </c>
@@ -8163,7 +8393,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18">
       <c r="A79" s="1">
         <v>959</v>
       </c>
@@ -8215,7 +8445,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18">
       <c r="A80" s="1">
         <v>960</v>
       </c>
@@ -8267,7 +8497,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18">
       <c r="A81" s="1">
         <v>962</v>
       </c>
@@ -8319,7 +8549,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18">
       <c r="A82" s="1">
         <v>964</v>
       </c>
@@ -8371,7 +8601,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18">
       <c r="A83" s="1">
         <v>966</v>
       </c>
@@ -8423,7 +8653,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18">
       <c r="A84" s="1">
         <v>968</v>
       </c>
@@ -8475,7 +8705,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18">
       <c r="A85" s="1">
         <v>970</v>
       </c>
@@ -8527,7 +8757,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18">
       <c r="A86" s="1">
         <v>972</v>
       </c>
@@ -8579,7 +8809,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18">
       <c r="A87" s="1">
         <v>974</v>
       </c>
@@ -8631,7 +8861,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18">
       <c r="A88" s="1">
         <v>976</v>
       </c>
@@ -8681,7 +8911,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -8701,7 +8931,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18">
       <c r="A90" s="1">
         <v>1005</v>
       </c>
@@ -8751,7 +8981,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18">
       <c r="A91" s="1">
         <v>1010</v>
       </c>
@@ -8803,7 +9033,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18">
       <c r="A92" s="1">
         <v>1020</v>
       </c>
@@ -8853,7 +9083,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18">
       <c r="A93" s="1">
         <v>1030</v>
       </c>
@@ -8903,7 +9133,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18">
       <c r="A94" s="1">
         <v>1040</v>
       </c>
@@ -8953,7 +9183,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18">
       <c r="A95" s="1">
         <v>1050</v>
       </c>
@@ -9003,7 +9233,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18">
       <c r="A96" s="1">
         <v>1060</v>
       </c>
@@ -9053,7 +9283,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18">
       <c r="A97" s="1">
         <v>1061</v>
       </c>
@@ -9101,7 +9331,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18">
       <c r="A98" s="1">
         <v>1070</v>
       </c>
@@ -9151,7 +9381,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18">
       <c r="A99" s="1">
         <v>1080</v>
       </c>
@@ -9201,7 +9431,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18">
       <c r="A100" s="1">
         <v>1099</v>
       </c>
@@ -9253,7 +9483,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18">
       <c r="A101" s="1">
         <v>1100</v>
       </c>
@@ -9303,7 +9533,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18">
       <c r="A102" s="1">
         <v>1101</v>
       </c>
@@ -9353,7 +9583,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18">
       <c r="A103" s="1">
         <v>1102</v>
       </c>
@@ -9403,7 +9633,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18">
       <c r="A104" s="1">
         <v>1103</v>
       </c>
@@ -9453,7 +9683,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18">
       <c r="A105" s="1">
         <v>1104</v>
       </c>
@@ -9503,7 +9733,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18">
       <c r="A106" s="1">
         <v>1105</v>
       </c>
@@ -9553,7 +9783,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18">
       <c r="A107" s="1">
         <v>1106</v>
       </c>
@@ -9603,7 +9833,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18">
       <c r="A108" s="1">
         <v>1107</v>
       </c>
@@ -9653,7 +9883,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18">
       <c r="A109" s="1">
         <v>1108</v>
       </c>
@@ -9703,7 +9933,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18">
       <c r="A110" s="1">
         <v>1110</v>
       </c>
@@ -9753,7 +9983,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18">
       <c r="A111" s="1">
         <v>1120</v>
       </c>
@@ -9803,7 +10033,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18">
       <c r="A112" s="1">
         <v>1130</v>
       </c>
@@ -9853,7 +10083,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18">
       <c r="A113" s="1">
         <v>1140</v>
       </c>
@@ -9901,7 +10131,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18">
       <c r="A114" s="1">
         <v>1200</v>
       </c>
@@ -9951,7 +10181,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18">
       <c r="A115" s="1">
         <v>1210</v>
       </c>
@@ -10001,7 +10231,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18">
       <c r="A116" s="1">
         <v>1220</v>
       </c>
@@ -10049,7 +10279,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18">
       <c r="A117" s="1">
         <v>1300</v>
       </c>
@@ -10099,7 +10329,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18">
       <c r="A118" s="1">
         <v>1310</v>
       </c>
@@ -10149,7 +10379,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18">
       <c r="A119" s="1">
         <v>1320</v>
       </c>
@@ -10199,7 +10429,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18">
       <c r="A120" s="1">
         <v>1330</v>
       </c>
@@ -10247,7 +10477,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="9" customHeight="1">
       <c r="A121" s="8"/>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
@@ -10267,7 +10497,7 @@
       <c r="Q121" s="8"/>
       <c r="R121" s="8"/>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18">
       <c r="A122" s="1">
         <v>1400</v>
       </c>
@@ -10319,7 +10549,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18">
       <c r="A123" s="1">
         <v>1410</v>
       </c>
@@ -10369,7 +10599,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18">
       <c r="A124" s="1">
         <v>1420</v>
       </c>
@@ -10421,7 +10651,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18">
       <c r="A125" s="1">
         <v>1430</v>
       </c>
@@ -10471,7 +10701,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18">
       <c r="A126" s="1">
         <v>1440</v>
       </c>
@@ -10511,7 +10741,7 @@
       </c>
       <c r="N126" s="1"/>
       <c r="O126" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P126" s="1" t="s">
         <v>47</v>
@@ -10523,7 +10753,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18">
       <c r="A127" s="1">
         <v>1450</v>
       </c>
@@ -10575,7 +10805,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18">
       <c r="A128" s="1">
         <v>1460</v>
       </c>
@@ -10621,11 +10851,11 @@
         <v>48</v>
       </c>
       <c r="Q128" s="1"/>
-      <c r="R128" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R128" s="41" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18">
       <c r="A129" s="1">
         <v>1470</v>
       </c>
@@ -10671,11 +10901,11 @@
         <v>48</v>
       </c>
       <c r="Q129" s="1"/>
-      <c r="R129" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R129" s="41" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18">
       <c r="A130" s="1">
         <v>1480</v>
       </c>
@@ -10719,11 +10949,11 @@
         <v>48</v>
       </c>
       <c r="Q130" s="1"/>
-      <c r="R130" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R130" s="41" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18">
       <c r="A131" s="1">
         <v>1490</v>
       </c>
@@ -10771,7 +11001,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18">
       <c r="A132" s="1">
         <v>1500</v>
       </c>
@@ -10819,7 +11049,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="9" customHeight="1">
       <c r="A133" s="8"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
@@ -10839,7 +11069,7 @@
       <c r="Q133" s="8"/>
       <c r="R133" s="8"/>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18">
       <c r="A134" s="1">
         <v>1600</v>
       </c>
@@ -10889,7 +11119,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18">
       <c r="A135" s="1">
         <v>1610</v>
       </c>
@@ -10937,7 +11167,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="30">
       <c r="A136" s="1">
         <v>1620</v>
       </c>
@@ -10987,7 +11217,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="9" customHeight="1">
       <c r="A137" s="8"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -11007,7 +11237,7 @@
       <c r="Q137" s="8"/>
       <c r="R137" s="8"/>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18">
       <c r="A138" s="1">
         <v>1700</v>
       </c>
@@ -11057,7 +11287,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18">
       <c r="A139" s="1">
         <v>1710</v>
       </c>
@@ -11107,7 +11337,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18">
       <c r="A140" s="1">
         <v>1800</v>
       </c>
@@ -11202,9 +11432,61 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56B137B-25C1-4EDC-B1AE-C1492D65B63B}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.375" style="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.625" style="37" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.75" style="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="38" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B1" s="38" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>944</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="39" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K116"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -11219,7 +11501,7 @@
     <col min="11" max="11" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
@@ -11254,7 +11536,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>416</v>
       </c>
@@ -11285,7 +11567,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>416</v>
       </c>
@@ -11314,7 +11596,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="30">
       <c r="A4" s="1" t="s">
         <v>416</v>
       </c>
@@ -11343,7 +11625,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>416</v>
       </c>
@@ -11372,7 +11654,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>416</v>
       </c>
@@ -11401,7 +11683,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>416</v>
       </c>
@@ -11430,7 +11712,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>416</v>
       </c>
@@ -11459,7 +11741,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
         <v>416</v>
       </c>
@@ -11488,7 +11770,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>416</v>
       </c>
@@ -11517,7 +11799,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>416</v>
       </c>
@@ -11546,7 +11828,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -11559,7 +11841,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>89</v>
       </c>
@@ -11588,7 +11870,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
         <v>89</v>
       </c>
@@ -11619,7 +11901,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
         <v>89</v>
       </c>
@@ -11650,7 +11932,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>89</v>
       </c>
@@ -11681,7 +11963,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
         <v>89</v>
       </c>
@@ -11710,7 +11992,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>89</v>
       </c>
@@ -11739,7 +12021,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>89</v>
       </c>
@@ -11768,7 +12050,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
         <v>89</v>
       </c>
@@ -11797,7 +12079,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -11810,7 +12092,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
         <v>94</v>
       </c>
@@ -11839,7 +12121,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
         <v>94</v>
       </c>
@@ -11870,7 +12152,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
         <v>94</v>
       </c>
@@ -11901,7 +12183,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
         <v>94</v>
       </c>
@@ -11930,7 +12212,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
         <v>94</v>
       </c>
@@ -11959,7 +12241,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
         <v>94</v>
       </c>
@@ -11988,7 +12270,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
         <v>94</v>
       </c>
@@ -12017,7 +12299,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -12030,7 +12312,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
         <v>177</v>
       </c>
@@ -12059,7 +12341,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
         <v>177</v>
       </c>
@@ -12088,7 +12370,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
         <v>177</v>
       </c>
@@ -12117,7 +12399,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
         <v>177</v>
       </c>
@@ -12148,7 +12430,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
         <v>177</v>
       </c>
@@ -12177,7 +12459,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -12190,7 +12472,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11">
       <c r="A36" s="1" t="s">
         <v>197</v>
       </c>
@@ -12221,7 +12503,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
         <v>197</v>
       </c>
@@ -12250,7 +12532,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11">
       <c r="A38" s="1" t="s">
         <v>197</v>
       </c>
@@ -12279,7 +12561,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11">
       <c r="A39" s="1" t="s">
         <v>197</v>
       </c>
@@ -12308,7 +12590,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
         <v>197</v>
       </c>
@@ -12337,7 +12619,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11">
       <c r="A41" s="1" t="s">
         <v>197</v>
       </c>
@@ -12366,7 +12648,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11">
       <c r="A42" s="1" t="s">
         <v>197</v>
       </c>
@@ -12395,7 +12677,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -12408,7 +12690,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11">
       <c r="A44" s="1" t="s">
         <v>200</v>
       </c>
@@ -12437,7 +12719,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11">
       <c r="A45" s="1" t="s">
         <v>200</v>
       </c>
@@ -12466,7 +12748,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
         <v>200</v>
       </c>
@@ -12495,7 +12777,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
         <v>200</v>
       </c>
@@ -12524,7 +12806,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -12537,7 +12819,7 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
         <v>304</v>
       </c>
@@ -12566,7 +12848,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11">
       <c r="A50" s="1" t="s">
         <v>304</v>
       </c>
@@ -12595,7 +12877,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11">
       <c r="A51" s="1" t="s">
         <v>304</v>
       </c>
@@ -12626,7 +12908,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11">
       <c r="A52" s="1" t="s">
         <v>304</v>
       </c>
@@ -12655,7 +12937,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11">
       <c r="A53" s="1" t="s">
         <v>304</v>
       </c>
@@ -12684,7 +12966,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -12697,7 +12979,7 @@
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11">
       <c r="A55" s="1" t="s">
         <v>338</v>
       </c>
@@ -12726,7 +13008,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11">
       <c r="A56" s="1" t="s">
         <v>338</v>
       </c>
@@ -12757,7 +13039,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11">
       <c r="A57" s="1" t="s">
         <v>338</v>
       </c>
@@ -12786,7 +13068,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11">
       <c r="A58" s="1" t="s">
         <v>338</v>
       </c>
@@ -12815,7 +13097,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11">
       <c r="A59" s="1" t="s">
         <v>338</v>
       </c>
@@ -12844,7 +13126,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -12857,7 +13139,7 @@
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11">
       <c r="A61" s="1" t="s">
         <v>361</v>
       </c>
@@ -12886,7 +13168,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11">
       <c r="A62" s="1" t="s">
         <v>361</v>
       </c>
@@ -12915,7 +13197,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11">
       <c r="A63" s="1" t="s">
         <v>361</v>
       </c>
@@ -12944,7 +13226,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11">
       <c r="A64" s="1" t="s">
         <v>361</v>
       </c>
@@ -12973,7 +13255,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -12986,7 +13268,7 @@
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11">
       <c r="A66" s="1" t="s">
         <v>367</v>
       </c>
@@ -13015,7 +13297,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11">
       <c r="A67" s="1" t="s">
         <v>367</v>
       </c>
@@ -13044,7 +13326,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11">
       <c r="A68" s="1" t="s">
         <v>367</v>
       </c>
@@ -13073,7 +13355,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -13086,7 +13368,7 @@
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11">
       <c r="A70" s="1" t="s">
         <v>258</v>
       </c>
@@ -13115,7 +13397,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11">
       <c r="A71" s="1" t="s">
         <v>258</v>
       </c>
@@ -13144,7 +13426,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11">
       <c r="A72" s="1" t="s">
         <v>258</v>
       </c>
@@ -13173,7 +13455,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11">
       <c r="A73" s="1" t="s">
         <v>258</v>
       </c>
@@ -13202,7 +13484,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -13215,7 +13497,7 @@
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11">
       <c r="A75" s="1" t="s">
         <v>240</v>
       </c>
@@ -13244,7 +13526,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11">
       <c r="A76" s="1" t="s">
         <v>240</v>
       </c>
@@ -13275,7 +13557,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11">
       <c r="A77" s="1" t="s">
         <v>240</v>
       </c>
@@ -13304,7 +13586,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11">
       <c r="A78" s="1" t="s">
         <v>240</v>
       </c>
@@ -13333,7 +13615,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11">
       <c r="A79" s="1" t="s">
         <v>240</v>
       </c>
@@ -13362,7 +13644,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -13375,7 +13657,7 @@
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11">
       <c r="A81" s="1" t="s">
         <v>236</v>
       </c>
@@ -13404,7 +13686,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11">
       <c r="A82" s="1" t="s">
         <v>236</v>
       </c>
@@ -13435,7 +13717,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11">
       <c r="A83" s="1" t="s">
         <v>236</v>
       </c>
@@ -13464,7 +13746,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11">
       <c r="A84" s="1" t="s">
         <v>236</v>
       </c>
@@ -13493,7 +13775,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -13506,7 +13788,7 @@
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
     </row>
-    <row r="86" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" ht="30">
       <c r="A86" s="1" t="s">
         <v>243</v>
       </c>
@@ -13537,7 +13819,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" ht="30">
       <c r="A87" s="1" t="s">
         <v>243</v>
       </c>
@@ -13566,7 +13848,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" ht="30">
       <c r="A88" s="1" t="s">
         <v>243</v>
       </c>
@@ -13595,7 +13877,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" ht="30">
       <c r="A89" s="1" t="s">
         <v>243</v>
       </c>
@@ -13626,7 +13908,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" ht="30">
       <c r="A90" s="1" t="s">
         <v>243</v>
       </c>
@@ -13655,7 +13937,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -13668,7 +13950,7 @@
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11">
       <c r="A92" s="1" t="s">
         <v>140</v>
       </c>
@@ -13697,7 +13979,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11">
       <c r="A93" s="1" t="s">
         <v>140</v>
       </c>
@@ -13728,7 +14010,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11">
       <c r="A94" s="1" t="s">
         <v>140</v>
       </c>
@@ -13757,7 +14039,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -13770,7 +14052,7 @@
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
         <v>144</v>
       </c>
@@ -13799,7 +14081,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
         <v>144</v>
       </c>
@@ -13828,7 +14110,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11">
       <c r="A98" s="1" t="s">
         <v>144</v>
       </c>
@@ -13857,7 +14139,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -13870,7 +14152,7 @@
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11">
       <c r="A100" s="1" t="s">
         <v>154</v>
       </c>
@@ -13899,7 +14181,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11">
       <c r="A101" s="1" t="s">
         <v>154</v>
       </c>
@@ -13928,7 +14210,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11">
       <c r="A102" s="1" t="s">
         <v>154</v>
       </c>
@@ -13957,7 +14239,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11">
       <c r="A103" s="1" t="s">
         <v>154</v>
       </c>
@@ -13986,7 +14268,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -13999,7 +14281,7 @@
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11">
       <c r="A105" s="1" t="s">
         <v>194</v>
       </c>
@@ -14028,7 +14310,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11">
       <c r="A106" s="1" t="s">
         <v>194</v>
       </c>
@@ -14059,7 +14341,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11">
       <c r="A107" s="1" t="s">
         <v>194</v>
       </c>
@@ -14088,7 +14370,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -14101,7 +14383,7 @@
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11">
       <c r="A109" s="1" t="s">
         <v>373</v>
       </c>
@@ -14130,7 +14412,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11">
       <c r="A110" s="1" t="s">
         <v>373</v>
       </c>
@@ -14159,7 +14441,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11">
       <c r="A111" s="1" t="s">
         <v>373</v>
       </c>
@@ -14188,7 +14470,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11">
       <c r="A112" s="1" t="s">
         <v>373</v>
       </c>
@@ -14217,7 +14499,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11">
       <c r="A113" s="1" t="s">
         <v>377</v>
       </c>
@@ -14246,7 +14528,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11">
       <c r="A114" s="1" t="s">
         <v>377</v>
       </c>
@@ -14275,7 +14557,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11">
       <c r="A115" s="1" t="s">
         <v>377</v>
       </c>
@@ -14304,7 +14586,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11">
       <c r="A116" s="1" t="s">
         <v>377</v>
       </c>
@@ -14357,15 +14639,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:BR2352"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="70" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70">
       <c r="A1" s="5" t="s">
         <v>55</v>
       </c>
@@ -14577,7 +14859,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:70">
       <c r="A2" t="s">
         <v>609</v>
       </c>
@@ -14789,7 +15071,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:70">
       <c r="A3" t="s">
         <v>658</v>
       </c>
@@ -15001,7 +15283,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:70">
       <c r="A4" t="s">
         <v>665</v>
       </c>
@@ -15210,7 +15492,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:70">
       <c r="A5" t="s">
         <v>387</v>
       </c>
@@ -15401,7 +15683,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:70">
       <c r="B6" t="s">
         <v>813</v>
       </c>
@@ -15577,7 +15859,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:70">
       <c r="B7" t="s">
         <v>846</v>
       </c>
@@ -15720,7 +16002,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:70">
       <c r="B8" t="s">
         <v>873</v>
       </c>
@@ -15830,7 +16112,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:70">
       <c r="B9" t="s">
         <v>889</v>
       </c>
@@ -15904,7 +16186,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="10" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:70">
       <c r="E10" t="s">
         <v>900</v>
       </c>
@@ -15957,7 +16239,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="11" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:70">
       <c r="E11" t="s">
         <v>387</v>
       </c>
@@ -15983,7 +16265,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="12" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:70">
       <c r="K12" t="s">
         <v>387</v>
       </c>
@@ -15994,7 +16276,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="13" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:70">
       <c r="U13" t="s">
         <v>906</v>
       </c>
@@ -16002,7 +16284,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="14" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:70">
       <c r="U14" t="s">
         <v>387</v>
       </c>
@@ -16010,1784 +16292,1791 @@
         <v>258</v>
       </c>
     </row>
-    <row r="15" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:70">
       <c r="BB15" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="1508" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="16" spans="54:54">
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>Street Scene</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508" spans="60:60">
       <c r="BH1508" s="12"/>
     </row>
-    <row r="1509" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1509" spans="60:60">
       <c r="BH1509" s="12"/>
     </row>
-    <row r="1510" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1510" spans="60:60">
       <c r="BH1510" s="12"/>
     </row>
-    <row r="1511" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1511" spans="60:60">
       <c r="BH1511" s="12"/>
     </row>
-    <row r="1512" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1512" spans="60:60">
       <c r="BH1512" s="12"/>
     </row>
-    <row r="1513" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1513" spans="60:60">
       <c r="BH1513" s="12"/>
     </row>
-    <row r="1514" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1514" spans="60:60">
       <c r="BH1514" s="12"/>
     </row>
-    <row r="1515" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1515" spans="60:60">
       <c r="BH1515" s="12"/>
     </row>
-    <row r="1516" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1516" spans="60:60">
       <c r="BH1516" s="12"/>
     </row>
-    <row r="1517" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1517" spans="60:60">
       <c r="BH1517" s="12"/>
     </row>
-    <row r="1518" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1518" spans="60:60">
       <c r="BH1518" s="12"/>
     </row>
-    <row r="1519" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1519" spans="60:60">
       <c r="BH1519" s="12"/>
     </row>
-    <row r="1520" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1520" spans="60:60">
       <c r="BH1520" s="12"/>
     </row>
-    <row r="1521" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1521" spans="60:60">
       <c r="BH1521" s="12"/>
     </row>
-    <row r="1522" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1522" spans="60:60">
       <c r="BH1522" s="12"/>
     </row>
-    <row r="1523" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1523" spans="60:60">
       <c r="BH1523" s="12"/>
     </row>
-    <row r="1524" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1524" spans="60:60">
       <c r="BH1524" s="12"/>
     </row>
-    <row r="1525" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1525" spans="60:60">
       <c r="BH1525" s="12"/>
     </row>
-    <row r="1526" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1526" spans="60:60">
       <c r="BH1526" s="12"/>
     </row>
-    <row r="1527" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1527" spans="60:60">
       <c r="BH1527" s="12"/>
     </row>
-    <row r="1528" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1528" spans="60:60">
       <c r="BH1528" s="12"/>
     </row>
-    <row r="1529" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1529" spans="60:60">
       <c r="BH1529" s="12"/>
     </row>
-    <row r="1530" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1530" spans="60:60">
       <c r="BH1530" s="12"/>
     </row>
-    <row r="1531" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1531" spans="60:60">
       <c r="BH1531" s="12"/>
     </row>
-    <row r="1532" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1532" spans="60:60">
       <c r="BH1532" s="12"/>
     </row>
-    <row r="1533" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1533" spans="60:60">
       <c r="BH1533" s="12"/>
     </row>
-    <row r="1534" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1534" spans="60:60">
       <c r="BH1534" s="12"/>
     </row>
-    <row r="1535" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1535" spans="60:60">
       <c r="BH1535" s="12"/>
     </row>
-    <row r="1536" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1536" spans="60:60">
       <c r="BH1536" s="12"/>
     </row>
-    <row r="1537" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1537" spans="60:60">
       <c r="BH1537" s="12"/>
     </row>
-    <row r="1538" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1538" spans="60:60">
       <c r="BH1538" s="12"/>
     </row>
-    <row r="1539" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1539" spans="60:60">
       <c r="BH1539" s="12"/>
     </row>
-    <row r="1540" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1540" spans="60:60">
       <c r="BH1540" s="12"/>
     </row>
-    <row r="1541" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1541" spans="60:60">
       <c r="BH1541" s="12"/>
     </row>
-    <row r="1542" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1542" spans="60:60">
       <c r="BH1542" s="12"/>
     </row>
-    <row r="1543" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1543" spans="60:60">
       <c r="BH1543" s="12"/>
     </row>
-    <row r="1544" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1544" spans="60:60">
       <c r="BH1544" s="12"/>
     </row>
-    <row r="1545" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1545" spans="60:60">
       <c r="BH1545" s="12"/>
     </row>
-    <row r="1546" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1546" spans="60:60">
       <c r="BH1546" s="12"/>
     </row>
-    <row r="1547" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1547" spans="60:60">
       <c r="BH1547" s="12"/>
     </row>
-    <row r="1548" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1548" spans="60:60">
       <c r="BH1548" s="12"/>
     </row>
-    <row r="1549" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1549" spans="60:60">
       <c r="BH1549" s="12"/>
     </row>
-    <row r="1550" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1550" spans="60:60">
       <c r="BH1550" s="12"/>
     </row>
-    <row r="1551" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1551" spans="60:60">
       <c r="BH1551" s="12"/>
     </row>
-    <row r="1552" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1552" spans="60:60">
       <c r="BH1552" s="12"/>
     </row>
-    <row r="1553" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1553" spans="60:60">
       <c r="BH1553" s="12"/>
     </row>
-    <row r="1554" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1554" spans="60:60">
       <c r="BH1554" s="12"/>
     </row>
-    <row r="1555" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1555" spans="60:60">
       <c r="BH1555" s="12"/>
     </row>
-    <row r="1556" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1556" spans="60:60">
       <c r="BH1556" s="12"/>
     </row>
-    <row r="1557" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1557" spans="60:60">
       <c r="BH1557" s="12"/>
     </row>
-    <row r="1558" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1558" spans="60:60">
       <c r="BH1558" s="12"/>
     </row>
-    <row r="1559" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1559" spans="60:60">
       <c r="BH1559" s="12"/>
     </row>
-    <row r="1560" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1560" spans="60:60">
       <c r="BH1560" s="12"/>
     </row>
-    <row r="1561" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1561" spans="60:60">
       <c r="BH1561" s="12"/>
     </row>
-    <row r="1562" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1562" spans="60:60">
       <c r="BH1562" s="12"/>
     </row>
-    <row r="1563" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1563" spans="60:60">
       <c r="BH1563" s="12"/>
     </row>
-    <row r="1564" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1564" spans="60:60">
       <c r="BH1564" s="12"/>
     </row>
-    <row r="1565" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1565" spans="60:60">
       <c r="BH1565" s="12"/>
     </row>
-    <row r="1566" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1566" spans="60:60">
       <c r="BH1566" s="12"/>
     </row>
-    <row r="1567" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1567" spans="60:60">
       <c r="BH1567" s="12"/>
     </row>
-    <row r="1568" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1568" spans="60:60">
       <c r="BH1568" s="12"/>
     </row>
-    <row r="1569" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1569" spans="60:60">
       <c r="BH1569" s="12"/>
     </row>
-    <row r="1570" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1570" spans="60:60">
       <c r="BH1570" s="12"/>
     </row>
-    <row r="1571" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1571" spans="60:60">
       <c r="BH1571" s="12"/>
     </row>
-    <row r="1572" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1572" spans="60:60">
       <c r="BH1572" s="12"/>
     </row>
-    <row r="1573" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1573" spans="60:60" ht="17.25">
       <c r="BH1573" s="13" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="1574" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1574" spans="60:60" ht="17.25">
       <c r="BH1574" s="24"/>
     </row>
-    <row r="1575" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1575" spans="60:60">
       <c r="BH1575" s="12"/>
     </row>
-    <row r="1576" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1576" spans="60:60">
       <c r="BH1576" s="12"/>
     </row>
-    <row r="1577" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1577" spans="60:60">
       <c r="BH1577" s="12"/>
     </row>
-    <row r="1578" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1578" spans="60:60">
       <c r="BH1578" s="12"/>
     </row>
-    <row r="1579" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1579" spans="60:60">
       <c r="BH1579" s="12"/>
     </row>
-    <row r="1580" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1580" spans="60:60">
       <c r="BH1580" s="12"/>
     </row>
-    <row r="1581" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1581" spans="60:60">
       <c r="BH1581" s="12"/>
     </row>
-    <row r="1582" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1582" spans="60:60">
       <c r="BH1582" s="12"/>
     </row>
-    <row r="1583" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1583" spans="60:60">
       <c r="BH1583" s="12"/>
     </row>
-    <row r="1584" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1584" spans="60:60">
       <c r="BH1584" s="12"/>
     </row>
-    <row r="1585" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1585" spans="60:60">
       <c r="BH1585" s="12"/>
     </row>
-    <row r="1586" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1586" spans="60:60">
       <c r="BH1586" s="12"/>
     </row>
-    <row r="1587" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1587" spans="60:60">
       <c r="BH1587" s="12"/>
     </row>
-    <row r="1588" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1588" spans="60:60">
       <c r="BH1588" s="12"/>
     </row>
-    <row r="1589" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1589" spans="60:60">
       <c r="BH1589" s="12"/>
     </row>
-    <row r="1590" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1590" spans="60:60">
       <c r="BH1590" s="12"/>
     </row>
-    <row r="1591" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1591" spans="60:60">
       <c r="BH1591" s="12"/>
     </row>
-    <row r="1592" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1592" spans="60:60">
       <c r="BH1592" s="12"/>
     </row>
-    <row r="1593" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1593" spans="60:60">
       <c r="BH1593" s="12"/>
     </row>
-    <row r="1594" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1594" spans="60:60">
       <c r="BH1594" s="12"/>
     </row>
-    <row r="1595" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1595" spans="60:60">
       <c r="BH1595" s="12"/>
     </row>
-    <row r="1596" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1596" spans="60:60">
       <c r="BH1596" s="12"/>
     </row>
-    <row r="1597" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1597" spans="60:60">
       <c r="BH1597" s="12"/>
     </row>
-    <row r="1598" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1598" spans="60:60">
       <c r="BH1598" s="12"/>
     </row>
-    <row r="1599" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1599" spans="60:60">
       <c r="BH1599" s="12"/>
     </row>
-    <row r="1600" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1600" spans="60:60">
       <c r="BH1600" s="12"/>
     </row>
-    <row r="1601" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1601" spans="60:60">
       <c r="BH1601" s="12"/>
     </row>
-    <row r="1602" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1602" spans="60:60">
       <c r="BH1602" s="12"/>
     </row>
-    <row r="1603" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1603" spans="60:60">
       <c r="BH1603" s="12"/>
     </row>
-    <row r="1604" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1604" spans="60:60">
       <c r="BH1604" s="12"/>
     </row>
-    <row r="1605" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1605" spans="60:60">
       <c r="BH1605" s="12"/>
     </row>
-    <row r="1606" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1606" spans="60:60">
       <c r="BH1606" s="12"/>
     </row>
-    <row r="1607" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1607" spans="60:60">
       <c r="BH1607" s="12"/>
     </row>
-    <row r="1608" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1608" spans="60:60">
       <c r="BH1608" s="12"/>
     </row>
-    <row r="1609" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1609" spans="60:60">
       <c r="BH1609" s="12"/>
     </row>
-    <row r="1610" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1610" spans="60:60">
       <c r="BH1610" s="12"/>
     </row>
-    <row r="1611" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1611" spans="60:60">
       <c r="BH1611" s="12"/>
     </row>
-    <row r="1612" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1612" spans="60:60">
       <c r="BH1612" s="12"/>
     </row>
-    <row r="1613" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1613" spans="60:60">
       <c r="BH1613" s="12"/>
     </row>
-    <row r="1614" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1614" spans="60:60">
       <c r="BH1614" s="12"/>
     </row>
-    <row r="1615" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1615" spans="60:60">
       <c r="BH1615" s="12"/>
     </row>
-    <row r="1616" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1616" spans="60:60">
       <c r="BH1616" s="12"/>
     </row>
-    <row r="1617" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1617" spans="60:60">
       <c r="BH1617" s="12"/>
     </row>
-    <row r="1618" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1618" spans="60:60">
       <c r="BH1618" s="12"/>
     </row>
-    <row r="1619" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1619" spans="60:60">
       <c r="BH1619" s="12"/>
     </row>
-    <row r="1620" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1620" spans="60:60">
       <c r="BH1620" s="12"/>
     </row>
-    <row r="1621" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1621" spans="60:60">
       <c r="BH1621" s="12"/>
     </row>
-    <row r="1622" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1622" spans="60:60">
       <c r="BH1622" s="12"/>
     </row>
-    <row r="1623" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1623" spans="60:60">
       <c r="BH1623" s="12"/>
     </row>
-    <row r="1624" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1624" spans="60:60">
       <c r="BH1624" s="12"/>
     </row>
-    <row r="1625" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1625" spans="60:60">
       <c r="BH1625" s="12"/>
     </row>
-    <row r="1626" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1626" spans="60:60">
       <c r="BH1626" s="12"/>
     </row>
-    <row r="1627" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1627" spans="60:60">
       <c r="BH1627" s="12"/>
     </row>
-    <row r="1628" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1628" spans="60:60">
       <c r="BH1628" s="12"/>
     </row>
-    <row r="1629" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1629" spans="60:60">
       <c r="BH1629" s="12"/>
     </row>
-    <row r="1630" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1630" spans="60:60">
       <c r="BH1630" s="12"/>
     </row>
-    <row r="1631" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1631" spans="60:60">
       <c r="BH1631" s="12"/>
     </row>
-    <row r="1632" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1632" spans="60:60">
       <c r="BH1632" s="12"/>
     </row>
-    <row r="1633" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1633" spans="60:60">
       <c r="BH1633" s="12"/>
     </row>
-    <row r="1634" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1634" spans="60:60">
       <c r="BH1634" s="12"/>
     </row>
-    <row r="1635" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1635" spans="60:60">
       <c r="BH1635" s="12"/>
     </row>
-    <row r="1636" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1636" spans="60:60">
       <c r="BH1636" s="12"/>
     </row>
-    <row r="1637" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1637" spans="60:60">
       <c r="BH1637" s="12"/>
     </row>
-    <row r="1638" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1638" spans="60:60">
       <c r="BH1638" s="12"/>
     </row>
-    <row r="1639" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1639" spans="60:60">
       <c r="BH1639" s="12"/>
     </row>
-    <row r="1640" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1640" spans="60:60">
       <c r="BH1640" s="12"/>
     </row>
-    <row r="1641" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1641" spans="60:60">
       <c r="BH1641" s="12"/>
     </row>
-    <row r="1642" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1642" spans="60:60">
       <c r="BH1642" s="12"/>
     </row>
-    <row r="1643" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1643" spans="60:60">
       <c r="BH1643" s="12"/>
     </row>
-    <row r="1644" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1644" spans="60:60">
       <c r="BH1644" s="12"/>
     </row>
-    <row r="1645" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1645" spans="60:60">
       <c r="BH1645" s="12"/>
     </row>
-    <row r="1646" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1646" spans="60:60">
       <c r="BH1646" s="12"/>
     </row>
-    <row r="1647" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1647" spans="60:60">
       <c r="BH1647" s="12"/>
     </row>
-    <row r="1648" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1648" spans="60:60">
       <c r="BH1648" s="12"/>
     </row>
-    <row r="1649" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1649" spans="60:60">
       <c r="BH1649" s="12"/>
     </row>
-    <row r="1650" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1650" spans="60:60">
       <c r="BH1650" s="12"/>
     </row>
-    <row r="1651" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1651" spans="60:60">
       <c r="BH1651" s="12"/>
     </row>
-    <row r="1652" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1652" spans="60:60">
       <c r="BH1652" s="12"/>
     </row>
-    <row r="1653" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1653" spans="60:60">
       <c r="BH1653" s="12"/>
     </row>
-    <row r="1654" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1654" spans="60:60">
       <c r="BH1654" s="12"/>
     </row>
-    <row r="1655" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1655" spans="60:60">
       <c r="BH1655" s="12"/>
     </row>
-    <row r="1656" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1656" spans="60:60">
       <c r="BH1656" s="12"/>
     </row>
-    <row r="1657" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1657" spans="60:60">
       <c r="BH1657" s="12"/>
     </row>
-    <row r="1658" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1658" spans="60:60">
       <c r="BH1658" s="12"/>
     </row>
-    <row r="1659" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1659" spans="60:60">
       <c r="BH1659" s="12"/>
     </row>
-    <row r="1660" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1660" spans="60:60">
       <c r="BH1660" s="12"/>
     </row>
-    <row r="1661" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1661" spans="60:60" ht="17.25">
       <c r="BH1661" s="24"/>
     </row>
-    <row r="1662" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1662" spans="60:60" ht="17.25">
       <c r="BH1662" s="24"/>
     </row>
-    <row r="1663" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1663" spans="60:60">
       <c r="BH1663" s="12"/>
     </row>
-    <row r="1664" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1664" spans="60:60">
       <c r="BH1664" s="12"/>
     </row>
-    <row r="1665" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1665" spans="60:60">
       <c r="BH1665" s="12"/>
     </row>
-    <row r="1666" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1666" spans="60:60">
       <c r="BH1666" s="12"/>
     </row>
-    <row r="1667" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1667" spans="60:60">
       <c r="BH1667" s="12"/>
     </row>
-    <row r="1668" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1668" spans="60:60">
       <c r="BH1668" s="12"/>
     </row>
-    <row r="1669" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1669" spans="60:60">
       <c r="BH1669" s="12"/>
     </row>
-    <row r="1670" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1670" spans="60:60">
       <c r="BH1670" s="12"/>
     </row>
-    <row r="1671" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1671" spans="60:60">
       <c r="BH1671" s="12"/>
     </row>
-    <row r="1672" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1672" spans="60:60">
       <c r="BH1672" s="12"/>
     </row>
-    <row r="1673" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1673" spans="60:60">
       <c r="BH1673" s="12"/>
     </row>
-    <row r="1674" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1674" spans="60:60">
       <c r="BH1674" s="12"/>
     </row>
-    <row r="1675" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1675" spans="60:60">
       <c r="BH1675" s="12"/>
     </row>
-    <row r="1676" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1676" spans="60:60">
       <c r="BH1676" s="12"/>
     </row>
-    <row r="1677" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1677" spans="60:60">
       <c r="BH1677" s="12"/>
     </row>
-    <row r="1678" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1678" spans="60:60">
       <c r="BH1678" s="12"/>
     </row>
-    <row r="1679" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1679" spans="60:60">
       <c r="BH1679" s="12"/>
     </row>
-    <row r="1680" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1680" spans="60:60">
       <c r="BH1680" s="12"/>
     </row>
-    <row r="1681" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1681" spans="60:60">
       <c r="BH1681" s="12"/>
     </row>
-    <row r="1682" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1682" spans="60:60">
       <c r="BH1682" s="12"/>
     </row>
-    <row r="1683" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1683" spans="60:60">
       <c r="BH1683" s="12"/>
     </row>
-    <row r="1684" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1684" spans="60:60">
       <c r="BH1684" s="12"/>
     </row>
-    <row r="1685" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1685" spans="60:60">
       <c r="BH1685" s="12"/>
     </row>
-    <row r="1686" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1686" spans="60:60">
       <c r="BH1686" s="12"/>
     </row>
-    <row r="1687" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1687" spans="60:60">
       <c r="BH1687" s="12"/>
     </row>
-    <row r="1688" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1688" spans="60:60">
       <c r="BH1688" s="12"/>
     </row>
-    <row r="1689" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1689" spans="60:60">
       <c r="BH1689" s="12"/>
     </row>
-    <row r="1690" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1690" spans="60:60">
       <c r="BH1690" s="12"/>
     </row>
-    <row r="1691" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1691" spans="60:60">
       <c r="BH1691" s="12"/>
     </row>
-    <row r="1692" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1692" spans="60:60">
       <c r="BH1692" s="12"/>
     </row>
-    <row r="1693" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1693" spans="60:60">
       <c r="BH1693" s="12"/>
     </row>
-    <row r="1694" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1694" spans="60:60">
       <c r="BH1694" s="12"/>
     </row>
-    <row r="1695" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1695" spans="60:60">
       <c r="BH1695" s="12"/>
     </row>
-    <row r="1696" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1696" spans="60:60">
       <c r="BH1696" s="12"/>
     </row>
-    <row r="1697" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1697" spans="60:60">
       <c r="BH1697" s="12"/>
     </row>
-    <row r="1698" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1698" spans="60:60">
       <c r="BH1698" s="12"/>
     </row>
-    <row r="1699" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1699" spans="60:60">
       <c r="BH1699" s="12"/>
     </row>
-    <row r="1700" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1700" spans="60:60">
       <c r="BH1700" s="12"/>
     </row>
-    <row r="1701" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1701" spans="60:60">
       <c r="BH1701" s="12"/>
     </row>
-    <row r="1702" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1702" spans="60:60">
       <c r="BH1702" s="12"/>
     </row>
-    <row r="1703" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1703" spans="60:60">
       <c r="BH1703" s="12"/>
     </row>
-    <row r="1704" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1704" spans="60:60">
       <c r="BH1704" s="12"/>
     </row>
-    <row r="1705" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1705" spans="60:60">
       <c r="BH1705" s="12"/>
     </row>
-    <row r="1706" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1706" spans="60:60">
       <c r="BH1706" s="12"/>
     </row>
-    <row r="1707" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1707" spans="60:60">
       <c r="BH1707" s="12"/>
     </row>
-    <row r="1708" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1708" spans="60:60">
       <c r="BH1708" s="12"/>
     </row>
-    <row r="1709" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1709" spans="60:60">
       <c r="BH1709" s="12"/>
     </row>
-    <row r="1710" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1710" spans="60:60">
       <c r="BH1710" s="12"/>
     </row>
-    <row r="1711" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1711" spans="60:60">
       <c r="BH1711" s="12"/>
     </row>
-    <row r="1712" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1712" spans="60:60">
       <c r="BH1712" s="12"/>
     </row>
-    <row r="1713" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1713" spans="60:60">
       <c r="BH1713" s="12"/>
     </row>
-    <row r="1714" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1714" spans="60:60">
       <c r="BH1714" s="12"/>
     </row>
-    <row r="1715" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1715" spans="60:60">
       <c r="BH1715" s="12"/>
     </row>
-    <row r="1716" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1716" spans="60:60">
       <c r="BH1716" s="12"/>
     </row>
-    <row r="1717" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1717" spans="60:60">
       <c r="BH1717" s="12"/>
     </row>
-    <row r="1718" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1718" spans="60:60">
       <c r="BH1718" s="12"/>
     </row>
-    <row r="1719" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1719" spans="60:60">
       <c r="BH1719" s="12"/>
     </row>
-    <row r="1720" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1720" spans="60:60">
       <c r="BH1720" s="12"/>
     </row>
-    <row r="1721" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1721" spans="60:60">
       <c r="BH1721" s="12"/>
     </row>
-    <row r="1722" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1722" spans="60:60">
       <c r="BH1722" s="12"/>
     </row>
-    <row r="1723" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1723" spans="60:60">
       <c r="BH1723" s="12"/>
     </row>
-    <row r="1724" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1724" spans="60:60">
       <c r="BH1724" s="12"/>
     </row>
-    <row r="1725" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1725" spans="60:60">
       <c r="BH1725" s="12"/>
     </row>
-    <row r="1726" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1726" spans="60:60">
       <c r="BH1726" s="12"/>
     </row>
-    <row r="1727" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1727" spans="60:60">
       <c r="BH1727" s="12"/>
     </row>
-    <row r="1728" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1728" spans="60:60">
       <c r="BH1728" s="12"/>
     </row>
-    <row r="1729" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1729" spans="60:60">
       <c r="BH1729" s="12"/>
     </row>
-    <row r="1730" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1730" spans="60:60">
       <c r="BH1730" s="12"/>
     </row>
-    <row r="1731" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1731" spans="60:60">
       <c r="BH1731" s="12"/>
     </row>
-    <row r="1732" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1732" spans="60:60">
       <c r="BH1732" s="12"/>
     </row>
-    <row r="1733" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1733" spans="60:60">
       <c r="BH1733" s="12"/>
     </row>
-    <row r="1734" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1734" spans="60:60">
       <c r="BH1734" s="12"/>
     </row>
-    <row r="1735" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1735" spans="60:60">
       <c r="BH1735" s="12"/>
     </row>
-    <row r="1736" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1736" spans="60:60">
       <c r="BH1736" s="12"/>
     </row>
-    <row r="1737" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1737" spans="60:60">
       <c r="BH1737" s="12"/>
     </row>
-    <row r="1738" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1738" spans="60:60">
       <c r="BH1738" s="12"/>
     </row>
-    <row r="1739" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1739" spans="60:60">
       <c r="BH1739" s="12"/>
     </row>
-    <row r="1740" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1740" spans="60:60">
       <c r="BH1740" s="12"/>
     </row>
-    <row r="1741" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1741" spans="60:60">
       <c r="BH1741" s="12"/>
     </row>
-    <row r="1742" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1742" spans="60:60">
       <c r="BH1742" s="12"/>
     </row>
-    <row r="1743" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1743" spans="60:60">
       <c r="BH1743" s="12"/>
     </row>
-    <row r="1744" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1744" spans="60:60">
       <c r="BH1744" s="12"/>
     </row>
-    <row r="1745" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1745" spans="60:60">
       <c r="BH1745" s="12"/>
     </row>
-    <row r="1746" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1746" spans="60:60">
       <c r="BH1746" s="12"/>
     </row>
-    <row r="1747" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1747" spans="60:60">
       <c r="BH1747" s="12"/>
     </row>
-    <row r="1748" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1748" spans="60:60">
       <c r="BH1748" s="12"/>
     </row>
-    <row r="1749" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1749" spans="60:60">
       <c r="BH1749" s="12"/>
     </row>
-    <row r="1750" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1750" spans="60:60" ht="17.25">
       <c r="BH1750" s="13"/>
     </row>
-    <row r="1751" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1751" spans="60:60" ht="16.5">
       <c r="BH1751" s="10"/>
     </row>
-    <row r="1752" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1752" spans="60:60" ht="16.5">
       <c r="BH1752" s="11"/>
     </row>
-    <row r="1753" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1753" spans="60:60" ht="17.25">
       <c r="BH1753" s="13"/>
     </row>
-    <row r="1754" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1754" spans="60:60" ht="16.5">
       <c r="BH1754" s="10"/>
     </row>
-    <row r="1755" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1755" spans="60:60" ht="16.5">
       <c r="BH1755" s="11"/>
     </row>
-    <row r="1756" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1756" spans="60:60" ht="17.25">
       <c r="BH1756" s="13"/>
     </row>
-    <row r="1757" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1757" spans="60:60">
       <c r="BH1757" s="12"/>
     </row>
-    <row r="1758" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1758" spans="60:60" ht="17.25">
       <c r="BH1758" s="13"/>
     </row>
-    <row r="1759" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1759" spans="60:60">
       <c r="BH1759" s="12"/>
     </row>
-    <row r="1760" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1760" spans="60:60" ht="17.25">
       <c r="BH1760" s="13"/>
     </row>
-    <row r="1761" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1761" spans="60:60">
       <c r="BH1761" s="12"/>
     </row>
-    <row r="1762" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1762" spans="60:60" ht="17.25">
       <c r="BH1762" s="13"/>
     </row>
-    <row r="1763" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1763" spans="60:60">
       <c r="BH1763" s="12"/>
     </row>
-    <row r="1764" spans="60:60" ht="24" x14ac:dyDescent="0.25">
+    <row r="1764" spans="60:60" ht="24">
       <c r="BH1764" s="14"/>
     </row>
-    <row r="1765" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1765" spans="60:60">
       <c r="BH1765" s="12"/>
     </row>
-    <row r="1766" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1766" spans="60:60" ht="17.25">
       <c r="BH1766" s="13"/>
     </row>
-    <row r="1767" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1767" spans="60:60">
       <c r="BH1767" s="12"/>
     </row>
-    <row r="1768" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1768" spans="60:60" ht="17.25">
       <c r="BH1768" s="13"/>
     </row>
-    <row r="1769" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1769" spans="60:60">
       <c r="BH1769" s="16"/>
     </row>
-    <row r="1770" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1770" spans="60:60" ht="17.25">
       <c r="BH1770" s="23"/>
     </row>
-    <row r="1771" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1771" spans="60:60" ht="17.25">
       <c r="BH1771" s="23"/>
     </row>
-    <row r="1772" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1772" spans="60:60" ht="17.25">
       <c r="BH1772" s="23"/>
     </row>
-    <row r="1773" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1773" spans="60:60" ht="17.25">
       <c r="BH1773" s="23"/>
     </row>
-    <row r="1774" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1774" spans="60:60" ht="17.25">
       <c r="BH1774" s="23"/>
     </row>
-    <row r="1775" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1775" spans="60:60" ht="17.25">
       <c r="BH1775" s="23"/>
     </row>
-    <row r="1776" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1776" spans="60:60">
       <c r="BH1776" s="12"/>
     </row>
-    <row r="1777" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1777" spans="60:60" ht="17.25">
       <c r="BH1777" s="13"/>
     </row>
-    <row r="1778" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1778" spans="60:60">
       <c r="BH1778" s="12"/>
     </row>
-    <row r="1779" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1779" spans="60:60">
       <c r="BH1779" s="12"/>
     </row>
-    <row r="1780" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1780" spans="60:60">
       <c r="BH1780" s="12"/>
     </row>
-    <row r="1782" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1782" spans="60:60">
       <c r="BH1782" s="12"/>
     </row>
-    <row r="1783" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1783" spans="60:60">
       <c r="BH1783" s="12"/>
     </row>
-    <row r="1784" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1784" spans="60:60">
       <c r="BH1784" s="12"/>
     </row>
-    <row r="1785" spans="60:60" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="1785" spans="60:60" ht="26.25">
       <c r="BH1785" s="20"/>
     </row>
-    <row r="1786" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1786" spans="60:60">
       <c r="BH1786" s="12"/>
     </row>
-    <row r="1787" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1787" spans="60:60" ht="17.25">
       <c r="BH1787" s="13"/>
     </row>
-    <row r="1788" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1788" spans="60:60">
       <c r="BH1788" s="9"/>
     </row>
-    <row r="1789" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1789" spans="60:60">
       <c r="BH1789" s="19"/>
     </row>
-    <row r="1790" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1790" spans="60:60">
       <c r="BH1790" s="19"/>
     </row>
-    <row r="1791" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1791" spans="60:60">
       <c r="BH1791" s="19"/>
     </row>
-    <row r="1792" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="1792" spans="60:60">
       <c r="BH1792" s="12"/>
     </row>
-    <row r="1977" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1977" spans="60:60" ht="16.5">
       <c r="BH1977" s="10"/>
     </row>
-    <row r="1978" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1978" spans="60:60" ht="16.5">
       <c r="BH1978" s="11"/>
     </row>
-    <row r="1979" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1979" spans="60:60" ht="17.25">
       <c r="BH1979" s="13"/>
     </row>
-    <row r="1980" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1980" spans="60:60" ht="16.5">
       <c r="BH1980" s="10"/>
     </row>
-    <row r="1981" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1981" spans="60:60" ht="16.5">
       <c r="BH1981" s="11"/>
     </row>
-    <row r="1982" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1982" spans="60:60" ht="17.25">
       <c r="BH1982" s="13"/>
     </row>
-    <row r="1983" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1983" spans="60:60" ht="16.5">
       <c r="BH1983" s="22"/>
     </row>
-    <row r="1984" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1984" spans="60:60" ht="16.5">
       <c r="BH1984" s="10"/>
     </row>
-    <row r="1985" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1985" spans="60:60" ht="16.5">
       <c r="BH1985" s="11"/>
     </row>
-    <row r="1986" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1986" spans="60:60" ht="17.25">
       <c r="BH1986" s="13"/>
     </row>
-    <row r="1987" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1987" spans="60:60" ht="16.5">
       <c r="BH1987" s="22"/>
     </row>
-    <row r="1988" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1988" spans="60:60" ht="16.5">
       <c r="BH1988" s="10"/>
     </row>
-    <row r="1989" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1989" spans="60:60" ht="16.5">
       <c r="BH1989" s="11"/>
     </row>
-    <row r="1990" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1990" spans="60:60" ht="17.25">
       <c r="BH1990" s="13"/>
     </row>
-    <row r="1991" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1991" spans="60:60" ht="16.5">
       <c r="BH1991" s="22"/>
     </row>
-    <row r="1992" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1992" spans="60:60" ht="16.5">
       <c r="BH1992" s="10"/>
     </row>
-    <row r="1993" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1993" spans="60:60" ht="16.5">
       <c r="BH1993" s="11"/>
     </row>
-    <row r="1994" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1994" spans="60:60" ht="17.25">
       <c r="BH1994" s="13"/>
     </row>
-    <row r="1995" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1995" spans="60:60" ht="16.5">
       <c r="BH1995" s="22"/>
     </row>
-    <row r="1996" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1996" spans="60:60" ht="16.5">
       <c r="BH1996" s="10"/>
     </row>
-    <row r="1997" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1997" spans="60:60" ht="16.5">
       <c r="BH1997" s="11"/>
     </row>
-    <row r="1998" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1998" spans="60:60" ht="17.25">
       <c r="BH1998" s="13"/>
     </row>
-    <row r="1999" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1999" spans="60:60" ht="16.5">
       <c r="BH1999" s="22"/>
     </row>
-    <row r="2000" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2000" spans="60:60" ht="16.5">
       <c r="BH2000" s="10"/>
     </row>
-    <row r="2001" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2001" spans="60:60" ht="16.5">
       <c r="BH2001" s="11"/>
     </row>
-    <row r="2002" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2002" spans="60:60" ht="17.25">
       <c r="BH2002" s="13"/>
     </row>
-    <row r="2003" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2003" spans="60:60" ht="16.5">
       <c r="BH2003" s="10"/>
     </row>
-    <row r="2004" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2004" spans="60:60" ht="16.5">
       <c r="BH2004" s="11"/>
     </row>
-    <row r="2005" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2005" spans="60:60" ht="17.25">
       <c r="BH2005" s="13"/>
     </row>
-    <row r="2006" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2006" spans="60:60" ht="16.5">
       <c r="BH2006" s="10"/>
     </row>
-    <row r="2007" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2007" spans="60:60" ht="16.5">
       <c r="BH2007" s="11"/>
     </row>
-    <row r="2008" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2008" spans="60:60" ht="17.25">
       <c r="BH2008" s="13"/>
     </row>
-    <row r="2009" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2009" spans="60:60" ht="16.5">
       <c r="BH2009" s="10"/>
     </row>
-    <row r="2010" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2010" spans="60:60" ht="16.5">
       <c r="BH2010" s="11"/>
     </row>
-    <row r="2011" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2011" spans="60:60" ht="17.25">
       <c r="BH2011" s="13"/>
     </row>
-    <row r="2012" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2012" spans="60:60" ht="16.5">
       <c r="BH2012" s="10"/>
     </row>
-    <row r="2013" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2013" spans="60:60" ht="16.5">
       <c r="BH2013" s="11"/>
     </row>
-    <row r="2014" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2014" spans="60:60" ht="17.25">
       <c r="BH2014" s="13"/>
     </row>
-    <row r="2015" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2015" spans="60:60" ht="16.5">
       <c r="BH2015" s="10"/>
     </row>
-    <row r="2016" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2016" spans="60:60" ht="16.5">
       <c r="BH2016" s="11"/>
     </row>
-    <row r="2017" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2017" spans="60:60" ht="17.25">
       <c r="BH2017" s="13"/>
     </row>
-    <row r="2018" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2018" spans="60:60" ht="16.5">
       <c r="BH2018" s="10"/>
     </row>
-    <row r="2019" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2019" spans="60:60" ht="16.5">
       <c r="BH2019" s="11"/>
     </row>
-    <row r="2020" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2020" spans="60:60" ht="17.25">
       <c r="BH2020" s="13"/>
     </row>
-    <row r="2021" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2021" spans="60:60" ht="16.5">
       <c r="BH2021" s="10"/>
     </row>
-    <row r="2022" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2022" spans="60:60" ht="16.5">
       <c r="BH2022" s="11"/>
     </row>
-    <row r="2023" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2023" spans="60:60" ht="17.25">
       <c r="BH2023" s="13"/>
     </row>
-    <row r="2024" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2024" spans="60:60" ht="16.5">
       <c r="BH2024" s="22"/>
     </row>
-    <row r="2025" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2025" spans="60:60" ht="16.5">
       <c r="BH2025" s="10"/>
     </row>
-    <row r="2026" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2026" spans="60:60" ht="16.5">
       <c r="BH2026" s="11"/>
     </row>
-    <row r="2027" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2027" spans="60:60" ht="17.25">
       <c r="BH2027" s="13"/>
     </row>
-    <row r="2028" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2028" spans="60:60" ht="16.5">
       <c r="BH2028" s="10"/>
     </row>
-    <row r="2029" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2029" spans="60:60" ht="16.5">
       <c r="BH2029" s="11"/>
     </row>
-    <row r="2030" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2030" spans="60:60" ht="17.25">
       <c r="BH2030" s="13"/>
     </row>
-    <row r="2031" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2031" spans="60:60" ht="16.5">
       <c r="BH2031" s="10"/>
     </row>
-    <row r="2032" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2032" spans="60:60" ht="16.5">
       <c r="BH2032" s="11"/>
     </row>
-    <row r="2033" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2033" spans="60:60" ht="17.25">
       <c r="BH2033" s="13"/>
     </row>
-    <row r="2034" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2034" spans="60:60" ht="16.5">
       <c r="BH2034" s="10"/>
     </row>
-    <row r="2035" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2035" spans="60:60" ht="16.5">
       <c r="BH2035" s="11"/>
     </row>
-    <row r="2036" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2036" spans="60:60" ht="16.5">
       <c r="BH2036" s="10"/>
     </row>
-    <row r="2037" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2037" spans="60:60" ht="16.5">
       <c r="BH2037" s="11"/>
     </row>
-    <row r="2038" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2038" spans="60:60" ht="16.5">
       <c r="BH2038" s="10"/>
     </row>
-    <row r="2039" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2039" spans="60:60" ht="16.5">
       <c r="BH2039" s="11"/>
     </row>
-    <row r="2040" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2040" spans="60:60" ht="16.5">
       <c r="BH2040" s="10"/>
     </row>
-    <row r="2041" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2041" spans="60:60" ht="16.5">
       <c r="BH2041" s="11"/>
     </row>
-    <row r="2042" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2042" spans="60:60" ht="16.5">
       <c r="BH2042" s="10"/>
     </row>
-    <row r="2043" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2043" spans="60:60" ht="16.5">
       <c r="BH2043" s="11"/>
     </row>
-    <row r="2044" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2044" spans="60:60" ht="16.5">
       <c r="BH2044" s="10"/>
     </row>
-    <row r="2045" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2045" spans="60:60" ht="16.5">
       <c r="BH2045" s="11"/>
     </row>
-    <row r="2046" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2046" spans="60:60" ht="16.5">
       <c r="BH2046" s="10"/>
     </row>
-    <row r="2047" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2047" spans="60:60" ht="16.5">
       <c r="BH2047" s="11"/>
     </row>
-    <row r="2048" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2048" spans="60:60" ht="16.5">
       <c r="BH2048" s="10"/>
     </row>
-    <row r="2049" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2049" spans="60:60" ht="16.5">
       <c r="BH2049" s="11"/>
     </row>
-    <row r="2050" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2050" spans="60:60" ht="16.5">
       <c r="BH2050" s="10"/>
     </row>
-    <row r="2051" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2051" spans="60:60" ht="16.5">
       <c r="BH2051" s="11"/>
     </row>
-    <row r="2052" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2052" spans="60:60" ht="17.25">
       <c r="BH2052" s="13"/>
     </row>
-    <row r="2053" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2053" spans="60:60" ht="16.5">
       <c r="BH2053" s="10"/>
     </row>
-    <row r="2054" spans="60:60" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2054" spans="60:60" ht="16.5">
       <c r="BH2054" s="11"/>
     </row>
-    <row r="2055" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2055" spans="60:60" ht="17.25">
       <c r="BH2055" s="13"/>
     </row>
-    <row r="2056" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2056" spans="60:60">
       <c r="BH2056" s="12"/>
     </row>
-    <row r="2057" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2057" spans="60:60" ht="17.25">
       <c r="BH2057" s="13"/>
     </row>
-    <row r="2058" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2058" spans="60:60">
       <c r="BH2058" s="12"/>
     </row>
-    <row r="2059" spans="60:60" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2059" spans="60:60" ht="20.25">
       <c r="BH2059" s="15"/>
     </row>
-    <row r="2060" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2060" spans="60:60">
       <c r="BH2060" s="12"/>
     </row>
-    <row r="2061" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2061" spans="60:60" ht="17.25">
       <c r="BH2061" s="13"/>
     </row>
-    <row r="2062" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2062" spans="60:60">
       <c r="BH2062" s="9"/>
     </row>
-    <row r="2063" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2063" spans="60:60">
       <c r="BH2063" s="26"/>
     </row>
-    <row r="2064" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2064" spans="60:60">
       <c r="BH2064" s="12"/>
     </row>
-    <row r="2065" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2065" spans="60:60" ht="17.25">
       <c r="BH2065" s="13"/>
     </row>
-    <row r="2066" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2066" spans="60:60">
       <c r="BH2066" s="12"/>
     </row>
-    <row r="2067" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2067" spans="60:60" ht="17.25">
       <c r="BH2067" s="13"/>
     </row>
-    <row r="2068" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2068" spans="60:60">
       <c r="BH2068" s="12"/>
     </row>
-    <row r="2069" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2069" spans="60:60">
       <c r="BH2069" s="12"/>
     </row>
-    <row r="2070" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2070" spans="60:60">
       <c r="BH2070" s="12"/>
     </row>
-    <row r="2072" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2072" spans="60:60">
       <c r="BH2072" s="12"/>
     </row>
-    <row r="2073" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2073" spans="60:60">
       <c r="BH2073" s="12"/>
     </row>
-    <row r="2074" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2074" spans="60:60">
       <c r="BH2074" s="12"/>
     </row>
-    <row r="2075" spans="60:60" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2075" spans="60:60" ht="20.25">
       <c r="BH2075" s="15"/>
     </row>
-    <row r="2076" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2076" spans="60:60">
       <c r="BH2076" s="12"/>
     </row>
-    <row r="2077" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2077" spans="60:60" ht="17.25">
       <c r="BH2077" s="13"/>
     </row>
-    <row r="2078" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2078" spans="60:60">
       <c r="BH2078" s="12"/>
     </row>
-    <row r="2079" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2079" spans="60:60" ht="17.25">
       <c r="BH2079" s="13"/>
     </row>
-    <row r="2080" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2080" spans="60:60">
       <c r="BH2080" s="12"/>
     </row>
-    <row r="2081" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2081" spans="60:60" ht="17.25">
       <c r="BH2081" s="13"/>
     </row>
-    <row r="2082" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2082" spans="60:60">
       <c r="BH2082" s="9"/>
     </row>
-    <row r="2083" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2083" spans="60:60">
       <c r="BH2083" s="19"/>
     </row>
-    <row r="2084" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2084" spans="60:60">
       <c r="BH2084" s="12"/>
     </row>
-    <row r="2085" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2085" spans="60:60">
       <c r="BH2085" s="12"/>
     </row>
-    <row r="2086" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2086" spans="60:60">
       <c r="BH2086" s="12"/>
     </row>
-    <row r="2088" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2088" spans="60:60">
       <c r="BH2088" s="12"/>
     </row>
-    <row r="2089" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2089" spans="60:60">
       <c r="BH2089" s="12"/>
     </row>
-    <row r="2090" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2090" spans="60:60">
       <c r="BH2090" s="12"/>
     </row>
-    <row r="2091" spans="60:60" ht="24" x14ac:dyDescent="0.25">
+    <row r="2091" spans="60:60" ht="24">
       <c r="BH2091" s="14"/>
     </row>
-    <row r="2092" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2092" spans="60:60">
       <c r="BH2092" s="12"/>
     </row>
-    <row r="2093" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2093" spans="60:60" ht="17.25">
       <c r="BH2093" s="13"/>
     </row>
-    <row r="2094" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2094" spans="60:60">
       <c r="BH2094" s="9"/>
     </row>
-    <row r="2095" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2095" spans="60:60">
       <c r="BH2095" s="19"/>
     </row>
-    <row r="2096" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2096" spans="60:60">
       <c r="BH2096" s="12"/>
     </row>
-    <row r="2097" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2097" spans="60:60" ht="17.25">
       <c r="BH2097" s="13"/>
     </row>
-    <row r="2098" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2098" spans="60:60">
       <c r="BH2098" s="9"/>
     </row>
-    <row r="2099" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2099" spans="60:60">
       <c r="BH2099" s="19"/>
     </row>
-    <row r="2100" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2100" spans="60:60">
       <c r="BH2100" s="12"/>
     </row>
-    <row r="2101" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2101" spans="60:60" ht="17.25">
       <c r="BH2101" s="13"/>
     </row>
-    <row r="2102" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2102" spans="60:60">
       <c r="BH2102" s="9"/>
     </row>
-    <row r="2103" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2103" spans="60:60">
       <c r="BH2103" s="19"/>
     </row>
-    <row r="2104" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2104" spans="60:60">
       <c r="BH2104" s="19"/>
     </row>
-    <row r="2105" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2105" spans="60:60">
       <c r="BH2105" s="19"/>
     </row>
-    <row r="2106" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2106" spans="60:60">
       <c r="BH2106" s="19"/>
     </row>
-    <row r="2107" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2107" spans="60:60">
       <c r="BH2107" s="19"/>
     </row>
-    <row r="2108" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2108" spans="60:60">
       <c r="BH2108" s="19"/>
     </row>
-    <row r="2109" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2109" spans="60:60">
       <c r="BH2109" s="12"/>
     </row>
-    <row r="2110" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2110" spans="60:60" ht="17.25">
       <c r="BH2110" s="13"/>
     </row>
-    <row r="2111" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2111" spans="60:60">
       <c r="BH2111" s="12"/>
     </row>
-    <row r="2112" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2112" spans="60:60">
       <c r="BH2112" s="12"/>
     </row>
-    <row r="2113" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2113" spans="60:60">
       <c r="BH2113" s="12"/>
     </row>
-    <row r="2115" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2115" spans="60:60">
       <c r="BH2115" s="12"/>
     </row>
-    <row r="2116" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2116" spans="60:60">
       <c r="BH2116" s="12"/>
     </row>
-    <row r="2117" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2117" spans="60:60">
       <c r="BH2117" s="12"/>
     </row>
-    <row r="2118" spans="60:60" ht="24" x14ac:dyDescent="0.25">
+    <row r="2118" spans="60:60" ht="24">
       <c r="BH2118" s="14"/>
     </row>
-    <row r="2119" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2119" spans="60:60">
       <c r="BH2119" s="12"/>
     </row>
-    <row r="2120" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2120" spans="60:60" ht="17.25">
       <c r="BH2120" s="13"/>
     </row>
-    <row r="2121" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2121" spans="60:60">
       <c r="BH2121" s="16"/>
     </row>
-    <row r="2122" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2122" spans="60:60" ht="17.25">
       <c r="BH2122" s="23"/>
     </row>
-    <row r="2123" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2123" spans="60:60" ht="17.25">
       <c r="BH2123" s="23"/>
     </row>
-    <row r="2124" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2124" spans="60:60" ht="17.25">
       <c r="BH2124" s="23"/>
     </row>
-    <row r="2125" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2125" spans="60:60" ht="17.25">
       <c r="BH2125" s="23"/>
     </row>
-    <row r="2126" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2126" spans="60:60" ht="17.25">
       <c r="BH2126" s="23"/>
     </row>
-    <row r="2127" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2127" spans="60:60" ht="17.25">
       <c r="BH2127" s="23"/>
     </row>
-    <row r="2128" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2128" spans="60:60" ht="17.25">
       <c r="BH2128" s="23"/>
     </row>
-    <row r="2129" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2129" spans="60:60">
       <c r="BH2129" s="12"/>
     </row>
-    <row r="2130" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2130" spans="60:60" ht="17.25">
       <c r="BH2130" s="13"/>
     </row>
-    <row r="2131" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2131" spans="60:60">
       <c r="BH2131" s="12"/>
     </row>
-    <row r="2132" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2132" spans="60:60" ht="17.25">
       <c r="BH2132" s="13"/>
     </row>
-    <row r="2133" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2133" spans="60:60">
       <c r="BH2133" s="12"/>
     </row>
-    <row r="2134" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2134" spans="60:60" ht="17.25">
       <c r="BH2134" s="13"/>
     </row>
-    <row r="2135" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2135" spans="60:60">
       <c r="BH2135" s="12"/>
     </row>
-    <row r="2136" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2136" spans="60:60" ht="17.25">
       <c r="BH2136" s="13"/>
     </row>
-    <row r="2137" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2137" spans="60:60">
       <c r="BH2137" s="9"/>
     </row>
-    <row r="2138" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2138" spans="60:60">
       <c r="BH2138" s="19"/>
     </row>
-    <row r="2139" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2139" spans="60:60">
       <c r="BH2139" s="19"/>
     </row>
-    <row r="2140" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2140" spans="60:60">
       <c r="BH2140" s="19"/>
     </row>
-    <row r="2141" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2141" spans="60:60">
       <c r="BH2141" s="19"/>
     </row>
-    <row r="2142" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2142" spans="60:60">
       <c r="BH2142" s="19"/>
     </row>
-    <row r="2143" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2143" spans="60:60">
       <c r="BH2143" s="19"/>
     </row>
-    <row r="2144" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2144" spans="60:60">
       <c r="BH2144" s="19"/>
     </row>
-    <row r="2145" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2145" spans="60:60">
       <c r="BH2145" s="12"/>
     </row>
-    <row r="2146" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2146" spans="60:60" ht="17.25">
       <c r="BH2146" s="13"/>
     </row>
-    <row r="2147" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2147" spans="60:60">
       <c r="BH2147" s="12"/>
     </row>
-    <row r="2148" spans="60:60" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2148" spans="60:60" ht="20.25">
       <c r="BH2148" s="15"/>
     </row>
-    <row r="2149" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2149" spans="60:60">
       <c r="BH2149" s="12"/>
     </row>
-    <row r="2150" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2150" spans="60:60" ht="17.25">
       <c r="BH2150" s="13"/>
     </row>
-    <row r="2151" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2151" spans="60:60">
       <c r="BH2151" s="9"/>
     </row>
-    <row r="2152" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2152" spans="60:60">
       <c r="BH2152" s="19"/>
     </row>
-    <row r="2153" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2153" spans="60:60">
       <c r="BH2153" s="12"/>
     </row>
-    <row r="2154" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2154" spans="60:60" ht="17.25">
       <c r="BH2154" s="13"/>
     </row>
-    <row r="2155" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2155" spans="60:60">
       <c r="BH2155" s="16"/>
     </row>
-    <row r="2156" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2156" spans="60:60">
       <c r="BH2156" s="25"/>
     </row>
-    <row r="2157" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2157" spans="60:60">
       <c r="BH2157" s="25"/>
     </row>
-    <row r="2158" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2158" spans="60:60">
       <c r="BH2158" s="12"/>
     </row>
-    <row r="2159" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2159" spans="60:60" ht="17.25">
       <c r="BH2159" s="13"/>
     </row>
-    <row r="2160" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2160" spans="60:60">
       <c r="BH2160" s="12"/>
     </row>
-    <row r="2161" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2161" spans="60:60" ht="17.25">
       <c r="BH2161" s="13"/>
     </row>
-    <row r="2162" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2162" spans="60:60">
       <c r="BH2162" s="12"/>
     </row>
-    <row r="2163" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2163" spans="60:60">
       <c r="BH2163" s="12"/>
     </row>
-    <row r="2164" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2164" spans="60:60">
       <c r="BH2164" s="12"/>
     </row>
-    <row r="2166" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2166" spans="60:60">
       <c r="BH2166" s="12"/>
     </row>
-    <row r="2167" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2167" spans="60:60">
       <c r="BH2167" s="12"/>
     </row>
-    <row r="2168" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2168" spans="60:60">
       <c r="BH2168" s="12"/>
     </row>
-    <row r="2169" spans="60:60" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2169" spans="60:60" ht="20.25">
       <c r="BH2169" s="15"/>
     </row>
-    <row r="2170" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2170" spans="60:60" ht="17.25">
       <c r="BH2170" s="21"/>
     </row>
-    <row r="2171" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2171" spans="60:60">
       <c r="BH2171" s="12"/>
     </row>
-    <row r="2172" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2172" spans="60:60" ht="17.25">
       <c r="BH2172" s="13"/>
     </row>
-    <row r="2173" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2173" spans="60:60">
       <c r="BH2173" s="9"/>
     </row>
-    <row r="2174" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2174" spans="60:60">
       <c r="BH2174" s="19"/>
     </row>
-    <row r="2175" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2175" spans="60:60">
       <c r="BH2175" s="12"/>
     </row>
-    <row r="2176" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2176" spans="60:60" ht="17.25">
       <c r="BH2176" s="13"/>
     </row>
-    <row r="2177" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2177" spans="60:60">
       <c r="BH2177" s="9"/>
     </row>
-    <row r="2178" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2178" spans="60:60">
       <c r="BH2178" s="19"/>
     </row>
-    <row r="2179" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2179" spans="60:60">
       <c r="BH2179" s="12"/>
     </row>
-    <row r="2180" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2180" spans="60:60" ht="17.25">
       <c r="BH2180" s="13"/>
     </row>
-    <row r="2181" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2181" spans="60:60">
       <c r="BH2181" s="12"/>
     </row>
-    <row r="2182" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2182" spans="60:60">
       <c r="BH2182" s="12"/>
     </row>
-    <row r="2183" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2183" spans="60:60">
       <c r="BH2183" s="12"/>
     </row>
-    <row r="2185" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2185" spans="60:60">
       <c r="BH2185" s="12"/>
     </row>
-    <row r="2186" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2186" spans="60:60">
       <c r="BH2186" s="12"/>
     </row>
-    <row r="2187" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2187" spans="60:60">
       <c r="BH2187" s="12"/>
     </row>
-    <row r="2188" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2188" spans="60:60" ht="17.25">
       <c r="BH2188" s="21"/>
     </row>
-    <row r="2189" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2189" spans="60:60">
       <c r="BH2189" s="12"/>
     </row>
-    <row r="2190" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2190" spans="60:60" ht="17.25">
       <c r="BH2190" s="13"/>
     </row>
-    <row r="2191" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2191" spans="60:60">
       <c r="BH2191" s="9"/>
     </row>
-    <row r="2192" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2192" spans="60:60">
       <c r="BH2192" s="19"/>
     </row>
-    <row r="2193" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2193" spans="60:60">
       <c r="BH2193" s="12"/>
     </row>
-    <row r="2194" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2194" spans="60:60" ht="17.25">
       <c r="BH2194" s="13"/>
     </row>
-    <row r="2195" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2195" spans="60:60">
       <c r="BH2195" s="9"/>
     </row>
-    <row r="2196" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2196" spans="60:60">
       <c r="BH2196" s="19"/>
     </row>
-    <row r="2197" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2197" spans="60:60">
       <c r="BH2197" s="12"/>
     </row>
-    <row r="2198" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2198" spans="60:60" ht="17.25">
       <c r="BH2198" s="13"/>
     </row>
-    <row r="2199" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2199" spans="60:60">
       <c r="BH2199" s="12"/>
     </row>
-    <row r="2200" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2200" spans="60:60">
       <c r="BH2200" s="12"/>
     </row>
-    <row r="2201" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2201" spans="60:60">
       <c r="BH2201" s="12"/>
     </row>
-    <row r="2203" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2203" spans="60:60">
       <c r="BH2203" s="12"/>
     </row>
-    <row r="2204" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2204" spans="60:60">
       <c r="BH2204" s="12"/>
     </row>
-    <row r="2205" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2205" spans="60:60">
       <c r="BH2205" s="12"/>
     </row>
-    <row r="2206" spans="60:60" ht="24" x14ac:dyDescent="0.25">
+    <row r="2206" spans="60:60" ht="24">
       <c r="BH2206" s="14"/>
     </row>
-    <row r="2207" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2207" spans="60:60">
       <c r="BH2207" s="12"/>
     </row>
-    <row r="2208" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2208" spans="60:60" ht="17.25">
       <c r="BH2208" s="13"/>
     </row>
-    <row r="2209" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2209" spans="60:60">
       <c r="BH2209" s="12"/>
     </row>
-    <row r="2210" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2210" spans="60:60" ht="17.25">
       <c r="BH2210" s="13"/>
     </row>
-    <row r="2211" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2211" spans="60:60">
       <c r="BH2211" s="12"/>
     </row>
-    <row r="2212" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2212" spans="60:60" ht="17.25">
       <c r="BH2212" s="13"/>
     </row>
-    <row r="2213" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2213" spans="60:60">
       <c r="BH2213" s="9"/>
     </row>
-    <row r="2214" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2214" spans="60:60">
       <c r="BH2214" s="19"/>
     </row>
-    <row r="2215" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2215" spans="60:60">
       <c r="BH2215" s="12"/>
     </row>
-    <row r="2216" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2216" spans="60:60" ht="17.25">
       <c r="BH2216" s="13"/>
     </row>
-    <row r="2217" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2217" spans="60:60">
       <c r="BH2217" s="9"/>
     </row>
-    <row r="2218" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2218" spans="60:60">
       <c r="BH2218" s="19"/>
     </row>
-    <row r="2219" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2219" spans="60:60">
       <c r="BH2219" s="12"/>
     </row>
-    <row r="2220" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2220" spans="60:60" ht="17.25">
       <c r="BH2220" s="13"/>
     </row>
-    <row r="2221" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2221" spans="60:60">
       <c r="BH2221" s="12"/>
     </row>
-    <row r="2222" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2222" spans="60:60">
       <c r="BH2222" s="12"/>
     </row>
-    <row r="2223" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2223" spans="60:60">
       <c r="BH2223" s="12"/>
     </row>
-    <row r="2225" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2225" spans="60:60">
       <c r="BH2225" s="12"/>
     </row>
-    <row r="2226" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2226" spans="60:60">
       <c r="BH2226" s="12"/>
     </row>
-    <row r="2227" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2227" spans="60:60">
       <c r="BH2227" s="12"/>
     </row>
-    <row r="2228" spans="60:60" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2228" spans="60:60" ht="20.25">
       <c r="BH2228" s="15"/>
     </row>
-    <row r="2229" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2229" spans="60:60">
       <c r="BH2229" s="12"/>
     </row>
-    <row r="2230" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2230" spans="60:60" ht="17.25">
       <c r="BH2230" s="13"/>
     </row>
-    <row r="2231" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2231" spans="60:60">
       <c r="BH2231" s="9"/>
     </row>
-    <row r="2232" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2232" spans="60:60">
       <c r="BH2232" s="19"/>
     </row>
-    <row r="2233" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2233" spans="60:60">
       <c r="BH2233" s="12"/>
     </row>
-    <row r="2234" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2234" spans="60:60" ht="17.25">
       <c r="BH2234" s="13"/>
     </row>
-    <row r="2235" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2235" spans="60:60">
       <c r="BH2235" s="16"/>
     </row>
-    <row r="2236" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2236" spans="60:60" ht="17.25">
       <c r="BH2236" s="17"/>
     </row>
-    <row r="2237" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2237" spans="60:60" ht="17.25">
       <c r="BH2237" s="17"/>
     </row>
-    <row r="2238" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2238" spans="60:60">
       <c r="BH2238" s="12"/>
     </row>
-    <row r="2239" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2239" spans="60:60" ht="17.25">
       <c r="BH2239" s="13"/>
     </row>
-    <row r="2240" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2240" spans="60:60">
       <c r="BH2240" s="9"/>
     </row>
-    <row r="2241" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2241" spans="60:60">
       <c r="BH2241" s="19"/>
     </row>
-    <row r="2242" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2242" spans="60:60">
       <c r="BH2242" s="12"/>
     </row>
-    <row r="2243" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2243" spans="60:60" ht="17.25">
       <c r="BH2243" s="13"/>
     </row>
-    <row r="2244" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2244" spans="60:60">
       <c r="BH2244" s="9"/>
     </row>
-    <row r="2245" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2245" spans="60:60">
       <c r="BH2245" s="19"/>
     </row>
-    <row r="2246" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2246" spans="60:60">
       <c r="BH2246" s="12"/>
     </row>
-    <row r="2247" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2247" spans="60:60" ht="17.25">
       <c r="BH2247" s="13"/>
     </row>
-    <row r="2248" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2248" spans="60:60">
       <c r="BH2248" s="12"/>
     </row>
-    <row r="2249" spans="60:60" ht="24" x14ac:dyDescent="0.25">
+    <row r="2249" spans="60:60" ht="24">
       <c r="BH2249" s="14"/>
     </row>
-    <row r="2250" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2250" spans="60:60" ht="17.25">
       <c r="BH2250" s="17"/>
     </row>
-    <row r="2251" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2251" spans="60:60" ht="17.25">
       <c r="BH2251" s="17"/>
     </row>
-    <row r="2252" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2252" spans="60:60" ht="17.25">
       <c r="BH2252" s="17"/>
     </row>
-    <row r="2253" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2253" spans="60:60" ht="17.25">
       <c r="BH2253" s="17"/>
     </row>
-    <row r="2254" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2254" spans="60:60" ht="17.25">
       <c r="BH2254" s="17"/>
     </row>
-    <row r="2255" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2255" spans="60:60" ht="17.25">
       <c r="BH2255" s="17"/>
     </row>
-    <row r="2256" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2256" spans="60:60" ht="17.25">
       <c r="BH2256" s="17"/>
     </row>
-    <row r="2257" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2257" spans="60:60" ht="17.25">
       <c r="BH2257" s="17"/>
     </row>
-    <row r="2258" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2258" spans="60:60" ht="17.25">
       <c r="BH2258" s="17"/>
     </row>
-    <row r="2259" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2259" spans="60:60" ht="17.25">
       <c r="BH2259" s="17"/>
     </row>
-    <row r="2260" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2260" spans="60:60" ht="17.25">
       <c r="BH2260" s="17"/>
     </row>
-    <row r="2261" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2261" spans="60:60" ht="17.25">
       <c r="BH2261" s="17"/>
     </row>
-    <row r="2262" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2262" spans="60:60" ht="17.25">
       <c r="BH2262" s="17"/>
     </row>
-    <row r="2263" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2263" spans="60:60" ht="17.25">
       <c r="BH2263" s="17"/>
     </row>
-    <row r="2264" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2264" spans="60:60" ht="17.25">
       <c r="BH2264" s="17"/>
     </row>
-    <row r="2265" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2265" spans="60:60">
       <c r="BH2265" s="12"/>
     </row>
-    <row r="2266" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2266" spans="60:60" ht="17.25">
       <c r="BH2266" s="13"/>
     </row>
-    <row r="2267" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2267" spans="60:60">
       <c r="BH2267" s="12"/>
     </row>
-    <row r="2268" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2268" spans="60:60" ht="17.25">
       <c r="BH2268" s="13"/>
     </row>
-    <row r="2269" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2269" spans="60:60">
       <c r="BH2269" s="12"/>
     </row>
-    <row r="2270" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2270" spans="60:60" ht="17.25">
       <c r="BH2270" s="13"/>
     </row>
-    <row r="2333" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2333" spans="60:60">
       <c r="BH2333" s="12"/>
     </row>
-    <row r="2334" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2334" spans="60:60" ht="17.25">
       <c r="BH2334" s="13"/>
     </row>
-    <row r="2335" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2335" spans="60:60">
       <c r="BH2335" s="9"/>
     </row>
-    <row r="2336" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2336" spans="60:60">
       <c r="BH2336" s="19"/>
     </row>
-    <row r="2337" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2337" spans="60:60">
       <c r="BH2337" s="19"/>
     </row>
-    <row r="2338" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2338" spans="60:60">
       <c r="BH2338" s="18"/>
     </row>
-    <row r="2339" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2339" spans="60:60">
       <c r="BH2339" s="19"/>
     </row>
-    <row r="2340" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2340" spans="60:60">
       <c r="BH2340" s="19"/>
     </row>
-    <row r="2341" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2341" spans="60:60">
       <c r="BH2341" s="19"/>
     </row>
-    <row r="2342" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2342" spans="60:60">
       <c r="BH2342" s="18"/>
     </row>
-    <row r="2343" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2343" spans="60:60">
       <c r="BH2343" s="19"/>
     </row>
-    <row r="2344" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2344" spans="60:60">
       <c r="BH2344" s="19"/>
     </row>
-    <row r="2345" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2345" spans="60:60">
       <c r="BH2345" s="19"/>
     </row>
-    <row r="2346" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2346" spans="60:60">
       <c r="BH2346" s="19"/>
     </row>
-    <row r="2347" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2347" spans="60:60">
       <c r="BH2347" s="12"/>
     </row>
-    <row r="2348" spans="60:60" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2348" spans="60:60" ht="20.25">
       <c r="BH2348" s="15"/>
     </row>
-    <row r="2349" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2349" spans="60:60">
       <c r="BH2349" s="12"/>
     </row>
-    <row r="2350" spans="60:60" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2350" spans="60:60" ht="17.25">
       <c r="BH2350" s="13"/>
     </row>
-    <row r="2351" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2351" spans="60:60">
       <c r="BH2351" s="9"/>
     </row>
-    <row r="2352" spans="60:60" x14ac:dyDescent="0.25">
+    <row r="2352" spans="60:60">
       <c r="BH2352" s="19"/>
     </row>
   </sheetData>
@@ -17796,16 +18085,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>908</v>
       </c>
@@ -17813,7 +18102,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>910</v>
       </c>
@@ -17821,7 +18110,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>912</v>
       </c>
@@ -17829,7 +18118,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>914</v>
       </c>
@@ -17837,7 +18126,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>916</v>
       </c>
@@ -17845,7 +18134,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>918</v>
       </c>
@@ -17853,7 +18142,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>919</v>
       </c>
@@ -17861,7 +18150,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>920</v>
       </c>
@@ -17869,7 +18158,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>922</v>
       </c>
@@ -17877,7 +18166,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>923</v>
       </c>
@@ -17885,7 +18174,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
         <v>924</v>
       </c>
@@ -17893,7 +18182,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>926</v>
       </c>
@@ -17901,7 +18190,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
         <v>928</v>
       </c>
@@ -17909,7 +18198,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>930</v>
       </c>
@@ -17917,7 +18206,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>932</v>
       </c>
@@ -17925,7 +18214,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>934</v>
       </c>
@@ -17933,7 +18222,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>935</v>
       </c>
@@ -17941,7 +18230,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>936</v>
       </c>
@@ -17949,363 +18238,13 @@
         <v>933</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>937</v>
       </c>
       <c r="B19" t="s">
         <v>938</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="92" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>940</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>940</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>940</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="7"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="7"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="7"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="7"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="7"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="7"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="7"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="7"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="7"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="7"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="7"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="7"/>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="7"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="7"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="7"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="7"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="7"/>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="7"/>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="7"/>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="7"/>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="7"/>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="7"/>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="7"/>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="7"/>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="7"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="7"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="7"/>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="7"/>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="7"/>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="7"/>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="7"/>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="7"/>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40" s="7"/>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41" s="7"/>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B42" s="7"/>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B43" s="7"/>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B44" s="7"/>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B45" s="7"/>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B46" s="7"/>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B47" s="7"/>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B48" s="7"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="7"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="7"/>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="7"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="7"/>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" s="7"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" s="7"/>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" s="7"/>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" s="7"/>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" s="7"/>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58" s="7"/>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" s="7"/>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" s="7"/>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61" s="7"/>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B62" s="7"/>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B63" s="7"/>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B64" s="7"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" s="7"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" s="7"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" s="7"/>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" s="7"/>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" s="7"/>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B70" s="7"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B71" s="7"/>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B72" s="7"/>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B73" s="7"/>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B74" s="7"/>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B75" s="7"/>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" s="7"/>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B77" s="7"/>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B78" s="7"/>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B79" s="7"/>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B80" s="7"/>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B81" s="7"/>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B82" s="7"/>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B83" s="7"/>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B84" s="7"/>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B85" s="7"/>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B86" s="7"/>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B87" s="7"/>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B88" s="7"/>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B89" s="7"/>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B90" s="7"/>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B91" s="7"/>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B92" s="7"/>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B93" s="7"/>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B94" s="7"/>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B95" s="7"/>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B96" s="7"/>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B97" s="7"/>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B98" s="7"/>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B99" s="7"/>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B100" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18316,133 +18255,346 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:C100"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="65" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="92" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>912</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>955</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>961</v>
-      </c>
+        <v>913</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" s="7"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="7"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" s="7"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" s="7"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" s="7"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" s="7"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" s="7"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" s="7"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" s="7"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" s="7"/>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="7"/>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="7"/>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="7"/>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="7"/>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="7"/>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="7"/>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="7"/>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="7"/>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="7"/>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="7"/>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="7"/>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="7"/>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="7"/>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="7"/>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="7"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="7"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="7"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="7"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="7"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="7"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="7"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="7"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="7"/>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="7"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="7"/>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="7"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="7"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="7"/>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="7"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="7"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="7"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="7"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="7"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="7"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="7"/>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="7"/>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="7"/>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="7"/>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="7"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="7"/>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="7"/>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="7"/>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="7"/>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="7"/>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="7"/>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="7"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="7"/>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="7"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="7"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="7"/>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="7"/>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="7"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="7"/>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="7"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="7"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="7"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="7"/>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="7"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="7"/>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="7"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="7"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="7"/>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="7"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="7"/>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="7"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="7"/>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="7"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="7"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="7"/>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="7"/>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="7"/>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="7"/>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="7"/>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" s="7"/>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="7"/>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="7"/>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="7"/>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="7"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="7"/>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="7"/>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="7"/>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="7"/>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18453,15 +18605,338 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="65" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="21">
+      <c r="A18" s="31" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="33" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="29" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="29" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="29" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="29" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="29" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="29" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="29" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="29" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="29" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="23.25">
+      <c r="A31" s="32" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="29" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="29" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="29" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="29" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="29" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="25.5">
+      <c r="A39" s="29" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="25.5">
+      <c r="A40" s="29" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="29" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="29" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B42" s="30" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>962</v>
       </c>
@@ -18469,7 +18944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -18477,7 +18952,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -18485,7 +18960,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -18493,7 +18968,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -18501,7 +18976,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -18509,7 +18984,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -18517,7 +18992,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -18525,7 +19000,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -18533,7 +19008,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
